--- a/internal_doc/05.测试设计/特性守护矩阵.xlsx
+++ b/internal_doc/05.测试设计/特性守护矩阵.xlsx
@@ -12,14 +12,14 @@
     <sheet name="Sheet3" sheetId="3" r:id="rId3"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet1!$B$1:$H$24</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet1!$B$1:$H$58</definedName>
   </definedNames>
   <calcPr calcId="124519"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="193" uniqueCount="101">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="202" uniqueCount="106">
   <si>
     <t>优先级</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -145,283 +145,303 @@
     <phoneticPr fontId="8" type="noConversion"/>
   </si>
   <si>
+    <t>数据存储</t>
+    <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
+    <t>数据压缩</t>
+    <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
+    <t>数据在线重组</t>
+    <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
+    <t>数据离线重组</t>
+    <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
+    <t>监控管理</t>
+    <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
+    <t>配置管理</t>
+    <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
+    <t>策略管理</t>
+    <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
+    <t>接口</t>
+    <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
+    <t>c/c++</t>
+    <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
+    <t>c#</t>
+    <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
+    <t>java</t>
+    <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
+    <t>python</t>
+    <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
+    <t>javascript</t>
+    <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
+    <t>php</t>
+    <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
+    <t>rest</t>
+    <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
+    <t>与hadoop、hive集成</t>
+    <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
+    <t>与spark（spark sql\spark stream）集成</t>
+    <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
+    <t>与Postgrep SQL集成</t>
+    <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
+    <t>元数据操作</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>集合空间</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>集合</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve">集群管理 </t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>域</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>数据中心对外SSL加密传输</t>
+    <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
+    <t>日志归档、重放</t>
+    <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
+    <t>1至7多级别的一致性策略</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>全量同步</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>增量同步</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>集群、组、节点管理</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>扩容</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>索引</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>SQL</t>
+    <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
+    <t>kettle</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>基本CRUD操作（query,insert，update，delete，upsert，count，lob，findAndModify，findAndRemove）</t>
+    <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
+    <t>集合垂直分区（主子表）</t>
+    <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
+    <t>SequoiaDB</t>
+    <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
+    <t>第三方产品集成</t>
+    <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
+    <t>第三方产品集成</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>王文净</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>黄晓妮</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>吴艳</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>数据可靠性</t>
+    <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
+    <t>王文净</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>赵育</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>赵育</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>update，upsert：更新符</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>query: 匹配符，选择符，排序，hint，flag，skip,limit、查询优化器</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>快照监控</t>
+    <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
+    <t>黄晓妮</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>SCM</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>梁雪望</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>基本操作</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>读、写、删文件</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>多中心</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>文件管理</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>集群管理</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>文件迁移、清理、缓存</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>节点启停、部署、配置</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>劳景堂</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>刘晓璇</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>范瑜</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>林苏强</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>林苏强</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>陈思琴</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>梁雪望</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>劳景堂</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>陈思琴</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>孟春生</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
     <t>读写分离</t>
     <phoneticPr fontId="8" type="noConversion"/>
   </si>
   <si>
-    <t>数据存储</t>
-    <phoneticPr fontId="8" type="noConversion"/>
-  </si>
-  <si>
-    <t>数据压缩</t>
-    <phoneticPr fontId="8" type="noConversion"/>
-  </si>
-  <si>
-    <t>数据在线重组</t>
-    <phoneticPr fontId="8" type="noConversion"/>
-  </si>
-  <si>
-    <t>数据离线重组</t>
-    <phoneticPr fontId="8" type="noConversion"/>
-  </si>
-  <si>
-    <t>监控管理</t>
-    <phoneticPr fontId="8" type="noConversion"/>
-  </si>
-  <si>
-    <t>配置管理</t>
-    <phoneticPr fontId="8" type="noConversion"/>
-  </si>
-  <si>
-    <t>策略管理</t>
-    <phoneticPr fontId="8" type="noConversion"/>
-  </si>
-  <si>
-    <t>接口</t>
-    <phoneticPr fontId="8" type="noConversion"/>
-  </si>
-  <si>
-    <t>c/c++</t>
-    <phoneticPr fontId="8" type="noConversion"/>
-  </si>
-  <si>
-    <t>c#</t>
-    <phoneticPr fontId="8" type="noConversion"/>
-  </si>
-  <si>
-    <t>java</t>
-    <phoneticPr fontId="8" type="noConversion"/>
-  </si>
-  <si>
-    <t>python</t>
-    <phoneticPr fontId="8" type="noConversion"/>
-  </si>
-  <si>
-    <t>javascript</t>
-    <phoneticPr fontId="8" type="noConversion"/>
-  </si>
-  <si>
-    <t>php</t>
-    <phoneticPr fontId="8" type="noConversion"/>
-  </si>
-  <si>
-    <t>rest</t>
-    <phoneticPr fontId="8" type="noConversion"/>
-  </si>
-  <si>
-    <t>与hadoop、hive集成</t>
-    <phoneticPr fontId="8" type="noConversion"/>
-  </si>
-  <si>
-    <t>与spark（spark sql\spark stream）集成</t>
-    <phoneticPr fontId="8" type="noConversion"/>
-  </si>
-  <si>
-    <t>与Postgrep SQL集成</t>
-    <phoneticPr fontId="8" type="noConversion"/>
-  </si>
-  <si>
-    <t>元数据操作</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>集合空间</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>集合</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t xml:space="preserve">集群管理 </t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>域</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>数据中心对外SSL加密传输</t>
-    <phoneticPr fontId="8" type="noConversion"/>
-  </si>
-  <si>
-    <t>日志归档、重放</t>
-    <phoneticPr fontId="8" type="noConversion"/>
-  </si>
-  <si>
-    <t>1至7多级别的一致性策略</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>全量同步</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>增量同步</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>集群、组、节点管理</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>扩容</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>web页面操作</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>索引</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>SQL</t>
-    <phoneticPr fontId="8" type="noConversion"/>
-  </si>
-  <si>
-    <t>kettle</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>基本CRUD操作（query,insert，update，delete，upsert，count，lob，findAndModify，findAndRemove）</t>
-    <phoneticPr fontId="8" type="noConversion"/>
-  </si>
-  <si>
-    <t>集合垂直分区（主子表）</t>
-    <phoneticPr fontId="8" type="noConversion"/>
-  </si>
-  <si>
-    <t>SequoiaDB</t>
-    <phoneticPr fontId="8" type="noConversion"/>
-  </si>
-  <si>
-    <t>第三方产品集成</t>
-    <phoneticPr fontId="8" type="noConversion"/>
-  </si>
-  <si>
-    <t>第三方产品集成</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>王文净</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>黄晓妮</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>吴艳</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>数据可靠性</t>
-    <phoneticPr fontId="8" type="noConversion"/>
-  </si>
-  <si>
-    <t>王文净</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>赵育</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>赵育</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>update，upsert：更新符</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>query: 匹配符，选择符，排序，hint，flag，skip,limit、查询优化器</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>快照监控</t>
-    <phoneticPr fontId="8" type="noConversion"/>
-  </si>
-  <si>
-    <t>黄晓妮</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>SCM</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>梁雪望</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>基本操作</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>读、写、删文件</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>多中心</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>文件管理</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>集群管理</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>文件迁移、清理、缓存</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>节点启停、部署、配置</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>劳景堂</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>刘晓璇</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>范瑜</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>林苏强</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>林苏强</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>陈思琴</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>梁雪望</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>劳景堂</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>陈思琴</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>孟春生</t>
+    <t>安全性</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>登入登出、密码管理</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>查询条件</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>ScmQueryBuilder匹配符查询</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>跨中心缓存文件</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -605,28 +625,16 @@
     <xf numFmtId="0" fontId="6" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="7" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="6" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="8" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="8" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="5" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="5" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="9" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -640,8 +648,8 @@
     <xf numFmtId="0" fontId="0" fillId="6" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="7" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -649,8 +657,20 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="0" fillId="8" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="9" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -946,7 +966,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:J56"/>
+  <dimension ref="A1:J58"/>
   <sheetFormatPr defaultRowHeight="13.5"/>
   <cols>
     <col min="3" max="3" width="55.25" customWidth="1"/>
@@ -962,7 +982,7 @@
       <c r="A1" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="B1" s="24" t="s">
+      <c r="B1" s="20" t="s">
         <v>7</v>
       </c>
       <c r="C1" s="5" t="s">
@@ -991,21 +1011,21 @@
       </c>
     </row>
     <row r="2" spans="1:10">
-      <c r="A2" s="18" t="s">
-        <v>68</v>
-      </c>
-      <c r="B2" s="19" t="s">
+      <c r="A2" s="29" t="s">
+        <v>66</v>
+      </c>
+      <c r="B2" s="16" t="s">
         <v>10</v>
       </c>
-      <c r="C2" s="20" t="s">
+      <c r="C2" s="17" t="s">
         <v>11</v>
       </c>
       <c r="D2" s="3"/>
       <c r="E2" s="3" t="s">
-        <v>71</v>
+        <v>69</v>
       </c>
       <c r="F2" s="3" t="s">
-        <v>100</v>
+        <v>98</v>
       </c>
       <c r="G2" s="3"/>
       <c r="H2" s="3"/>
@@ -1013,19 +1033,19 @@
       <c r="J2" s="3"/>
     </row>
     <row r="3" spans="1:10">
-      <c r="A3" s="18"/>
-      <c r="B3" s="25" t="s">
+      <c r="A3" s="29"/>
+      <c r="B3" s="21" t="s">
         <v>12</v>
       </c>
-      <c r="C3" s="15" t="s">
-        <v>55</v>
+      <c r="C3" s="14" t="s">
+        <v>54</v>
       </c>
       <c r="D3" s="9"/>
       <c r="E3" s="3" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="F3" s="3" t="s">
-        <v>96</v>
+        <v>94</v>
       </c>
       <c r="G3" s="6"/>
       <c r="H3" s="3"/>
@@ -1033,19 +1053,19 @@
       <c r="J3" s="3"/>
     </row>
     <row r="4" spans="1:10" ht="27" customHeight="1">
-      <c r="A4" s="18"/>
-      <c r="B4" s="26" t="s">
-        <v>74</v>
-      </c>
-      <c r="C4" s="20" t="s">
+      <c r="A4" s="29"/>
+      <c r="B4" s="27" t="s">
+        <v>72</v>
+      </c>
+      <c r="C4" s="17" t="s">
         <v>13</v>
       </c>
       <c r="D4" s="3"/>
       <c r="E4" s="3" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="F4" s="3" t="s">
-        <v>97</v>
+        <v>95</v>
       </c>
       <c r="G4" s="6"/>
       <c r="H4" s="3"/>
@@ -1053,17 +1073,17 @@
       <c r="J4" s="3"/>
     </row>
     <row r="5" spans="1:10">
-      <c r="A5" s="18"/>
-      <c r="B5" s="26"/>
-      <c r="C5" s="20" t="s">
+      <c r="A5" s="29"/>
+      <c r="B5" s="27"/>
+      <c r="C5" s="17" t="s">
         <v>14</v>
       </c>
       <c r="D5" s="3"/>
       <c r="E5" s="3" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="F5" s="3" t="s">
-        <v>97</v>
+        <v>95</v>
       </c>
       <c r="G5" s="3"/>
       <c r="H5" s="3"/>
@@ -1071,17 +1091,17 @@
       <c r="J5" s="3"/>
     </row>
     <row r="6" spans="1:10">
-      <c r="A6" s="18"/>
-      <c r="B6" s="26"/>
-      <c r="C6" s="20" t="s">
+      <c r="A6" s="29"/>
+      <c r="B6" s="27"/>
+      <c r="C6" s="17" t="s">
         <v>15</v>
       </c>
       <c r="D6" s="10"/>
       <c r="E6" s="3" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="F6" s="3" t="s">
-        <v>97</v>
+        <v>95</v>
       </c>
       <c r="G6" s="6"/>
       <c r="H6" s="3"/>
@@ -1089,17 +1109,17 @@
       <c r="J6" s="3"/>
     </row>
     <row r="7" spans="1:10">
-      <c r="A7" s="18"/>
-      <c r="B7" s="26"/>
-      <c r="C7" s="20" t="s">
+      <c r="A7" s="29"/>
+      <c r="B7" s="27"/>
+      <c r="C7" s="17" t="s">
         <v>16</v>
       </c>
       <c r="D7" s="11"/>
       <c r="E7" s="3" t="s">
-        <v>81</v>
+        <v>79</v>
       </c>
       <c r="F7" s="3" t="s">
-        <v>91</v>
+        <v>89</v>
       </c>
       <c r="G7" s="6"/>
       <c r="H7" s="3"/>
@@ -1107,17 +1127,17 @@
       <c r="J7" s="3"/>
     </row>
     <row r="8" spans="1:10">
-      <c r="A8" s="18"/>
-      <c r="B8" s="26"/>
-      <c r="C8" s="20" t="s">
-        <v>56</v>
+      <c r="A8" s="29"/>
+      <c r="B8" s="27"/>
+      <c r="C8" s="17" t="s">
+        <v>55</v>
       </c>
       <c r="D8" s="3"/>
       <c r="E8" s="3" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="F8" s="3" t="s">
-        <v>91</v>
+        <v>89</v>
       </c>
       <c r="G8" s="7"/>
       <c r="H8" s="8"/>
@@ -1125,17 +1145,17 @@
       <c r="J8" s="3"/>
     </row>
     <row r="9" spans="1:10">
-      <c r="A9" s="18"/>
-      <c r="B9" s="26"/>
-      <c r="C9" s="20" t="s">
+      <c r="A9" s="29"/>
+      <c r="B9" s="27"/>
+      <c r="C9" s="17" t="s">
         <v>17</v>
       </c>
       <c r="D9" s="3"/>
       <c r="E9" s="3" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="F9" s="3" t="s">
-        <v>91</v>
+        <v>89</v>
       </c>
       <c r="G9" s="7"/>
       <c r="H9" s="8"/>
@@ -1143,17 +1163,17 @@
       <c r="J9" s="3"/>
     </row>
     <row r="10" spans="1:10">
-      <c r="A10" s="18"/>
-      <c r="B10" s="26"/>
-      <c r="C10" s="20" t="s">
+      <c r="A10" s="29"/>
+      <c r="B10" s="27"/>
+      <c r="C10" s="17" t="s">
         <v>18</v>
       </c>
       <c r="D10" s="3"/>
       <c r="E10" s="3" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="F10" s="3" t="s">
-        <v>91</v>
+        <v>89</v>
       </c>
       <c r="G10" s="7"/>
       <c r="H10" s="8"/>
@@ -1161,19 +1181,19 @@
       <c r="J10" s="3"/>
     </row>
     <row r="11" spans="1:10">
-      <c r="A11" s="18"/>
-      <c r="B11" s="14" t="s">
+      <c r="A11" s="29"/>
+      <c r="B11" s="26" t="s">
         <v>19</v>
       </c>
-      <c r="C11" s="15" t="s">
+      <c r="C11" s="14" t="s">
         <v>20</v>
       </c>
       <c r="D11" s="3"/>
       <c r="E11" s="3" t="s">
-        <v>75</v>
+        <v>73</v>
       </c>
       <c r="F11" s="3" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
       <c r="G11" s="12"/>
       <c r="H11" s="3"/>
@@ -1181,17 +1201,17 @@
       <c r="J11" s="3"/>
     </row>
     <row r="12" spans="1:10">
-      <c r="A12" s="18"/>
-      <c r="B12" s="14"/>
-      <c r="C12" s="15" t="s">
-        <v>57</v>
+      <c r="A12" s="29"/>
+      <c r="B12" s="26"/>
+      <c r="C12" s="14" t="s">
+        <v>56</v>
       </c>
       <c r="D12" s="3"/>
       <c r="E12" s="3" t="s">
-        <v>75</v>
+        <v>73</v>
       </c>
       <c r="F12" s="3" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
       <c r="G12" s="12"/>
       <c r="H12" s="3"/>
@@ -1199,17 +1219,17 @@
       <c r="J12" s="3"/>
     </row>
     <row r="13" spans="1:10">
-      <c r="A13" s="18"/>
-      <c r="B13" s="14"/>
-      <c r="C13" s="15" t="s">
-        <v>58</v>
+      <c r="A13" s="29"/>
+      <c r="B13" s="26"/>
+      <c r="C13" s="14" t="s">
+        <v>57</v>
       </c>
       <c r="D13" s="3"/>
       <c r="E13" s="3" t="s">
-        <v>75</v>
+        <v>73</v>
       </c>
       <c r="F13" s="3" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
       <c r="G13" s="12"/>
       <c r="H13" s="3"/>
@@ -1217,17 +1237,17 @@
       <c r="J13" s="3"/>
     </row>
     <row r="14" spans="1:10">
-      <c r="A14" s="18"/>
-      <c r="B14" s="14"/>
-      <c r="C14" s="15" t="s">
-        <v>59</v>
+      <c r="A14" s="29"/>
+      <c r="B14" s="26"/>
+      <c r="C14" s="14" t="s">
+        <v>58</v>
       </c>
       <c r="D14" s="3"/>
       <c r="E14" s="3" t="s">
-        <v>75</v>
+        <v>73</v>
       </c>
       <c r="F14" s="3" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
       <c r="G14" s="12"/>
       <c r="H14" s="3"/>
@@ -1235,19 +1255,19 @@
       <c r="J14" s="3"/>
     </row>
     <row r="15" spans="1:10">
-      <c r="A15" s="18"/>
-      <c r="B15" s="26" t="s">
+      <c r="A15" s="29"/>
+      <c r="B15" s="27" t="s">
         <v>21</v>
       </c>
-      <c r="C15" s="20" t="s">
+      <c r="C15" s="17" t="s">
         <v>22</v>
       </c>
       <c r="D15" s="3"/>
       <c r="E15" s="3" t="s">
-        <v>76</v>
+        <v>74</v>
       </c>
       <c r="F15" s="3" t="s">
-        <v>92</v>
+        <v>90</v>
       </c>
       <c r="G15" s="7"/>
       <c r="H15" s="8"/>
@@ -1255,17 +1275,17 @@
       <c r="J15" s="3"/>
     </row>
     <row r="16" spans="1:10">
-      <c r="A16" s="18"/>
-      <c r="B16" s="26"/>
-      <c r="C16" s="20" t="s">
-        <v>67</v>
+      <c r="A16" s="29"/>
+      <c r="B16" s="27"/>
+      <c r="C16" s="17" t="s">
+        <v>65</v>
       </c>
       <c r="D16" s="3"/>
       <c r="E16" s="3" t="s">
-        <v>76</v>
+        <v>74</v>
       </c>
       <c r="F16" s="3" t="s">
-        <v>92</v>
+        <v>90</v>
       </c>
       <c r="G16" s="12"/>
       <c r="H16" s="3"/>
@@ -1273,17 +1293,17 @@
       <c r="J16" s="3"/>
     </row>
     <row r="17" spans="1:10">
-      <c r="A17" s="18"/>
-      <c r="B17" s="26"/>
-      <c r="C17" s="20" t="s">
+      <c r="A17" s="29"/>
+      <c r="B17" s="27"/>
+      <c r="C17" s="17" t="s">
         <v>23</v>
       </c>
       <c r="D17" s="3"/>
       <c r="E17" s="3" t="s">
-        <v>76</v>
+        <v>74</v>
       </c>
       <c r="F17" s="3" t="s">
-        <v>92</v>
+        <v>90</v>
       </c>
       <c r="G17" s="13"/>
       <c r="H17" s="3"/>
@@ -1291,17 +1311,17 @@
       <c r="J17" s="3"/>
     </row>
     <row r="18" spans="1:10">
-      <c r="A18" s="18"/>
-      <c r="B18" s="26"/>
-      <c r="C18" s="20" t="s">
+      <c r="A18" s="29"/>
+      <c r="B18" s="27"/>
+      <c r="C18" s="17" t="s">
         <v>24</v>
       </c>
       <c r="D18" s="2"/>
       <c r="E18" s="3" t="s">
-        <v>76</v>
+        <v>74</v>
       </c>
       <c r="F18" s="3" t="s">
-        <v>92</v>
+        <v>90</v>
       </c>
       <c r="G18" s="6"/>
       <c r="H18" s="3"/>
@@ -1309,17 +1329,17 @@
       <c r="J18" s="3"/>
     </row>
     <row r="19" spans="1:10">
-      <c r="A19" s="18"/>
-      <c r="B19" s="26"/>
-      <c r="C19" s="20" t="s">
+      <c r="A19" s="29"/>
+      <c r="B19" s="27"/>
+      <c r="C19" s="17" t="s">
         <v>25</v>
       </c>
       <c r="D19" s="2"/>
       <c r="E19" s="3" t="s">
-        <v>76</v>
+        <v>74</v>
       </c>
       <c r="F19" s="3" t="s">
-        <v>92</v>
+        <v>90</v>
       </c>
       <c r="G19" s="7"/>
       <c r="H19" s="8"/>
@@ -1327,19 +1347,19 @@
       <c r="J19" s="3"/>
     </row>
     <row r="20" spans="1:10" ht="27">
-      <c r="A20" s="18"/>
-      <c r="B20" s="14" t="s">
+      <c r="A20" s="29"/>
+      <c r="B20" s="26" t="s">
         <v>26</v>
       </c>
-      <c r="C20" s="15" t="s">
-        <v>66</v>
+      <c r="C20" s="14" t="s">
+        <v>64</v>
       </c>
       <c r="D20" s="2"/>
       <c r="E20" s="3" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="F20" s="3" t="s">
-        <v>91</v>
+        <v>89</v>
       </c>
       <c r="G20" s="13"/>
       <c r="H20" s="3"/>
@@ -1347,17 +1367,17 @@
       <c r="J20" s="3"/>
     </row>
     <row r="21" spans="1:10" ht="27">
-      <c r="A21" s="18"/>
-      <c r="B21" s="14"/>
-      <c r="C21" s="15" t="s">
-        <v>79</v>
+      <c r="A21" s="29"/>
+      <c r="B21" s="26"/>
+      <c r="C21" s="14" t="s">
+        <v>77</v>
       </c>
       <c r="D21" s="2"/>
       <c r="E21" s="3" t="s">
-        <v>77</v>
+        <v>75</v>
       </c>
       <c r="F21" s="3" t="s">
-        <v>96</v>
+        <v>94</v>
       </c>
       <c r="G21" s="13"/>
       <c r="H21" s="3"/>
@@ -1365,17 +1385,17 @@
       <c r="J21" s="3"/>
     </row>
     <row r="22" spans="1:10">
-      <c r="A22" s="18"/>
-      <c r="B22" s="14"/>
-      <c r="C22" s="15" t="s">
-        <v>78</v>
+      <c r="A22" s="29"/>
+      <c r="B22" s="26"/>
+      <c r="C22" s="14" t="s">
+        <v>76</v>
       </c>
       <c r="D22" s="2"/>
       <c r="E22" s="3" t="s">
-        <v>77</v>
+        <v>75</v>
       </c>
       <c r="F22" s="3" t="s">
-        <v>92</v>
+        <v>90</v>
       </c>
       <c r="G22" s="13"/>
       <c r="H22" s="3"/>
@@ -1383,17 +1403,17 @@
       <c r="J22" s="3"/>
     </row>
     <row r="23" spans="1:10">
-      <c r="A23" s="18"/>
-      <c r="B23" s="14"/>
-      <c r="C23" s="15" t="s">
+      <c r="A23" s="29"/>
+      <c r="B23" s="26"/>
+      <c r="C23" s="14" t="s">
         <v>27</v>
       </c>
       <c r="D23" s="3"/>
       <c r="E23" s="3" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="F23" s="3" t="s">
-        <v>95</v>
+        <v>93</v>
       </c>
       <c r="G23" s="3"/>
       <c r="H23" s="3"/>
@@ -1401,17 +1421,17 @@
       <c r="J23" s="3"/>
     </row>
     <row r="24" spans="1:10">
-      <c r="A24" s="18"/>
-      <c r="B24" s="14"/>
-      <c r="C24" s="15" t="s">
+      <c r="A24" s="29"/>
+      <c r="B24" s="26"/>
+      <c r="C24" s="14" t="s">
         <v>28</v>
       </c>
       <c r="D24" s="3"/>
       <c r="E24" s="3" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="F24" s="3" t="s">
-        <v>95</v>
+        <v>93</v>
       </c>
       <c r="G24" s="7"/>
       <c r="H24" s="8"/>
@@ -1419,614 +1439,657 @@
       <c r="J24" s="3"/>
     </row>
     <row r="25" spans="1:10">
-      <c r="A25" s="18"/>
-      <c r="B25" s="14"/>
-      <c r="C25" s="15" t="s">
+      <c r="A25" s="29"/>
+      <c r="B25" s="26"/>
+      <c r="C25" s="14" t="s">
         <v>29</v>
       </c>
       <c r="D25" s="1"/>
       <c r="E25" s="3" t="s">
-        <v>77</v>
+        <v>75</v>
       </c>
       <c r="F25" s="3" t="s">
-        <v>92</v>
-      </c>
-      <c r="G25" s="24"/>
+        <v>90</v>
+      </c>
+      <c r="G25" s="20"/>
       <c r="H25" s="1"/>
       <c r="I25" s="1"/>
       <c r="J25" s="1"/>
     </row>
     <row r="26" spans="1:10">
-      <c r="A26" s="18"/>
-      <c r="B26" s="14"/>
-      <c r="C26" s="15" t="s">
+      <c r="A26" s="29"/>
+      <c r="B26" s="26"/>
+      <c r="C26" s="14" t="s">
         <v>30</v>
       </c>
       <c r="D26" s="1"/>
       <c r="E26" s="3" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="F26" s="3" t="s">
-        <v>95</v>
-      </c>
-      <c r="G26" s="24"/>
+        <v>93</v>
+      </c>
+      <c r="G26" s="20"/>
       <c r="H26" s="1"/>
       <c r="I26" s="1"/>
       <c r="J26" s="1"/>
     </row>
     <row r="27" spans="1:10">
-      <c r="A27" s="18"/>
-      <c r="B27" s="14"/>
-      <c r="C27" s="15" t="s">
-        <v>31</v>
+      <c r="A27" s="29"/>
+      <c r="B27" s="26"/>
+      <c r="C27" s="14" t="s">
+        <v>99</v>
       </c>
       <c r="D27" s="1"/>
       <c r="E27" s="3" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="F27" s="3" t="s">
-        <v>95</v>
-      </c>
-      <c r="G27" s="24"/>
+        <v>93</v>
+      </c>
+      <c r="G27" s="20"/>
       <c r="H27" s="1"/>
       <c r="I27" s="1"/>
       <c r="J27" s="1"/>
     </row>
     <row r="28" spans="1:10" ht="27" customHeight="1">
-      <c r="A28" s="18"/>
-      <c r="B28" s="16" t="s">
-        <v>50</v>
-      </c>
-      <c r="C28" s="17" t="s">
-        <v>54</v>
+      <c r="A28" s="29"/>
+      <c r="B28" s="25" t="s">
+        <v>49</v>
+      </c>
+      <c r="C28" s="15" t="s">
+        <v>53</v>
       </c>
       <c r="D28" s="1"/>
       <c r="E28" s="3" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="F28" s="1" t="s">
-        <v>93</v>
-      </c>
-      <c r="G28" s="24"/>
+        <v>91</v>
+      </c>
+      <c r="G28" s="20"/>
       <c r="H28" s="1"/>
       <c r="I28" s="1"/>
       <c r="J28" s="1"/>
     </row>
     <row r="29" spans="1:10">
-      <c r="A29" s="18"/>
-      <c r="B29" s="16"/>
-      <c r="C29" s="17" t="s">
-        <v>51</v>
+      <c r="A29" s="29"/>
+      <c r="B29" s="25"/>
+      <c r="C29" s="15" t="s">
+        <v>50</v>
       </c>
       <c r="D29" s="1"/>
       <c r="E29" s="3" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="F29" s="1" t="s">
-        <v>93</v>
-      </c>
-      <c r="G29" s="24"/>
+        <v>91</v>
+      </c>
+      <c r="G29" s="20"/>
       <c r="H29" s="1"/>
       <c r="I29" s="1"/>
       <c r="J29" s="1"/>
     </row>
     <row r="30" spans="1:10">
-      <c r="A30" s="18"/>
-      <c r="B30" s="16"/>
-      <c r="C30" s="17" t="s">
-        <v>52</v>
+      <c r="A30" s="29"/>
+      <c r="B30" s="25"/>
+      <c r="C30" s="15" t="s">
+        <v>51</v>
       </c>
       <c r="D30" s="1"/>
       <c r="E30" s="3" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="F30" s="1" t="s">
-        <v>93</v>
-      </c>
-      <c r="G30" s="24"/>
+        <v>91</v>
+      </c>
+      <c r="G30" s="20"/>
       <c r="H30" s="1"/>
       <c r="I30" s="1"/>
       <c r="J30" s="1"/>
     </row>
     <row r="31" spans="1:10">
-      <c r="A31" s="18"/>
-      <c r="B31" s="16"/>
-      <c r="C31" s="17" t="s">
-        <v>63</v>
+      <c r="A31" s="29"/>
+      <c r="B31" s="25"/>
+      <c r="C31" s="15" t="s">
+        <v>61</v>
       </c>
       <c r="D31" s="1"/>
       <c r="E31" s="1" t="s">
-        <v>76</v>
+        <v>74</v>
       </c>
       <c r="F31" s="3" t="s">
-        <v>96</v>
-      </c>
-      <c r="G31" s="24"/>
+        <v>94</v>
+      </c>
+      <c r="G31" s="20"/>
       <c r="H31" s="1"/>
       <c r="I31" s="1"/>
       <c r="J31" s="1"/>
     </row>
     <row r="32" spans="1:10">
-      <c r="A32" s="18"/>
-      <c r="B32" s="14" t="s">
-        <v>53</v>
-      </c>
-      <c r="C32" s="15" t="s">
-        <v>60</v>
+      <c r="A32" s="29"/>
+      <c r="B32" s="26" t="s">
+        <v>52</v>
+      </c>
+      <c r="C32" s="14" t="s">
+        <v>59</v>
       </c>
       <c r="D32" s="1"/>
       <c r="E32" s="3" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="F32" s="1" t="s">
-        <v>91</v>
-      </c>
-      <c r="G32" s="24"/>
+        <v>89</v>
+      </c>
+      <c r="G32" s="20"/>
       <c r="H32" s="1"/>
       <c r="I32" s="1"/>
       <c r="J32" s="1"/>
     </row>
     <row r="33" spans="1:10">
-      <c r="A33" s="18"/>
-      <c r="B33" s="14"/>
-      <c r="C33" s="15" t="s">
-        <v>62</v>
+      <c r="A33" s="29"/>
+      <c r="B33" s="26"/>
+      <c r="C33" s="14" t="s">
+        <v>100</v>
       </c>
       <c r="D33" s="1"/>
       <c r="E33" s="3" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="F33" s="1" t="s">
-        <v>91</v>
-      </c>
-      <c r="G33" s="24"/>
+        <v>89</v>
+      </c>
+      <c r="G33" s="20"/>
       <c r="H33" s="1"/>
       <c r="I33" s="1"/>
       <c r="J33" s="1"/>
     </row>
     <row r="34" spans="1:10">
-      <c r="A34" s="18"/>
-      <c r="B34" s="14"/>
-      <c r="C34" s="15" t="s">
-        <v>61</v>
+      <c r="A34" s="29"/>
+      <c r="B34" s="26"/>
+      <c r="C34" s="14" t="s">
+        <v>60</v>
       </c>
       <c r="D34" s="1"/>
       <c r="E34" s="3" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="F34" s="1" t="s">
-        <v>91</v>
-      </c>
-      <c r="G34" s="24"/>
+        <v>89</v>
+      </c>
+      <c r="G34" s="20"/>
       <c r="H34" s="1"/>
       <c r="I34" s="1"/>
       <c r="J34" s="1"/>
     </row>
     <row r="35" spans="1:10">
-      <c r="A35" s="18"/>
-      <c r="B35" s="26" t="s">
+      <c r="A35" s="29"/>
+      <c r="B35" s="27" t="s">
+        <v>31</v>
+      </c>
+      <c r="C35" s="17" t="s">
         <v>32</v>
-      </c>
-      <c r="C35" s="20" t="s">
-        <v>33</v>
       </c>
       <c r="D35" s="1"/>
       <c r="E35" s="3" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="F35" s="1" t="s">
-        <v>94</v>
-      </c>
-      <c r="G35" s="24"/>
+        <v>92</v>
+      </c>
+      <c r="G35" s="20"/>
       <c r="H35" s="1"/>
       <c r="I35" s="1"/>
       <c r="J35" s="1"/>
     </row>
     <row r="36" spans="1:10">
-      <c r="A36" s="18"/>
-      <c r="B36" s="26"/>
-      <c r="C36" s="20" t="s">
-        <v>34</v>
+      <c r="A36" s="29"/>
+      <c r="B36" s="27"/>
+      <c r="C36" s="17" t="s">
+        <v>33</v>
       </c>
       <c r="D36" s="1"/>
       <c r="E36" s="3" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="F36" s="1" t="s">
-        <v>94</v>
-      </c>
-      <c r="G36" s="24"/>
+        <v>92</v>
+      </c>
+      <c r="G36" s="20"/>
       <c r="H36" s="1"/>
       <c r="I36" s="1"/>
       <c r="J36" s="1"/>
     </row>
     <row r="37" spans="1:10">
-      <c r="A37" s="18"/>
-      <c r="B37" s="26"/>
-      <c r="C37" s="20" t="s">
-        <v>35</v>
+      <c r="A37" s="29"/>
+      <c r="B37" s="27"/>
+      <c r="C37" s="17" t="s">
+        <v>34</v>
       </c>
       <c r="D37" s="1"/>
       <c r="E37" s="3" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="F37" s="1" t="s">
-        <v>94</v>
-      </c>
-      <c r="G37" s="24"/>
+        <v>92</v>
+      </c>
+      <c r="G37" s="20"/>
       <c r="H37" s="1"/>
       <c r="I37" s="1"/>
       <c r="J37" s="1"/>
     </row>
     <row r="38" spans="1:10">
-      <c r="A38" s="18"/>
-      <c r="B38" s="14" t="s">
-        <v>36</v>
-      </c>
-      <c r="C38" s="15" t="s">
-        <v>80</v>
+      <c r="A38" s="29"/>
+      <c r="B38" s="26" t="s">
+        <v>35</v>
+      </c>
+      <c r="C38" s="14" t="s">
+        <v>78</v>
       </c>
       <c r="D38" s="1"/>
       <c r="E38" s="3" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="F38" s="1" t="s">
-        <v>93</v>
-      </c>
-      <c r="G38" s="24"/>
+        <v>91</v>
+      </c>
+      <c r="G38" s="20"/>
       <c r="H38" s="1"/>
       <c r="I38" s="1"/>
       <c r="J38" s="1"/>
     </row>
     <row r="39" spans="1:10">
-      <c r="A39" s="18"/>
-      <c r="B39" s="14"/>
-      <c r="C39" s="15" t="s">
-        <v>37</v>
+      <c r="A39" s="29"/>
+      <c r="B39" s="26"/>
+      <c r="C39" s="14" t="s">
+        <v>36</v>
       </c>
       <c r="D39" s="1"/>
       <c r="E39" s="3" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="F39" s="1" t="s">
-        <v>93</v>
-      </c>
-      <c r="G39" s="24"/>
+        <v>91</v>
+      </c>
+      <c r="G39" s="20"/>
       <c r="H39" s="1"/>
       <c r="I39" s="1"/>
       <c r="J39" s="1"/>
     </row>
     <row r="40" spans="1:10">
-      <c r="A40" s="18"/>
-      <c r="B40" s="14"/>
-      <c r="C40" s="15" t="s">
-        <v>38</v>
+      <c r="A40" s="29"/>
+      <c r="B40" s="26"/>
+      <c r="C40" s="14" t="s">
+        <v>37</v>
       </c>
       <c r="D40" s="1"/>
       <c r="E40" s="3" t="s">
-        <v>77</v>
+        <v>75</v>
       </c>
       <c r="F40" s="1" t="s">
-        <v>92</v>
-      </c>
-      <c r="G40" s="24"/>
+        <v>90</v>
+      </c>
+      <c r="G40" s="20"/>
       <c r="H40" s="1"/>
       <c r="I40" s="1"/>
       <c r="J40" s="1"/>
     </row>
     <row r="41" spans="1:10">
-      <c r="A41" s="18"/>
-      <c r="B41" s="26" t="s">
+      <c r="A41" s="29"/>
+      <c r="B41" s="27" t="s">
+        <v>38</v>
+      </c>
+      <c r="C41" s="17" t="s">
         <v>39</v>
-      </c>
-      <c r="C41" s="20" t="s">
-        <v>40</v>
       </c>
       <c r="D41" s="1"/>
       <c r="E41" s="3" t="s">
-        <v>75</v>
+        <v>73</v>
       </c>
       <c r="F41" s="1" t="s">
-        <v>83</v>
-      </c>
-      <c r="G41" s="24"/>
+        <v>81</v>
+      </c>
+      <c r="G41" s="20"/>
       <c r="H41" s="1"/>
       <c r="I41" s="1"/>
       <c r="J41" s="1"/>
     </row>
     <row r="42" spans="1:10">
-      <c r="A42" s="18"/>
-      <c r="B42" s="26"/>
-      <c r="C42" s="20" t="s">
-        <v>41</v>
+      <c r="A42" s="29"/>
+      <c r="B42" s="27"/>
+      <c r="C42" s="17" t="s">
+        <v>40</v>
       </c>
       <c r="D42" s="1"/>
       <c r="E42" s="3" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="F42" s="1" t="s">
-        <v>98</v>
-      </c>
-      <c r="G42" s="24"/>
+        <v>96</v>
+      </c>
+      <c r="G42" s="20"/>
       <c r="H42" s="1"/>
       <c r="I42" s="1"/>
       <c r="J42" s="1"/>
     </row>
     <row r="43" spans="1:10">
-      <c r="A43" s="18"/>
-      <c r="B43" s="26"/>
-      <c r="C43" s="20" t="s">
-        <v>42</v>
+      <c r="A43" s="29"/>
+      <c r="B43" s="27"/>
+      <c r="C43" s="17" t="s">
+        <v>41</v>
       </c>
       <c r="D43" s="1"/>
       <c r="E43" s="3" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="F43" s="1" t="s">
-        <v>98</v>
-      </c>
-      <c r="G43" s="24"/>
+        <v>96</v>
+      </c>
+      <c r="G43" s="20"/>
       <c r="H43" s="1"/>
       <c r="I43" s="1"/>
       <c r="J43" s="1"/>
     </row>
     <row r="44" spans="1:10">
-      <c r="A44" s="18"/>
-      <c r="B44" s="26"/>
-      <c r="C44" s="20" t="s">
-        <v>43</v>
+      <c r="A44" s="29"/>
+      <c r="B44" s="27"/>
+      <c r="C44" s="17" t="s">
+        <v>42</v>
       </c>
       <c r="D44" s="1"/>
       <c r="E44" s="3" t="s">
-        <v>76</v>
+        <v>74</v>
       </c>
       <c r="F44" s="1" t="s">
-        <v>99</v>
-      </c>
-      <c r="G44" s="24"/>
+        <v>97</v>
+      </c>
+      <c r="G44" s="20"/>
       <c r="H44" s="1"/>
       <c r="I44" s="1"/>
       <c r="J44" s="1"/>
     </row>
     <row r="45" spans="1:10">
-      <c r="A45" s="18"/>
-      <c r="B45" s="26"/>
-      <c r="C45" s="20" t="s">
-        <v>44</v>
+      <c r="A45" s="29"/>
+      <c r="B45" s="27"/>
+      <c r="C45" s="17" t="s">
+        <v>43</v>
       </c>
       <c r="D45" s="1"/>
       <c r="E45" s="3" t="s">
-        <v>75</v>
+        <v>73</v>
       </c>
       <c r="F45" s="1" t="s">
-        <v>100</v>
-      </c>
-      <c r="G45" s="24"/>
+        <v>98</v>
+      </c>
+      <c r="G45" s="20"/>
       <c r="H45" s="1"/>
       <c r="I45" s="1"/>
       <c r="J45" s="1"/>
     </row>
     <row r="46" spans="1:10">
-      <c r="A46" s="18"/>
-      <c r="B46" s="26"/>
-      <c r="C46" s="20" t="s">
-        <v>45</v>
+      <c r="A46" s="29"/>
+      <c r="B46" s="27"/>
+      <c r="C46" s="17" t="s">
+        <v>44</v>
       </c>
       <c r="D46" s="1"/>
       <c r="E46" s="3" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="F46" s="1" t="s">
-        <v>94</v>
-      </c>
-      <c r="G46" s="24"/>
+        <v>92</v>
+      </c>
+      <c r="G46" s="20"/>
       <c r="H46" s="1"/>
       <c r="I46" s="1"/>
       <c r="J46" s="1"/>
     </row>
     <row r="47" spans="1:10">
-      <c r="A47" s="18"/>
-      <c r="B47" s="26"/>
-      <c r="C47" s="20" t="s">
-        <v>64</v>
+      <c r="A47" s="29"/>
+      <c r="B47" s="27"/>
+      <c r="C47" s="17" t="s">
+        <v>62</v>
       </c>
       <c r="D47" s="1"/>
       <c r="E47" s="3" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="F47" s="1" t="s">
-        <v>94</v>
-      </c>
-      <c r="G47" s="24"/>
+        <v>92</v>
+      </c>
+      <c r="G47" s="20"/>
       <c r="H47" s="1"/>
       <c r="I47" s="1"/>
       <c r="J47" s="1"/>
     </row>
     <row r="48" spans="1:10">
-      <c r="A48" s="18"/>
-      <c r="B48" s="26"/>
-      <c r="C48" s="20" t="s">
-        <v>46</v>
+      <c r="A48" s="29"/>
+      <c r="B48" s="27"/>
+      <c r="C48" s="17" t="s">
+        <v>45</v>
       </c>
       <c r="D48" s="1"/>
       <c r="E48" s="3" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="F48" s="1" t="s">
-        <v>93</v>
-      </c>
-      <c r="G48" s="24"/>
+        <v>91</v>
+      </c>
+      <c r="G48" s="20"/>
       <c r="H48" s="1"/>
       <c r="I48" s="1"/>
       <c r="J48" s="1"/>
     </row>
     <row r="49" spans="1:10">
-      <c r="A49" s="21" t="s">
+      <c r="A49" s="28" t="s">
+        <v>80</v>
+      </c>
+      <c r="B49" s="18" t="s">
         <v>82</v>
       </c>
-      <c r="B49" s="22" t="s">
-        <v>84</v>
-      </c>
-      <c r="C49" s="23" t="s">
-        <v>85</v>
+      <c r="C49" s="19" t="s">
+        <v>83</v>
       </c>
       <c r="D49" s="1"/>
       <c r="E49" s="3" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="F49" s="1" t="s">
-        <v>93</v>
-      </c>
-      <c r="G49" s="24"/>
+        <v>91</v>
+      </c>
+      <c r="G49" s="20"/>
       <c r="H49" s="1"/>
       <c r="I49" s="1"/>
       <c r="J49" s="1"/>
     </row>
     <row r="50" spans="1:10">
-      <c r="A50" s="21"/>
-      <c r="B50" s="22" t="s">
-        <v>86</v>
-      </c>
-      <c r="C50" s="23"/>
+      <c r="A50" s="28"/>
+      <c r="B50" s="18" t="s">
+        <v>84</v>
+      </c>
+      <c r="C50" s="19" t="s">
+        <v>105</v>
+      </c>
       <c r="D50" s="1"/>
       <c r="E50" s="3" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="F50" s="1" t="s">
-        <v>93</v>
-      </c>
-      <c r="G50" s="24"/>
+        <v>91</v>
+      </c>
+      <c r="G50" s="20"/>
       <c r="H50" s="1"/>
       <c r="I50" s="1"/>
       <c r="J50" s="1"/>
     </row>
     <row r="51" spans="1:10">
-      <c r="A51" s="21"/>
-      <c r="B51" s="22" t="s">
+      <c r="A51" s="28"/>
+      <c r="B51" s="18" t="s">
+        <v>85</v>
+      </c>
+      <c r="C51" s="19" t="s">
         <v>87</v>
-      </c>
-      <c r="C51" s="23" t="s">
-        <v>89</v>
       </c>
       <c r="D51" s="1"/>
       <c r="E51" s="3" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="F51" s="1" t="s">
-        <v>93</v>
-      </c>
-      <c r="G51" s="24"/>
+        <v>91</v>
+      </c>
+      <c r="G51" s="20"/>
       <c r="H51" s="1"/>
       <c r="I51" s="1"/>
       <c r="J51" s="1"/>
     </row>
     <row r="52" spans="1:10">
-      <c r="A52" s="21"/>
-      <c r="B52" s="22" t="s">
+      <c r="A52" s="28"/>
+      <c r="B52" s="18" t="s">
+        <v>86</v>
+      </c>
+      <c r="C52" s="19" t="s">
         <v>88</v>
-      </c>
-      <c r="C52" s="23" t="s">
-        <v>90</v>
       </c>
       <c r="D52" s="1"/>
       <c r="E52" s="3" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="F52" s="1" t="s">
-        <v>93</v>
-      </c>
-      <c r="G52" s="24"/>
+        <v>91</v>
+      </c>
+      <c r="G52" s="20"/>
       <c r="H52" s="1"/>
       <c r="I52" s="1"/>
       <c r="J52" s="1"/>
     </row>
     <row r="53" spans="1:10">
-      <c r="A53" s="27" t="s">
-        <v>69</v>
-      </c>
-      <c r="B53" s="28" t="s">
-        <v>70</v>
-      </c>
-      <c r="C53" s="29" t="s">
-        <v>47</v>
+      <c r="A53" s="28"/>
+      <c r="B53" s="18" t="s">
+        <v>101</v>
+      </c>
+      <c r="C53" s="19" t="s">
+        <v>102</v>
       </c>
       <c r="D53" s="1"/>
       <c r="E53" s="3" t="s">
-        <v>75</v>
+        <v>70</v>
       </c>
       <c r="F53" s="1" t="s">
-        <v>100</v>
-      </c>
-      <c r="G53" s="24"/>
+        <v>91</v>
+      </c>
+      <c r="G53" s="20"/>
       <c r="H53" s="1"/>
       <c r="I53" s="1"/>
       <c r="J53" s="1"/>
     </row>
     <row r="54" spans="1:10">
-      <c r="A54" s="27"/>
-      <c r="B54" s="28"/>
-      <c r="C54" s="29" t="s">
-        <v>48</v>
+      <c r="A54" s="28"/>
+      <c r="B54" s="18" t="s">
+        <v>103</v>
+      </c>
+      <c r="C54" s="19" t="s">
+        <v>104</v>
       </c>
       <c r="D54" s="1"/>
       <c r="E54" s="3" t="s">
-        <v>73</v>
+        <v>70</v>
       </c>
       <c r="F54" s="1" t="s">
         <v>91</v>
       </c>
-      <c r="G54" s="24"/>
+      <c r="G54" s="20"/>
       <c r="H54" s="1"/>
       <c r="I54" s="1"/>
       <c r="J54" s="1"/>
     </row>
     <row r="55" spans="1:10">
-      <c r="A55" s="27"/>
-      <c r="B55" s="28"/>
-      <c r="C55" s="29" t="s">
-        <v>49</v>
+      <c r="A55" s="23" t="s">
+        <v>67</v>
+      </c>
+      <c r="B55" s="24" t="s">
+        <v>68</v>
+      </c>
+      <c r="C55" s="22" t="s">
+        <v>46</v>
       </c>
       <c r="D55" s="1"/>
       <c r="E55" s="3" t="s">
-        <v>76</v>
+        <v>73</v>
       </c>
       <c r="F55" s="1" t="s">
-        <v>92</v>
-      </c>
-      <c r="G55" s="24"/>
+        <v>98</v>
+      </c>
+      <c r="G55" s="20"/>
       <c r="H55" s="1"/>
       <c r="I55" s="1"/>
       <c r="J55" s="1"/>
     </row>
     <row r="56" spans="1:10">
-      <c r="A56" s="27"/>
-      <c r="B56" s="28"/>
-      <c r="C56" s="29" t="s">
-        <v>65</v>
+      <c r="A56" s="23"/>
+      <c r="B56" s="24"/>
+      <c r="C56" s="22" t="s">
+        <v>47</v>
       </c>
       <c r="D56" s="1"/>
       <c r="E56" s="3" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="F56" s="1" t="s">
-        <v>94</v>
-      </c>
-      <c r="G56" s="24"/>
+        <v>89</v>
+      </c>
+      <c r="G56" s="20"/>
       <c r="H56" s="1"/>
       <c r="I56" s="1"/>
       <c r="J56" s="1"/>
     </row>
+    <row r="57" spans="1:10">
+      <c r="A57" s="23"/>
+      <c r="B57" s="24"/>
+      <c r="C57" s="22" t="s">
+        <v>48</v>
+      </c>
+      <c r="D57" s="1"/>
+      <c r="E57" s="3" t="s">
+        <v>74</v>
+      </c>
+      <c r="F57" s="1" t="s">
+        <v>90</v>
+      </c>
+      <c r="G57" s="20"/>
+      <c r="H57" s="1"/>
+      <c r="I57" s="1"/>
+      <c r="J57" s="1"/>
+    </row>
+    <row r="58" spans="1:10">
+      <c r="A58" s="23"/>
+      <c r="B58" s="24"/>
+      <c r="C58" s="22" t="s">
+        <v>63</v>
+      </c>
+      <c r="D58" s="1"/>
+      <c r="E58" s="3" t="s">
+        <v>70</v>
+      </c>
+      <c r="F58" s="1" t="s">
+        <v>92</v>
+      </c>
+      <c r="G58" s="20"/>
+      <c r="H58" s="1"/>
+      <c r="I58" s="1"/>
+      <c r="J58" s="1"/>
+    </row>
   </sheetData>
-  <autoFilter ref="B1:H24">
+  <autoFilter ref="B1:H58">
+    <filterColumn colId="3"/>
     <filterColumn colId="5"/>
   </autoFilter>
   <mergeCells count="13">
-    <mergeCell ref="A53:A56"/>
-    <mergeCell ref="B53:B56"/>
+    <mergeCell ref="A55:A58"/>
+    <mergeCell ref="B55:B58"/>
     <mergeCell ref="B28:B31"/>
     <mergeCell ref="B32:B34"/>
     <mergeCell ref="B4:B10"/>
-    <mergeCell ref="A49:A52"/>
+    <mergeCell ref="A49:A54"/>
     <mergeCell ref="A2:A48"/>
     <mergeCell ref="B11:B14"/>
     <mergeCell ref="B15:B19"/>

--- a/internal_doc/05.测试设计/特性守护矩阵.xlsx
+++ b/internal_doc/05.测试设计/特性守护矩阵.xlsx
@@ -193,10 +193,6 @@
     <phoneticPr fontId="8" type="noConversion"/>
   </si>
   <si>
-    <t>javascript</t>
-    <phoneticPr fontId="8" type="noConversion"/>
-  </si>
-  <si>
     <t>php</t>
     <phoneticPr fontId="8" type="noConversion"/>
   </si>
@@ -443,6 +439,10 @@
   <si>
     <t>跨中心缓存文件</t>
     <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>javascript：shell，-s, -f</t>
+    <phoneticPr fontId="8" type="noConversion"/>
   </si>
 </sst>
 </file>
@@ -1012,7 +1012,7 @@
     </row>
     <row r="2" spans="1:10">
       <c r="A2" s="29" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="B2" s="16" t="s">
         <v>10</v>
@@ -1022,10 +1022,10 @@
       </c>
       <c r="D2" s="3"/>
       <c r="E2" s="3" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="F2" s="3" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="G2" s="3"/>
       <c r="H2" s="3"/>
@@ -1038,14 +1038,14 @@
         <v>12</v>
       </c>
       <c r="C3" s="14" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="D3" s="9"/>
       <c r="E3" s="3" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="F3" s="3" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="G3" s="6"/>
       <c r="H3" s="3"/>
@@ -1055,17 +1055,17 @@
     <row r="4" spans="1:10" ht="27" customHeight="1">
       <c r="A4" s="29"/>
       <c r="B4" s="27" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="C4" s="17" t="s">
         <v>13</v>
       </c>
       <c r="D4" s="3"/>
       <c r="E4" s="3" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="F4" s="3" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="G4" s="6"/>
       <c r="H4" s="3"/>
@@ -1080,10 +1080,10 @@
       </c>
       <c r="D5" s="3"/>
       <c r="E5" s="3" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="F5" s="3" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="G5" s="3"/>
       <c r="H5" s="3"/>
@@ -1098,10 +1098,10 @@
       </c>
       <c r="D6" s="10"/>
       <c r="E6" s="3" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="F6" s="3" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="G6" s="6"/>
       <c r="H6" s="3"/>
@@ -1116,10 +1116,10 @@
       </c>
       <c r="D7" s="11"/>
       <c r="E7" s="3" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="F7" s="3" t="s">
-        <v>89</v>
+        <v>91</v>
       </c>
       <c r="G7" s="6"/>
       <c r="H7" s="3"/>
@@ -1130,14 +1130,14 @@
       <c r="A8" s="29"/>
       <c r="B8" s="27"/>
       <c r="C8" s="17" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="D8" s="3"/>
       <c r="E8" s="3" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="F8" s="3" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="G8" s="7"/>
       <c r="H8" s="8"/>
@@ -1152,10 +1152,10 @@
       </c>
       <c r="D9" s="3"/>
       <c r="E9" s="3" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="F9" s="3" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="G9" s="7"/>
       <c r="H9" s="8"/>
@@ -1170,10 +1170,10 @@
       </c>
       <c r="D10" s="3"/>
       <c r="E10" s="3" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="F10" s="3" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="G10" s="7"/>
       <c r="H10" s="8"/>
@@ -1190,10 +1190,10 @@
       </c>
       <c r="D11" s="3"/>
       <c r="E11" s="3" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="F11" s="3" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="G11" s="12"/>
       <c r="H11" s="3"/>
@@ -1204,14 +1204,14 @@
       <c r="A12" s="29"/>
       <c r="B12" s="26"/>
       <c r="C12" s="14" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="D12" s="3"/>
       <c r="E12" s="3" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="F12" s="3" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="G12" s="12"/>
       <c r="H12" s="3"/>
@@ -1222,14 +1222,14 @@
       <c r="A13" s="29"/>
       <c r="B13" s="26"/>
       <c r="C13" s="14" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="D13" s="3"/>
       <c r="E13" s="3" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="F13" s="3" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="G13" s="12"/>
       <c r="H13" s="3"/>
@@ -1240,14 +1240,14 @@
       <c r="A14" s="29"/>
       <c r="B14" s="26"/>
       <c r="C14" s="14" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="D14" s="3"/>
       <c r="E14" s="3" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="F14" s="3" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="G14" s="12"/>
       <c r="H14" s="3"/>
@@ -1264,10 +1264,10 @@
       </c>
       <c r="D15" s="3"/>
       <c r="E15" s="3" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="F15" s="3" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="G15" s="7"/>
       <c r="H15" s="8"/>
@@ -1278,14 +1278,14 @@
       <c r="A16" s="29"/>
       <c r="B16" s="27"/>
       <c r="C16" s="17" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="D16" s="3"/>
       <c r="E16" s="3" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="F16" s="3" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="G16" s="12"/>
       <c r="H16" s="3"/>
@@ -1300,10 +1300,10 @@
       </c>
       <c r="D17" s="3"/>
       <c r="E17" s="3" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="F17" s="3" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="G17" s="13"/>
       <c r="H17" s="3"/>
@@ -1318,10 +1318,10 @@
       </c>
       <c r="D18" s="2"/>
       <c r="E18" s="3" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="F18" s="3" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="G18" s="6"/>
       <c r="H18" s="3"/>
@@ -1336,10 +1336,10 @@
       </c>
       <c r="D19" s="2"/>
       <c r="E19" s="3" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="F19" s="3" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="G19" s="7"/>
       <c r="H19" s="8"/>
@@ -1352,14 +1352,14 @@
         <v>26</v>
       </c>
       <c r="C20" s="14" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="D20" s="2"/>
       <c r="E20" s="3" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="F20" s="3" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="G20" s="13"/>
       <c r="H20" s="3"/>
@@ -1370,14 +1370,14 @@
       <c r="A21" s="29"/>
       <c r="B21" s="26"/>
       <c r="C21" s="14" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="D21" s="2"/>
       <c r="E21" s="3" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="F21" s="3" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="G21" s="13"/>
       <c r="H21" s="3"/>
@@ -1388,14 +1388,14 @@
       <c r="A22" s="29"/>
       <c r="B22" s="26"/>
       <c r="C22" s="14" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="D22" s="2"/>
       <c r="E22" s="3" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="F22" s="3" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="G22" s="13"/>
       <c r="H22" s="3"/>
@@ -1410,10 +1410,10 @@
       </c>
       <c r="D23" s="3"/>
       <c r="E23" s="3" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="F23" s="3" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="G23" s="3"/>
       <c r="H23" s="3"/>
@@ -1428,10 +1428,10 @@
       </c>
       <c r="D24" s="3"/>
       <c r="E24" s="3" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="F24" s="3" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="G24" s="7"/>
       <c r="H24" s="8"/>
@@ -1446,10 +1446,10 @@
       </c>
       <c r="D25" s="1"/>
       <c r="E25" s="3" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="F25" s="3" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="G25" s="20"/>
       <c r="H25" s="1"/>
@@ -1464,10 +1464,10 @@
       </c>
       <c r="D26" s="1"/>
       <c r="E26" s="3" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="F26" s="3" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="G26" s="20"/>
       <c r="H26" s="1"/>
@@ -1478,14 +1478,14 @@
       <c r="A27" s="29"/>
       <c r="B27" s="26"/>
       <c r="C27" s="14" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="D27" s="1"/>
       <c r="E27" s="3" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="F27" s="3" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="G27" s="20"/>
       <c r="H27" s="1"/>
@@ -1495,17 +1495,17 @@
     <row r="28" spans="1:10" ht="27" customHeight="1">
       <c r="A28" s="29"/>
       <c r="B28" s="25" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="C28" s="15" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="D28" s="1"/>
       <c r="E28" s="3" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="F28" s="1" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="G28" s="20"/>
       <c r="H28" s="1"/>
@@ -1516,14 +1516,14 @@
       <c r="A29" s="29"/>
       <c r="B29" s="25"/>
       <c r="C29" s="15" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="D29" s="1"/>
       <c r="E29" s="3" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="F29" s="1" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="G29" s="20"/>
       <c r="H29" s="1"/>
@@ -1534,14 +1534,14 @@
       <c r="A30" s="29"/>
       <c r="B30" s="25"/>
       <c r="C30" s="15" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="D30" s="1"/>
       <c r="E30" s="3" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="F30" s="1" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="G30" s="20"/>
       <c r="H30" s="1"/>
@@ -1552,14 +1552,14 @@
       <c r="A31" s="29"/>
       <c r="B31" s="25"/>
       <c r="C31" s="15" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="D31" s="1"/>
       <c r="E31" s="1" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="F31" s="3" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="G31" s="20"/>
       <c r="H31" s="1"/>
@@ -1569,17 +1569,17 @@
     <row r="32" spans="1:10">
       <c r="A32" s="29"/>
       <c r="B32" s="26" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="C32" s="14" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="D32" s="1"/>
       <c r="E32" s="3" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="F32" s="1" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="G32" s="20"/>
       <c r="H32" s="1"/>
@@ -1590,14 +1590,14 @@
       <c r="A33" s="29"/>
       <c r="B33" s="26"/>
       <c r="C33" s="14" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="D33" s="1"/>
       <c r="E33" s="3" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="F33" s="1" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="G33" s="20"/>
       <c r="H33" s="1"/>
@@ -1608,14 +1608,14 @@
       <c r="A34" s="29"/>
       <c r="B34" s="26"/>
       <c r="C34" s="14" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="D34" s="1"/>
       <c r="E34" s="3" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="F34" s="1" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="G34" s="20"/>
       <c r="H34" s="1"/>
@@ -1632,10 +1632,10 @@
       </c>
       <c r="D35" s="1"/>
       <c r="E35" s="3" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="F35" s="1" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="G35" s="20"/>
       <c r="H35" s="1"/>
@@ -1650,10 +1650,10 @@
       </c>
       <c r="D36" s="1"/>
       <c r="E36" s="3" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="F36" s="1" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="G36" s="20"/>
       <c r="H36" s="1"/>
@@ -1668,10 +1668,10 @@
       </c>
       <c r="D37" s="1"/>
       <c r="E37" s="3" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="F37" s="1" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="G37" s="20"/>
       <c r="H37" s="1"/>
@@ -1684,14 +1684,14 @@
         <v>35</v>
       </c>
       <c r="C38" s="14" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="D38" s="1"/>
       <c r="E38" s="3" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="F38" s="1" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="G38" s="20"/>
       <c r="H38" s="1"/>
@@ -1706,10 +1706,10 @@
       </c>
       <c r="D39" s="1"/>
       <c r="E39" s="3" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="F39" s="1" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="G39" s="20"/>
       <c r="H39" s="1"/>
@@ -1724,10 +1724,10 @@
       </c>
       <c r="D40" s="1"/>
       <c r="E40" s="3" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="F40" s="1" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="G40" s="20"/>
       <c r="H40" s="1"/>
@@ -1744,10 +1744,10 @@
       </c>
       <c r="D41" s="1"/>
       <c r="E41" s="3" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="F41" s="1" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="G41" s="20"/>
       <c r="H41" s="1"/>
@@ -1762,10 +1762,10 @@
       </c>
       <c r="D42" s="1"/>
       <c r="E42" s="3" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="F42" s="1" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="G42" s="20"/>
       <c r="H42" s="1"/>
@@ -1780,10 +1780,10 @@
       </c>
       <c r="D43" s="1"/>
       <c r="E43" s="3" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="F43" s="1" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="G43" s="20"/>
       <c r="H43" s="1"/>
@@ -1798,10 +1798,10 @@
       </c>
       <c r="D44" s="1"/>
       <c r="E44" s="3" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="F44" s="1" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="G44" s="20"/>
       <c r="H44" s="1"/>
@@ -1812,14 +1812,14 @@
       <c r="A45" s="29"/>
       <c r="B45" s="27"/>
       <c r="C45" s="17" t="s">
-        <v>43</v>
+        <v>105</v>
       </c>
       <c r="D45" s="1"/>
       <c r="E45" s="3" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="F45" s="1" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="G45" s="20"/>
       <c r="H45" s="1"/>
@@ -1830,14 +1830,14 @@
       <c r="A46" s="29"/>
       <c r="B46" s="27"/>
       <c r="C46" s="17" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="D46" s="1"/>
       <c r="E46" s="3" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="F46" s="1" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="G46" s="20"/>
       <c r="H46" s="1"/>
@@ -1848,14 +1848,14 @@
       <c r="A47" s="29"/>
       <c r="B47" s="27"/>
       <c r="C47" s="17" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="D47" s="1"/>
       <c r="E47" s="3" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="F47" s="1" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="G47" s="20"/>
       <c r="H47" s="1"/>
@@ -1866,14 +1866,14 @@
       <c r="A48" s="29"/>
       <c r="B48" s="27"/>
       <c r="C48" s="17" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="D48" s="1"/>
       <c r="E48" s="3" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="F48" s="1" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="G48" s="20"/>
       <c r="H48" s="1"/>
@@ -1882,20 +1882,20 @@
     </row>
     <row r="49" spans="1:10">
       <c r="A49" s="28" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="B49" s="18" t="s">
+        <v>81</v>
+      </c>
+      <c r="C49" s="19" t="s">
         <v>82</v>
-      </c>
-      <c r="C49" s="19" t="s">
-        <v>83</v>
       </c>
       <c r="D49" s="1"/>
       <c r="E49" s="3" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="F49" s="1" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="G49" s="20"/>
       <c r="H49" s="1"/>
@@ -1905,17 +1905,17 @@
     <row r="50" spans="1:10">
       <c r="A50" s="28"/>
       <c r="B50" s="18" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="C50" s="19" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="D50" s="1"/>
       <c r="E50" s="3" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="F50" s="1" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="G50" s="20"/>
       <c r="H50" s="1"/>
@@ -1925,17 +1925,17 @@
     <row r="51" spans="1:10">
       <c r="A51" s="28"/>
       <c r="B51" s="18" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="C51" s="19" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="D51" s="1"/>
       <c r="E51" s="3" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="F51" s="1" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="G51" s="20"/>
       <c r="H51" s="1"/>
@@ -1945,17 +1945,17 @@
     <row r="52" spans="1:10">
       <c r="A52" s="28"/>
       <c r="B52" s="18" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="C52" s="19" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="D52" s="1"/>
       <c r="E52" s="3" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="F52" s="1" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="G52" s="20"/>
       <c r="H52" s="1"/>
@@ -1965,17 +1965,17 @@
     <row r="53" spans="1:10">
       <c r="A53" s="28"/>
       <c r="B53" s="18" t="s">
+        <v>100</v>
+      </c>
+      <c r="C53" s="19" t="s">
         <v>101</v>
-      </c>
-      <c r="C53" s="19" t="s">
-        <v>102</v>
       </c>
       <c r="D53" s="1"/>
       <c r="E53" s="3" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="F53" s="1" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="G53" s="20"/>
       <c r="H53" s="1"/>
@@ -1985,17 +1985,17 @@
     <row r="54" spans="1:10">
       <c r="A54" s="28"/>
       <c r="B54" s="18" t="s">
+        <v>102</v>
+      </c>
+      <c r="C54" s="19" t="s">
         <v>103</v>
-      </c>
-      <c r="C54" s="19" t="s">
-        <v>104</v>
       </c>
       <c r="D54" s="1"/>
       <c r="E54" s="3" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="F54" s="1" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="G54" s="20"/>
       <c r="H54" s="1"/>
@@ -2004,20 +2004,20 @@
     </row>
     <row r="55" spans="1:10">
       <c r="A55" s="23" t="s">
+        <v>66</v>
+      </c>
+      <c r="B55" s="24" t="s">
         <v>67</v>
       </c>
-      <c r="B55" s="24" t="s">
-        <v>68</v>
-      </c>
       <c r="C55" s="22" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="D55" s="1"/>
       <c r="E55" s="3" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="F55" s="1" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="G55" s="20"/>
       <c r="H55" s="1"/>
@@ -2028,14 +2028,14 @@
       <c r="A56" s="23"/>
       <c r="B56" s="24"/>
       <c r="C56" s="22" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="D56" s="1"/>
       <c r="E56" s="3" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="F56" s="1" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="G56" s="20"/>
       <c r="H56" s="1"/>
@@ -2046,14 +2046,14 @@
       <c r="A57" s="23"/>
       <c r="B57" s="24"/>
       <c r="C57" s="22" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="D57" s="1"/>
       <c r="E57" s="3" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="F57" s="1" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="G57" s="20"/>
       <c r="H57" s="1"/>
@@ -2064,14 +2064,14 @@
       <c r="A58" s="23"/>
       <c r="B58" s="24"/>
       <c r="C58" s="22" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="D58" s="1"/>
       <c r="E58" s="3" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="F58" s="1" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="G58" s="20"/>
       <c r="H58" s="1"/>

--- a/internal_doc/05.测试设计/特性守护矩阵.xlsx
+++ b/internal_doc/05.测试设计/特性守护矩阵.xlsx
@@ -12,14 +12,14 @@
     <sheet name="Sheet3" sheetId="3" r:id="rId3"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet1!$B$1:$H$58</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet1!$B$1:$H$59</definedName>
   </definedNames>
   <calcPr calcId="124519"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="202" uniqueCount="106">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="203" uniqueCount="107">
   <si>
     <t>优先级</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -417,32 +417,36 @@
     <phoneticPr fontId="8" type="noConversion"/>
   </si>
   <si>
+    <t>安全性</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>登入登出、密码管理</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>查询条件</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>ScmQueryBuilder匹配符查询</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>跨中心缓存文件</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>javascript：shell，-s, -f</t>
+    <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
     <t>web页面操作</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>安全性</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>登入登出、密码管理</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>查询条件</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>ScmQueryBuilder匹配符查询</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>跨中心缓存文件</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>javascript：shell，-s, -f</t>
-    <phoneticPr fontId="8" type="noConversion"/>
+    <t>安装、部署</t>
+    <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
 </file>
@@ -966,7 +970,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:J58"/>
+  <dimension ref="A1:J59"/>
   <sheetFormatPr defaultRowHeight="13.5"/>
   <cols>
     <col min="3" max="3" width="55.25" customWidth="1"/>
@@ -1590,7 +1594,7 @@
       <c r="A33" s="29"/>
       <c r="B33" s="26"/>
       <c r="C33" s="14" t="s">
-        <v>99</v>
+        <v>106</v>
       </c>
       <c r="D33" s="1"/>
       <c r="E33" s="3" t="s">
@@ -1608,15 +1612,11 @@
       <c r="A34" s="29"/>
       <c r="B34" s="26"/>
       <c r="C34" s="14" t="s">
-        <v>59</v>
+        <v>105</v>
       </c>
       <c r="D34" s="1"/>
-      <c r="E34" s="3" t="s">
-        <v>70</v>
-      </c>
-      <c r="F34" s="1" t="s">
-        <v>88</v>
-      </c>
+      <c r="E34" s="3"/>
+      <c r="F34" s="1"/>
       <c r="G34" s="20"/>
       <c r="H34" s="1"/>
       <c r="I34" s="1"/>
@@ -1624,18 +1624,16 @@
     </row>
     <row r="35" spans="1:10">
       <c r="A35" s="29"/>
-      <c r="B35" s="27" t="s">
-        <v>31</v>
-      </c>
-      <c r="C35" s="17" t="s">
-        <v>32</v>
+      <c r="B35" s="26"/>
+      <c r="C35" s="14" t="s">
+        <v>59</v>
       </c>
       <c r="D35" s="1"/>
       <c r="E35" s="3" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="F35" s="1" t="s">
-        <v>91</v>
+        <v>88</v>
       </c>
       <c r="G35" s="20"/>
       <c r="H35" s="1"/>
@@ -1644,9 +1642,11 @@
     </row>
     <row r="36" spans="1:10">
       <c r="A36" s="29"/>
-      <c r="B36" s="27"/>
+      <c r="B36" s="27" t="s">
+        <v>31</v>
+      </c>
       <c r="C36" s="17" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="D36" s="1"/>
       <c r="E36" s="3" t="s">
@@ -1664,7 +1664,7 @@
       <c r="A37" s="29"/>
       <c r="B37" s="27"/>
       <c r="C37" s="17" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="D37" s="1"/>
       <c r="E37" s="3" t="s">
@@ -1680,18 +1680,16 @@
     </row>
     <row r="38" spans="1:10">
       <c r="A38" s="29"/>
-      <c r="B38" s="26" t="s">
-        <v>35</v>
-      </c>
-      <c r="C38" s="14" t="s">
-        <v>77</v>
+      <c r="B38" s="27"/>
+      <c r="C38" s="17" t="s">
+        <v>34</v>
       </c>
       <c r="D38" s="1"/>
       <c r="E38" s="3" t="s">
         <v>69</v>
       </c>
       <c r="F38" s="1" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="G38" s="20"/>
       <c r="H38" s="1"/>
@@ -1700,9 +1698,11 @@
     </row>
     <row r="39" spans="1:10">
       <c r="A39" s="29"/>
-      <c r="B39" s="26"/>
+      <c r="B39" s="26" t="s">
+        <v>35</v>
+      </c>
       <c r="C39" s="14" t="s">
-        <v>36</v>
+        <v>77</v>
       </c>
       <c r="D39" s="1"/>
       <c r="E39" s="3" t="s">
@@ -1720,14 +1720,14 @@
       <c r="A40" s="29"/>
       <c r="B40" s="26"/>
       <c r="C40" s="14" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="D40" s="1"/>
       <c r="E40" s="3" t="s">
-        <v>74</v>
+        <v>69</v>
       </c>
       <c r="F40" s="1" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="G40" s="20"/>
       <c r="H40" s="1"/>
@@ -1736,18 +1736,16 @@
     </row>
     <row r="41" spans="1:10">
       <c r="A41" s="29"/>
-      <c r="B41" s="27" t="s">
-        <v>38</v>
-      </c>
-      <c r="C41" s="17" t="s">
-        <v>39</v>
+      <c r="B41" s="26"/>
+      <c r="C41" s="14" t="s">
+        <v>37</v>
       </c>
       <c r="D41" s="1"/>
       <c r="E41" s="3" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="F41" s="1" t="s">
-        <v>80</v>
+        <v>89</v>
       </c>
       <c r="G41" s="20"/>
       <c r="H41" s="1"/>
@@ -1756,16 +1754,18 @@
     </row>
     <row r="42" spans="1:10">
       <c r="A42" s="29"/>
-      <c r="B42" s="27"/>
+      <c r="B42" s="27" t="s">
+        <v>38</v>
+      </c>
       <c r="C42" s="17" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="D42" s="1"/>
       <c r="E42" s="3" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="F42" s="1" t="s">
-        <v>95</v>
+        <v>80</v>
       </c>
       <c r="G42" s="20"/>
       <c r="H42" s="1"/>
@@ -1776,7 +1776,7 @@
       <c r="A43" s="29"/>
       <c r="B43" s="27"/>
       <c r="C43" s="17" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="D43" s="1"/>
       <c r="E43" s="3" t="s">
@@ -1794,14 +1794,14 @@
       <c r="A44" s="29"/>
       <c r="B44" s="27"/>
       <c r="C44" s="17" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="D44" s="1"/>
       <c r="E44" s="3" t="s">
-        <v>73</v>
+        <v>70</v>
       </c>
       <c r="F44" s="1" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="G44" s="20"/>
       <c r="H44" s="1"/>
@@ -1812,14 +1812,14 @@
       <c r="A45" s="29"/>
       <c r="B45" s="27"/>
       <c r="C45" s="17" t="s">
-        <v>105</v>
+        <v>42</v>
       </c>
       <c r="D45" s="1"/>
       <c r="E45" s="3" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="F45" s="1" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="G45" s="20"/>
       <c r="H45" s="1"/>
@@ -1830,14 +1830,14 @@
       <c r="A46" s="29"/>
       <c r="B46" s="27"/>
       <c r="C46" s="17" t="s">
-        <v>43</v>
+        <v>104</v>
       </c>
       <c r="D46" s="1"/>
       <c r="E46" s="3" t="s">
-        <v>69</v>
+        <v>72</v>
       </c>
       <c r="F46" s="1" t="s">
-        <v>91</v>
+        <v>97</v>
       </c>
       <c r="G46" s="20"/>
       <c r="H46" s="1"/>
@@ -1848,7 +1848,7 @@
       <c r="A47" s="29"/>
       <c r="B47" s="27"/>
       <c r="C47" s="17" t="s">
-        <v>61</v>
+        <v>43</v>
       </c>
       <c r="D47" s="1"/>
       <c r="E47" s="3" t="s">
@@ -1866,14 +1866,14 @@
       <c r="A48" s="29"/>
       <c r="B48" s="27"/>
       <c r="C48" s="17" t="s">
-        <v>44</v>
+        <v>61</v>
       </c>
       <c r="D48" s="1"/>
       <c r="E48" s="3" t="s">
         <v>69</v>
       </c>
       <c r="F48" s="1" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="G48" s="20"/>
       <c r="H48" s="1"/>
@@ -1881,14 +1881,10 @@
       <c r="J48" s="1"/>
     </row>
     <row r="49" spans="1:10">
-      <c r="A49" s="28" t="s">
-        <v>79</v>
-      </c>
-      <c r="B49" s="18" t="s">
-        <v>81</v>
-      </c>
-      <c r="C49" s="19" t="s">
-        <v>82</v>
+      <c r="A49" s="29"/>
+      <c r="B49" s="27"/>
+      <c r="C49" s="17" t="s">
+        <v>44</v>
       </c>
       <c r="D49" s="1"/>
       <c r="E49" s="3" t="s">
@@ -1903,12 +1899,14 @@
       <c r="J49" s="1"/>
     </row>
     <row r="50" spans="1:10">
-      <c r="A50" s="28"/>
+      <c r="A50" s="28" t="s">
+        <v>79</v>
+      </c>
       <c r="B50" s="18" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
       <c r="C50" s="19" t="s">
-        <v>104</v>
+        <v>82</v>
       </c>
       <c r="D50" s="1"/>
       <c r="E50" s="3" t="s">
@@ -1925,10 +1923,10 @@
     <row r="51" spans="1:10">
       <c r="A51" s="28"/>
       <c r="B51" s="18" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="C51" s="19" t="s">
-        <v>86</v>
+        <v>103</v>
       </c>
       <c r="D51" s="1"/>
       <c r="E51" s="3" t="s">
@@ -1945,10 +1943,10 @@
     <row r="52" spans="1:10">
       <c r="A52" s="28"/>
       <c r="B52" s="18" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="C52" s="19" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="D52" s="1"/>
       <c r="E52" s="3" t="s">
@@ -1965,10 +1963,10 @@
     <row r="53" spans="1:10">
       <c r="A53" s="28"/>
       <c r="B53" s="18" t="s">
-        <v>100</v>
+        <v>85</v>
       </c>
       <c r="C53" s="19" t="s">
-        <v>101</v>
+        <v>87</v>
       </c>
       <c r="D53" s="1"/>
       <c r="E53" s="3" t="s">
@@ -1985,10 +1983,10 @@
     <row r="54" spans="1:10">
       <c r="A54" s="28"/>
       <c r="B54" s="18" t="s">
-        <v>102</v>
+        <v>99</v>
       </c>
       <c r="C54" s="19" t="s">
-        <v>103</v>
+        <v>100</v>
       </c>
       <c r="D54" s="1"/>
       <c r="E54" s="3" t="s">
@@ -2003,21 +2001,19 @@
       <c r="J54" s="1"/>
     </row>
     <row r="55" spans="1:10">
-      <c r="A55" s="23" t="s">
-        <v>66</v>
-      </c>
-      <c r="B55" s="24" t="s">
-        <v>67</v>
-      </c>
-      <c r="C55" s="22" t="s">
-        <v>45</v>
+      <c r="A55" s="28"/>
+      <c r="B55" s="18" t="s">
+        <v>101</v>
+      </c>
+      <c r="C55" s="19" t="s">
+        <v>102</v>
       </c>
       <c r="D55" s="1"/>
       <c r="E55" s="3" t="s">
-        <v>72</v>
+        <v>69</v>
       </c>
       <c r="F55" s="1" t="s">
-        <v>97</v>
+        <v>90</v>
       </c>
       <c r="G55" s="20"/>
       <c r="H55" s="1"/>
@@ -2025,17 +2021,21 @@
       <c r="J55" s="1"/>
     </row>
     <row r="56" spans="1:10">
-      <c r="A56" s="23"/>
-      <c r="B56" s="24"/>
+      <c r="A56" s="23" t="s">
+        <v>66</v>
+      </c>
+      <c r="B56" s="24" t="s">
+        <v>67</v>
+      </c>
       <c r="C56" s="22" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="D56" s="1"/>
       <c r="E56" s="3" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="F56" s="1" t="s">
-        <v>88</v>
+        <v>97</v>
       </c>
       <c r="G56" s="20"/>
       <c r="H56" s="1"/>
@@ -2046,14 +2046,14 @@
       <c r="A57" s="23"/>
       <c r="B57" s="24"/>
       <c r="C57" s="22" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="D57" s="1"/>
       <c r="E57" s="3" t="s">
-        <v>73</v>
+        <v>70</v>
       </c>
       <c r="F57" s="1" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="G57" s="20"/>
       <c r="H57" s="1"/>
@@ -2064,39 +2064,57 @@
       <c r="A58" s="23"/>
       <c r="B58" s="24"/>
       <c r="C58" s="22" t="s">
-        <v>62</v>
+        <v>47</v>
       </c>
       <c r="D58" s="1"/>
       <c r="E58" s="3" t="s">
-        <v>69</v>
+        <v>73</v>
       </c>
       <c r="F58" s="1" t="s">
-        <v>91</v>
+        <v>89</v>
       </c>
       <c r="G58" s="20"/>
       <c r="H58" s="1"/>
       <c r="I58" s="1"/>
       <c r="J58" s="1"/>
     </row>
+    <row r="59" spans="1:10">
+      <c r="A59" s="23"/>
+      <c r="B59" s="24"/>
+      <c r="C59" s="22" t="s">
+        <v>62</v>
+      </c>
+      <c r="D59" s="1"/>
+      <c r="E59" s="3" t="s">
+        <v>69</v>
+      </c>
+      <c r="F59" s="1" t="s">
+        <v>91</v>
+      </c>
+      <c r="G59" s="20"/>
+      <c r="H59" s="1"/>
+      <c r="I59" s="1"/>
+      <c r="J59" s="1"/>
+    </row>
   </sheetData>
-  <autoFilter ref="B1:H58">
+  <autoFilter ref="B1:H59">
     <filterColumn colId="3"/>
     <filterColumn colId="5"/>
   </autoFilter>
   <mergeCells count="13">
-    <mergeCell ref="A55:A58"/>
-    <mergeCell ref="B55:B58"/>
+    <mergeCell ref="A56:A59"/>
+    <mergeCell ref="B56:B59"/>
     <mergeCell ref="B28:B31"/>
-    <mergeCell ref="B32:B34"/>
+    <mergeCell ref="B32:B35"/>
     <mergeCell ref="B4:B10"/>
-    <mergeCell ref="A49:A54"/>
-    <mergeCell ref="A2:A48"/>
+    <mergeCell ref="A50:A55"/>
+    <mergeCell ref="A2:A49"/>
     <mergeCell ref="B11:B14"/>
     <mergeCell ref="B15:B19"/>
     <mergeCell ref="B20:B27"/>
-    <mergeCell ref="B35:B37"/>
-    <mergeCell ref="B38:B40"/>
-    <mergeCell ref="B41:B48"/>
+    <mergeCell ref="B36:B38"/>
+    <mergeCell ref="B39:B41"/>
+    <mergeCell ref="B42:B49"/>
   </mergeCells>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/internal_doc/05.测试设计/特性守护矩阵.xlsx
+++ b/internal_doc/05.测试设计/特性守护矩阵.xlsx
@@ -19,7 +19,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="203" uniqueCount="107">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="205" uniqueCount="107">
   <si>
     <t>优先级</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -1615,8 +1615,12 @@
         <v>105</v>
       </c>
       <c r="D34" s="1"/>
-      <c r="E34" s="3"/>
-      <c r="F34" s="1"/>
+      <c r="E34" s="3" t="s">
+        <v>70</v>
+      </c>
+      <c r="F34" s="1" t="s">
+        <v>88</v>
+      </c>
       <c r="G34" s="20"/>
       <c r="H34" s="1"/>
       <c r="I34" s="1"/>

--- a/internal_doc/05.测试设计/特性守护矩阵.xlsx
+++ b/internal_doc/05.测试设计/特性守护矩阵.xlsx
@@ -401,7 +401,43 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>劳景堂</t>
+    <t>孟春生</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>读写分离</t>
+    <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
+    <t>安全性</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>登入登出、密码管理</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>查询条件</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>ScmQueryBuilder匹配符查询</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>跨中心缓存文件</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>javascript：shell，-s, -f</t>
+    <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
+    <t>web页面操作</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>安装、部署</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
@@ -409,43 +445,7 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>孟春生</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>读写分离</t>
-    <phoneticPr fontId="8" type="noConversion"/>
-  </si>
-  <si>
-    <t>安全性</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>登入登出、密码管理</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>查询条件</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>ScmQueryBuilder匹配符查询</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>跨中心缓存文件</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>javascript：shell，-s, -f</t>
-    <phoneticPr fontId="8" type="noConversion"/>
-  </si>
-  <si>
-    <t>web页面操作</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>安装、部署</t>
+    <t>刘晓璇</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -682,6 +682,74 @@
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
+  <colors>
+    <indexedColors>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008000"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00808000"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="00C0C0C0"/>
+      <rgbColor rgb="00808080"/>
+      <rgbColor rgb="009999FF"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00FFFFCC"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00660066"/>
+      <rgbColor rgb="00FF8080"/>
+      <rgbColor rgb="000066CC"/>
+      <rgbColor rgb="00CCCCFF"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="0000CCFF"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00CCFFCC"/>
+      <rgbColor rgb="00FFFF99"/>
+      <rgbColor rgb="0099CCFF"/>
+      <rgbColor rgb="00FF99CC"/>
+      <rgbColor rgb="00CC99FF"/>
+      <rgbColor rgb="00FFCC99"/>
+      <rgbColor rgb="003366FF"/>
+      <rgbColor rgb="0033CCCC"/>
+      <rgbColor rgb="0099CC00"/>
+      <rgbColor rgb="00FFCC00"/>
+      <rgbColor rgb="00FF9900"/>
+      <rgbColor rgb="00FF6600"/>
+      <rgbColor rgb="00666699"/>
+      <rgbColor rgb="00969696"/>
+      <rgbColor rgb="00003366"/>
+      <rgbColor rgb="00339966"/>
+      <rgbColor rgb="00003300"/>
+      <rgbColor rgb="00333300"/>
+      <rgbColor rgb="00993300"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00333399"/>
+      <rgbColor rgb="00333333"/>
+    </indexedColors>
+  </colors>
 </styleSheet>
 </file>
 
@@ -693,7 +761,7 @@
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
       <a:lt1>
-        <a:sysClr val="window" lastClr="FFFFFF"/>
+        <a:sysClr val="window" lastClr="CCE8CF"/>
       </a:lt1>
       <a:dk2>
         <a:srgbClr val="1F497D"/>
@@ -1029,7 +1097,7 @@
         <v>68</v>
       </c>
       <c r="F2" s="3" t="s">
-        <v>97</v>
+        <v>95</v>
       </c>
       <c r="G2" s="3"/>
       <c r="H2" s="3"/>
@@ -1141,7 +1209,7 @@
         <v>70</v>
       </c>
       <c r="F8" s="3" t="s">
-        <v>88</v>
+        <v>93</v>
       </c>
       <c r="G8" s="7"/>
       <c r="H8" s="8"/>
@@ -1159,7 +1227,7 @@
         <v>70</v>
       </c>
       <c r="F9" s="3" t="s">
-        <v>88</v>
+        <v>93</v>
       </c>
       <c r="G9" s="7"/>
       <c r="H9" s="8"/>
@@ -1177,7 +1245,7 @@
         <v>70</v>
       </c>
       <c r="F10" s="3" t="s">
-        <v>88</v>
+        <v>105</v>
       </c>
       <c r="G10" s="7"/>
       <c r="H10" s="8"/>
@@ -1363,7 +1431,7 @@
         <v>70</v>
       </c>
       <c r="F20" s="3" t="s">
-        <v>88</v>
+        <v>105</v>
       </c>
       <c r="G20" s="13"/>
       <c r="H20" s="3"/>
@@ -1482,7 +1550,7 @@
       <c r="A27" s="29"/>
       <c r="B27" s="26"/>
       <c r="C27" s="14" t="s">
-        <v>98</v>
+        <v>96</v>
       </c>
       <c r="D27" s="1"/>
       <c r="E27" s="3" t="s">
@@ -1583,7 +1651,7 @@
         <v>70</v>
       </c>
       <c r="F32" s="1" t="s">
-        <v>88</v>
+        <v>105</v>
       </c>
       <c r="G32" s="20"/>
       <c r="H32" s="1"/>
@@ -1594,14 +1662,14 @@
       <c r="A33" s="29"/>
       <c r="B33" s="26"/>
       <c r="C33" s="14" t="s">
-        <v>106</v>
+        <v>104</v>
       </c>
       <c r="D33" s="1"/>
       <c r="E33" s="3" t="s">
         <v>70</v>
       </c>
       <c r="F33" s="1" t="s">
-        <v>88</v>
+        <v>105</v>
       </c>
       <c r="G33" s="20"/>
       <c r="H33" s="1"/>
@@ -1612,14 +1680,14 @@
       <c r="A34" s="29"/>
       <c r="B34" s="26"/>
       <c r="C34" s="14" t="s">
-        <v>105</v>
+        <v>103</v>
       </c>
       <c r="D34" s="1"/>
       <c r="E34" s="3" t="s">
         <v>70</v>
       </c>
       <c r="F34" s="1" t="s">
-        <v>88</v>
+        <v>93</v>
       </c>
       <c r="G34" s="20"/>
       <c r="H34" s="1"/>
@@ -1637,7 +1705,7 @@
         <v>70</v>
       </c>
       <c r="F35" s="1" t="s">
-        <v>88</v>
+        <v>93</v>
       </c>
       <c r="G35" s="20"/>
       <c r="H35" s="1"/>
@@ -1787,7 +1855,7 @@
         <v>70</v>
       </c>
       <c r="F43" s="1" t="s">
-        <v>95</v>
+        <v>93</v>
       </c>
       <c r="G43" s="20"/>
       <c r="H43" s="1"/>
@@ -1805,7 +1873,7 @@
         <v>70</v>
       </c>
       <c r="F44" s="1" t="s">
-        <v>95</v>
+        <v>93</v>
       </c>
       <c r="G44" s="20"/>
       <c r="H44" s="1"/>
@@ -1823,7 +1891,7 @@
         <v>73</v>
       </c>
       <c r="F45" s="1" t="s">
-        <v>96</v>
+        <v>106</v>
       </c>
       <c r="G45" s="20"/>
       <c r="H45" s="1"/>
@@ -1834,14 +1902,14 @@
       <c r="A46" s="29"/>
       <c r="B46" s="27"/>
       <c r="C46" s="17" t="s">
-        <v>104</v>
+        <v>102</v>
       </c>
       <c r="D46" s="1"/>
       <c r="E46" s="3" t="s">
         <v>72</v>
       </c>
       <c r="F46" s="1" t="s">
-        <v>97</v>
+        <v>95</v>
       </c>
       <c r="G46" s="20"/>
       <c r="H46" s="1"/>
@@ -1930,7 +1998,7 @@
         <v>83</v>
       </c>
       <c r="C51" s="19" t="s">
-        <v>103</v>
+        <v>101</v>
       </c>
       <c r="D51" s="1"/>
       <c r="E51" s="3" t="s">
@@ -1987,10 +2055,10 @@
     <row r="54" spans="1:10">
       <c r="A54" s="28"/>
       <c r="B54" s="18" t="s">
-        <v>99</v>
+        <v>97</v>
       </c>
       <c r="C54" s="19" t="s">
-        <v>100</v>
+        <v>98</v>
       </c>
       <c r="D54" s="1"/>
       <c r="E54" s="3" t="s">
@@ -2007,10 +2075,10 @@
     <row r="55" spans="1:10">
       <c r="A55" s="28"/>
       <c r="B55" s="18" t="s">
-        <v>101</v>
+        <v>99</v>
       </c>
       <c r="C55" s="19" t="s">
-        <v>102</v>
+        <v>100</v>
       </c>
       <c r="D55" s="1"/>
       <c r="E55" s="3" t="s">
@@ -2039,7 +2107,7 @@
         <v>72</v>
       </c>
       <c r="F56" s="1" t="s">
-        <v>97</v>
+        <v>95</v>
       </c>
       <c r="G56" s="20"/>
       <c r="H56" s="1"/>

--- a/internal_doc/05.测试设计/特性守护矩阵.xlsx
+++ b/internal_doc/05.测试设计/特性守护矩阵.xlsx
@@ -12,14 +12,14 @@
     <sheet name="Sheet3" sheetId="3" r:id="rId3"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet1!$B$1:$H$59</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet1!$B$1:$H$75</definedName>
   </definedNames>
   <calcPr calcId="124519"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="205" uniqueCount="107">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="256" uniqueCount="131">
   <si>
     <t>优先级</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -177,10 +177,6 @@
     <phoneticPr fontId="8" type="noConversion"/>
   </si>
   <si>
-    <t>c/c++</t>
-    <phoneticPr fontId="8" type="noConversion"/>
-  </si>
-  <si>
     <t>c#</t>
     <phoneticPr fontId="8" type="noConversion"/>
   </si>
@@ -265,10 +261,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>SQL</t>
-    <phoneticPr fontId="8" type="noConversion"/>
-  </si>
-  <si>
     <t>kettle</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -297,10 +289,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>黄晓妮</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>吴艳</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -317,63 +305,222 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
+    <t>update，upsert：更新符</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>query: 匹配符，选择符，排序，hint，flag，skip,limit、查询优化器</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>快照监控</t>
+    <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
+    <t>SCM</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>读、写、删文件</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>文件管理</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>集群管理</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>节点启停、部署、配置</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>刘晓璇</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>范瑜</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>陈思琴</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>读写分离</t>
+    <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
+    <t>ScmQueryBuilder匹配符查询</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>javascript：shell，-s, -f</t>
+    <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
+    <t>web页面操作</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>安装、部署</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>陈思琴</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>刘晓璇</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>卢伟康</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>卢伟康</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>陈思琴</t>
+  </si>
+  <si>
+    <t>王可心</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>全文索引</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>刘晓璇</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
     <t>赵育</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>update，upsert：更新符</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>query: 匹配符，选择符，排序，hint，flag，skip,limit、查询优化器</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>快照监控</t>
-    <phoneticPr fontId="8" type="noConversion"/>
-  </si>
-  <si>
-    <t>黄晓妮</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>SCM</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>梁雪望</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>基本操作</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>读、写、删文件</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>多中心</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>文件管理</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>集群管理</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>文件迁移、清理、缓存</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>节点启停、部署、配置</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>劳景堂</t>
+    <t>赵小妮</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>吴艳</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>c++</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>c</t>
+    <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
+    <t>王文净</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>任务管理</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>asynctask（单个迁移、单个缓存）</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>task（迁移任务、清理任务）</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>scheduletask（异步调度任务）</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>鉴权管理</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>内置SQL</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>自定义元数据</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>跨中心读文件</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>更新文件版本</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>断点文件续传</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>数据源管理</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>multids（ceph/hbase/hdfs）</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>驱动</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>rest</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>文件夹管理</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>目录创建、删除、移动</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>批次管理</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>创建/删除批次、批次挂载/去挂载文件、批次增加自定义元数据</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>登入登出、密码管理、权限认证</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>微服务权限管理</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>系统管理</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>session、site、workspace管理</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>吴艳</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>mysql连接器</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>sequoiaFS</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
@@ -381,71 +528,19 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>范瑜</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>林苏强</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>林苏强</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>陈思琴</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>梁雪望</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>孟春生</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>读写分离</t>
-    <phoneticPr fontId="8" type="noConversion"/>
-  </si>
-  <si>
-    <t>安全性</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>登入登出、密码管理</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>查询条件</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>ScmQueryBuilder匹配符查询</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>跨中心缓存文件</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>javascript：shell，-s, -f</t>
-    <phoneticPr fontId="8" type="noConversion"/>
-  </si>
-  <si>
-    <t>web页面操作</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>安装、部署</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>陈思琴</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>刘晓璇</t>
+    <t>自增字段</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>赵育</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>赵小妮</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>赵小妮</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -578,7 +673,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="3">
     <border>
       <left/>
       <right/>
@@ -601,11 +696,22 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="30">
+  <cellXfs count="35">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="5" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
@@ -654,6 +760,17 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="8" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="2" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="0" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="7" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -1038,7 +1155,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:J59"/>
+  <dimension ref="A1:J76"/>
   <sheetFormatPr defaultRowHeight="13.5"/>
   <cols>
     <col min="3" max="3" width="55.25" customWidth="1"/>
@@ -1083,8 +1200,8 @@
       </c>
     </row>
     <row r="2" spans="1:10">
-      <c r="A2" s="29" t="s">
-        <v>65</v>
+      <c r="A2" s="34" t="s">
+        <v>63</v>
       </c>
       <c r="B2" s="16" t="s">
         <v>10</v>
@@ -1094,10 +1211,10 @@
       </c>
       <c r="D2" s="3"/>
       <c r="E2" s="3" t="s">
-        <v>68</v>
+        <v>66</v>
       </c>
       <c r="F2" s="3" t="s">
-        <v>95</v>
+        <v>90</v>
       </c>
       <c r="G2" s="3"/>
       <c r="H2" s="3"/>
@@ -1105,19 +1222,19 @@
       <c r="J2" s="3"/>
     </row>
     <row r="3" spans="1:10">
-      <c r="A3" s="29"/>
+      <c r="A3" s="34"/>
       <c r="B3" s="21" t="s">
         <v>12</v>
       </c>
       <c r="C3" s="14" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="D3" s="9"/>
       <c r="E3" s="3" t="s">
-        <v>70</v>
+        <v>67</v>
       </c>
       <c r="F3" s="3" t="s">
-        <v>93</v>
+        <v>81</v>
       </c>
       <c r="G3" s="6"/>
       <c r="H3" s="3"/>
@@ -1125,19 +1242,19 @@
       <c r="J3" s="3"/>
     </row>
     <row r="4" spans="1:10" ht="27" customHeight="1">
-      <c r="A4" s="29"/>
-      <c r="B4" s="27" t="s">
-        <v>71</v>
+      <c r="A4" s="34"/>
+      <c r="B4" s="32" t="s">
+        <v>68</v>
       </c>
       <c r="C4" s="17" t="s">
         <v>13</v>
       </c>
       <c r="D4" s="3"/>
       <c r="E4" s="3" t="s">
-        <v>70</v>
+        <v>67</v>
       </c>
       <c r="F4" s="3" t="s">
-        <v>94</v>
+        <v>92</v>
       </c>
       <c r="G4" s="6"/>
       <c r="H4" s="3"/>
@@ -1145,17 +1262,17 @@
       <c r="J4" s="3"/>
     </row>
     <row r="5" spans="1:10">
-      <c r="A5" s="29"/>
-      <c r="B5" s="27"/>
+      <c r="A5" s="34"/>
+      <c r="B5" s="32"/>
       <c r="C5" s="17" t="s">
         <v>14</v>
       </c>
       <c r="D5" s="3"/>
       <c r="E5" s="3" t="s">
-        <v>70</v>
+        <v>67</v>
       </c>
       <c r="F5" s="3" t="s">
-        <v>94</v>
+        <v>92</v>
       </c>
       <c r="G5" s="3"/>
       <c r="H5" s="3"/>
@@ -1163,17 +1280,17 @@
       <c r="J5" s="3"/>
     </row>
     <row r="6" spans="1:10">
-      <c r="A6" s="29"/>
-      <c r="B6" s="27"/>
+      <c r="A6" s="34"/>
+      <c r="B6" s="32"/>
       <c r="C6" s="17" t="s">
         <v>15</v>
       </c>
       <c r="D6" s="10"/>
       <c r="E6" s="3" t="s">
-        <v>70</v>
+        <v>67</v>
       </c>
       <c r="F6" s="3" t="s">
-        <v>94</v>
+        <v>92</v>
       </c>
       <c r="G6" s="6"/>
       <c r="H6" s="3"/>
@@ -1181,17 +1298,17 @@
       <c r="J6" s="3"/>
     </row>
     <row r="7" spans="1:10">
-      <c r="A7" s="29"/>
-      <c r="B7" s="27"/>
+      <c r="A7" s="34"/>
+      <c r="B7" s="32"/>
       <c r="C7" s="17" t="s">
         <v>16</v>
       </c>
       <c r="D7" s="11"/>
       <c r="E7" s="3" t="s">
-        <v>78</v>
+        <v>81</v>
       </c>
       <c r="F7" s="3" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="G7" s="6"/>
       <c r="H7" s="3"/>
@@ -1199,17 +1316,17 @@
       <c r="J7" s="3"/>
     </row>
     <row r="8" spans="1:10">
-      <c r="A8" s="29"/>
-      <c r="B8" s="27"/>
+      <c r="A8" s="34"/>
+      <c r="B8" s="32"/>
       <c r="C8" s="17" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="D8" s="3"/>
       <c r="E8" s="3" t="s">
-        <v>70</v>
+        <v>67</v>
       </c>
       <c r="F8" s="3" t="s">
-        <v>93</v>
+        <v>81</v>
       </c>
       <c r="G8" s="7"/>
       <c r="H8" s="8"/>
@@ -1217,17 +1334,17 @@
       <c r="J8" s="3"/>
     </row>
     <row r="9" spans="1:10">
-      <c r="A9" s="29"/>
-      <c r="B9" s="27"/>
+      <c r="A9" s="34"/>
+      <c r="B9" s="32"/>
       <c r="C9" s="17" t="s">
         <v>17</v>
       </c>
       <c r="D9" s="3"/>
       <c r="E9" s="3" t="s">
-        <v>70</v>
+        <v>67</v>
       </c>
       <c r="F9" s="3" t="s">
-        <v>93</v>
+        <v>81</v>
       </c>
       <c r="G9" s="7"/>
       <c r="H9" s="8"/>
@@ -1235,17 +1352,17 @@
       <c r="J9" s="3"/>
     </row>
     <row r="10" spans="1:10">
-      <c r="A10" s="29"/>
-      <c r="B10" s="27"/>
+      <c r="A10" s="34"/>
+      <c r="B10" s="32"/>
       <c r="C10" s="17" t="s">
         <v>18</v>
       </c>
       <c r="D10" s="3"/>
       <c r="E10" s="3" t="s">
-        <v>70</v>
+        <v>67</v>
       </c>
       <c r="F10" s="3" t="s">
-        <v>105</v>
+        <v>87</v>
       </c>
       <c r="G10" s="7"/>
       <c r="H10" s="8"/>
@@ -1253,8 +1370,8 @@
       <c r="J10" s="3"/>
     </row>
     <row r="11" spans="1:10">
-      <c r="A11" s="29"/>
-      <c r="B11" s="26" t="s">
+      <c r="A11" s="34"/>
+      <c r="B11" s="31" t="s">
         <v>19</v>
       </c>
       <c r="C11" s="14" t="s">
@@ -1262,10 +1379,10 @@
       </c>
       <c r="D11" s="3"/>
       <c r="E11" s="3" t="s">
-        <v>72</v>
+        <v>92</v>
       </c>
       <c r="F11" s="3" t="s">
-        <v>80</v>
+        <v>66</v>
       </c>
       <c r="G11" s="12"/>
       <c r="H11" s="3"/>
@@ -1273,17 +1390,17 @@
       <c r="J11" s="3"/>
     </row>
     <row r="12" spans="1:10">
-      <c r="A12" s="29"/>
-      <c r="B12" s="26"/>
+      <c r="A12" s="34"/>
+      <c r="B12" s="31"/>
       <c r="C12" s="14" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="D12" s="3"/>
       <c r="E12" s="3" t="s">
-        <v>72</v>
+        <v>92</v>
       </c>
       <c r="F12" s="3" t="s">
-        <v>80</v>
+        <v>66</v>
       </c>
       <c r="G12" s="12"/>
       <c r="H12" s="3"/>
@@ -1291,17 +1408,17 @@
       <c r="J12" s="3"/>
     </row>
     <row r="13" spans="1:10">
-      <c r="A13" s="29"/>
-      <c r="B13" s="26"/>
+      <c r="A13" s="34"/>
+      <c r="B13" s="31"/>
       <c r="C13" s="14" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="D13" s="3"/>
       <c r="E13" s="3" t="s">
-        <v>72</v>
+        <v>66</v>
       </c>
       <c r="F13" s="3" t="s">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="G13" s="12"/>
       <c r="H13" s="3"/>
@@ -1309,17 +1426,17 @@
       <c r="J13" s="3"/>
     </row>
     <row r="14" spans="1:10">
-      <c r="A14" s="29"/>
-      <c r="B14" s="26"/>
+      <c r="A14" s="34"/>
+      <c r="B14" s="31"/>
       <c r="C14" s="14" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="D14" s="3"/>
       <c r="E14" s="3" t="s">
-        <v>72</v>
+        <v>69</v>
       </c>
       <c r="F14" s="3" t="s">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="G14" s="12"/>
       <c r="H14" s="3"/>
@@ -1327,8 +1444,8 @@
       <c r="J14" s="3"/>
     </row>
     <row r="15" spans="1:10">
-      <c r="A15" s="29"/>
-      <c r="B15" s="27" t="s">
+      <c r="A15" s="34"/>
+      <c r="B15" s="32" t="s">
         <v>21</v>
       </c>
       <c r="C15" s="17" t="s">
@@ -1336,10 +1453,10 @@
       </c>
       <c r="D15" s="3"/>
       <c r="E15" s="3" t="s">
-        <v>73</v>
+        <v>70</v>
       </c>
       <c r="F15" s="3" t="s">
-        <v>89</v>
+        <v>79</v>
       </c>
       <c r="G15" s="7"/>
       <c r="H15" s="8"/>
@@ -1347,17 +1464,17 @@
       <c r="J15" s="3"/>
     </row>
     <row r="16" spans="1:10">
-      <c r="A16" s="29"/>
-      <c r="B16" s="27"/>
+      <c r="A16" s="34"/>
+      <c r="B16" s="32"/>
       <c r="C16" s="17" t="s">
-        <v>64</v>
+        <v>62</v>
       </c>
       <c r="D16" s="3"/>
       <c r="E16" s="3" t="s">
-        <v>73</v>
+        <v>70</v>
       </c>
       <c r="F16" s="3" t="s">
-        <v>89</v>
+        <v>79</v>
       </c>
       <c r="G16" s="12"/>
       <c r="H16" s="3"/>
@@ -1365,17 +1482,17 @@
       <c r="J16" s="3"/>
     </row>
     <row r="17" spans="1:10">
-      <c r="A17" s="29"/>
-      <c r="B17" s="27"/>
+      <c r="A17" s="34"/>
+      <c r="B17" s="32"/>
       <c r="C17" s="17" t="s">
         <v>23</v>
       </c>
       <c r="D17" s="3"/>
       <c r="E17" s="3" t="s">
-        <v>73</v>
+        <v>70</v>
       </c>
       <c r="F17" s="3" t="s">
-        <v>89</v>
+        <v>79</v>
       </c>
       <c r="G17" s="13"/>
       <c r="H17" s="3"/>
@@ -1383,17 +1500,17 @@
       <c r="J17" s="3"/>
     </row>
     <row r="18" spans="1:10">
-      <c r="A18" s="29"/>
-      <c r="B18" s="27"/>
+      <c r="A18" s="34"/>
+      <c r="B18" s="32"/>
       <c r="C18" s="17" t="s">
         <v>24</v>
       </c>
       <c r="D18" s="2"/>
       <c r="E18" s="3" t="s">
-        <v>73</v>
+        <v>70</v>
       </c>
       <c r="F18" s="3" t="s">
-        <v>89</v>
+        <v>79</v>
       </c>
       <c r="G18" s="6"/>
       <c r="H18" s="3"/>
@@ -1401,17 +1518,17 @@
       <c r="J18" s="3"/>
     </row>
     <row r="19" spans="1:10">
-      <c r="A19" s="29"/>
-      <c r="B19" s="27"/>
+      <c r="A19" s="34"/>
+      <c r="B19" s="32"/>
       <c r="C19" s="17" t="s">
         <v>25</v>
       </c>
       <c r="D19" s="2"/>
       <c r="E19" s="3" t="s">
-        <v>73</v>
+        <v>70</v>
       </c>
       <c r="F19" s="3" t="s">
-        <v>89</v>
+        <v>79</v>
       </c>
       <c r="G19" s="7"/>
       <c r="H19" s="8"/>
@@ -1419,19 +1536,19 @@
       <c r="J19" s="3"/>
     </row>
     <row r="20" spans="1:10" ht="27">
-      <c r="A20" s="29"/>
-      <c r="B20" s="26" t="s">
+      <c r="A20" s="34"/>
+      <c r="B20" s="31" t="s">
         <v>26</v>
       </c>
       <c r="C20" s="14" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="D20" s="2"/>
       <c r="E20" s="3" t="s">
-        <v>70</v>
+        <v>67</v>
       </c>
       <c r="F20" s="3" t="s">
-        <v>105</v>
+        <v>87</v>
       </c>
       <c r="G20" s="13"/>
       <c r="H20" s="3"/>
@@ -1439,17 +1556,17 @@
       <c r="J20" s="3"/>
     </row>
     <row r="21" spans="1:10" ht="27">
-      <c r="A21" s="29"/>
-      <c r="B21" s="26"/>
+      <c r="A21" s="34"/>
+      <c r="B21" s="31"/>
       <c r="C21" s="14" t="s">
-        <v>76</v>
+        <v>72</v>
       </c>
       <c r="D21" s="2"/>
       <c r="E21" s="3" t="s">
-        <v>74</v>
+        <v>70</v>
       </c>
       <c r="F21" s="3" t="s">
-        <v>93</v>
+        <v>79</v>
       </c>
       <c r="G21" s="13"/>
       <c r="H21" s="3"/>
@@ -1457,17 +1574,17 @@
       <c r="J21" s="3"/>
     </row>
     <row r="22" spans="1:10">
-      <c r="A22" s="29"/>
-      <c r="B22" s="26"/>
+      <c r="A22" s="34"/>
+      <c r="B22" s="31"/>
       <c r="C22" s="14" t="s">
-        <v>75</v>
+        <v>93</v>
       </c>
       <c r="D22" s="2"/>
       <c r="E22" s="3" t="s">
-        <v>74</v>
+        <v>95</v>
       </c>
       <c r="F22" s="3" t="s">
-        <v>89</v>
+        <v>126</v>
       </c>
       <c r="G22" s="13"/>
       <c r="H22" s="3"/>
@@ -1475,71 +1592,71 @@
       <c r="J22" s="3"/>
     </row>
     <row r="23" spans="1:10">
-      <c r="A23" s="29"/>
-      <c r="B23" s="26"/>
+      <c r="A23" s="34"/>
+      <c r="B23" s="31"/>
       <c r="C23" s="14" t="s">
-        <v>27</v>
-      </c>
-      <c r="D23" s="3"/>
+        <v>71</v>
+      </c>
+      <c r="D23" s="2"/>
       <c r="E23" s="3" t="s">
-        <v>69</v>
+        <v>130</v>
       </c>
       <c r="F23" s="3" t="s">
-        <v>92</v>
-      </c>
-      <c r="G23" s="3"/>
+        <v>95</v>
+      </c>
+      <c r="G23" s="13"/>
       <c r="H23" s="3"/>
       <c r="I23" s="3"/>
       <c r="J23" s="3"/>
     </row>
     <row r="24" spans="1:10">
-      <c r="A24" s="29"/>
-      <c r="B24" s="26"/>
+      <c r="A24" s="34"/>
+      <c r="B24" s="31"/>
       <c r="C24" s="14" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="D24" s="3"/>
       <c r="E24" s="3" t="s">
-        <v>69</v>
+        <v>89</v>
       </c>
       <c r="F24" s="3" t="s">
-        <v>92</v>
-      </c>
-      <c r="G24" s="7"/>
-      <c r="H24" s="8"/>
-      <c r="I24" s="8"/>
+        <v>67</v>
+      </c>
+      <c r="G24" s="3"/>
+      <c r="H24" s="3"/>
+      <c r="I24" s="3"/>
       <c r="J24" s="3"/>
     </row>
     <row r="25" spans="1:10">
-      <c r="A25" s="29"/>
-      <c r="B25" s="26"/>
+      <c r="A25" s="34"/>
+      <c r="B25" s="31"/>
       <c r="C25" s="14" t="s">
+        <v>28</v>
+      </c>
+      <c r="D25" s="3"/>
+      <c r="E25" s="3" t="s">
+        <v>89</v>
+      </c>
+      <c r="F25" s="3" t="s">
+        <v>67</v>
+      </c>
+      <c r="G25" s="7"/>
+      <c r="H25" s="8"/>
+      <c r="I25" s="8"/>
+      <c r="J25" s="3"/>
+    </row>
+    <row r="26" spans="1:10">
+      <c r="A26" s="34"/>
+      <c r="B26" s="31"/>
+      <c r="C26" s="14" t="s">
         <v>29</v>
-      </c>
-      <c r="D25" s="1"/>
-      <c r="E25" s="3" t="s">
-        <v>74</v>
-      </c>
-      <c r="F25" s="3" t="s">
-        <v>89</v>
-      </c>
-      <c r="G25" s="20"/>
-      <c r="H25" s="1"/>
-      <c r="I25" s="1"/>
-      <c r="J25" s="1"/>
-    </row>
-    <row r="26" spans="1:10">
-      <c r="A26" s="29"/>
-      <c r="B26" s="26"/>
-      <c r="C26" s="14" t="s">
-        <v>30</v>
       </c>
       <c r="D26" s="1"/>
       <c r="E26" s="3" t="s">
-        <v>69</v>
+        <v>96</v>
       </c>
       <c r="F26" s="3" t="s">
-        <v>92</v>
+        <v>70</v>
       </c>
       <c r="G26" s="20"/>
       <c r="H26" s="1"/>
@@ -1547,37 +1664,35 @@
       <c r="J26" s="1"/>
     </row>
     <row r="27" spans="1:10">
-      <c r="A27" s="29"/>
-      <c r="B27" s="26"/>
+      <c r="A27" s="34"/>
+      <c r="B27" s="31"/>
       <c r="C27" s="14" t="s">
-        <v>96</v>
+        <v>30</v>
       </c>
       <c r="D27" s="1"/>
       <c r="E27" s="3" t="s">
-        <v>69</v>
+        <v>81</v>
       </c>
       <c r="F27" s="3" t="s">
-        <v>92</v>
+        <v>70</v>
       </c>
       <c r="G27" s="20"/>
       <c r="H27" s="1"/>
       <c r="I27" s="1"/>
       <c r="J27" s="1"/>
     </row>
-    <row r="28" spans="1:10" ht="27" customHeight="1">
-      <c r="A28" s="29"/>
-      <c r="B28" s="25" t="s">
-        <v>48</v>
-      </c>
-      <c r="C28" s="15" t="s">
-        <v>52</v>
+    <row r="28" spans="1:10">
+      <c r="A28" s="34"/>
+      <c r="B28" s="31"/>
+      <c r="C28" s="14" t="s">
+        <v>106</v>
       </c>
       <c r="D28" s="1"/>
       <c r="E28" s="3" t="s">
-        <v>69</v>
-      </c>
-      <c r="F28" s="1" t="s">
-        <v>90</v>
+        <v>81</v>
+      </c>
+      <c r="F28" s="3" t="s">
+        <v>70</v>
       </c>
       <c r="G28" s="20"/>
       <c r="H28" s="1"/>
@@ -1585,35 +1700,37 @@
       <c r="J28" s="1"/>
     </row>
     <row r="29" spans="1:10">
-      <c r="A29" s="29"/>
-      <c r="B29" s="25"/>
-      <c r="C29" s="15" t="s">
-        <v>49</v>
+      <c r="A29" s="34"/>
+      <c r="B29" s="31"/>
+      <c r="C29" s="14" t="s">
+        <v>82</v>
       </c>
       <c r="D29" s="1"/>
       <c r="E29" s="3" t="s">
-        <v>69</v>
-      </c>
-      <c r="F29" s="1" t="s">
-        <v>90</v>
+        <v>92</v>
+      </c>
+      <c r="F29" s="3" t="s">
+        <v>67</v>
       </c>
       <c r="G29" s="20"/>
       <c r="H29" s="1"/>
       <c r="I29" s="1"/>
       <c r="J29" s="1"/>
     </row>
-    <row r="30" spans="1:10">
-      <c r="A30" s="29"/>
-      <c r="B30" s="25"/>
+    <row r="30" spans="1:10" ht="27" customHeight="1">
+      <c r="A30" s="34"/>
+      <c r="B30" s="30" t="s">
+        <v>47</v>
+      </c>
       <c r="C30" s="15" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="D30" s="1"/>
       <c r="E30" s="3" t="s">
-        <v>69</v>
+        <v>89</v>
       </c>
       <c r="F30" s="1" t="s">
-        <v>90</v>
+        <v>67</v>
       </c>
       <c r="G30" s="20"/>
       <c r="H30" s="1"/>
@@ -1621,17 +1738,17 @@
       <c r="J30" s="1"/>
     </row>
     <row r="31" spans="1:10">
-      <c r="A31" s="29"/>
-      <c r="B31" s="25"/>
+      <c r="A31" s="34"/>
+      <c r="B31" s="30"/>
       <c r="C31" s="15" t="s">
-        <v>60</v>
+        <v>48</v>
       </c>
       <c r="D31" s="1"/>
-      <c r="E31" s="1" t="s">
-        <v>73</v>
-      </c>
-      <c r="F31" s="3" t="s">
-        <v>93</v>
+      <c r="E31" s="3" t="s">
+        <v>89</v>
+      </c>
+      <c r="F31" s="1" t="s">
+        <v>67</v>
       </c>
       <c r="G31" s="20"/>
       <c r="H31" s="1"/>
@@ -1639,19 +1756,17 @@
       <c r="J31" s="1"/>
     </row>
     <row r="32" spans="1:10">
-      <c r="A32" s="29"/>
-      <c r="B32" s="26" t="s">
-        <v>51</v>
-      </c>
-      <c r="C32" s="14" t="s">
-        <v>58</v>
+      <c r="A32" s="34"/>
+      <c r="B32" s="30"/>
+      <c r="C32" s="15" t="s">
+        <v>49</v>
       </c>
       <c r="D32" s="1"/>
       <c r="E32" s="3" t="s">
-        <v>70</v>
+        <v>89</v>
       </c>
       <c r="F32" s="1" t="s">
-        <v>105</v>
+        <v>67</v>
       </c>
       <c r="G32" s="20"/>
       <c r="H32" s="1"/>
@@ -1659,17 +1774,17 @@
       <c r="J32" s="1"/>
     </row>
     <row r="33" spans="1:10">
-      <c r="A33" s="29"/>
-      <c r="B33" s="26"/>
-      <c r="C33" s="14" t="s">
-        <v>104</v>
+      <c r="A33" s="34"/>
+      <c r="B33" s="30"/>
+      <c r="C33" s="15" t="s">
+        <v>59</v>
       </c>
       <c r="D33" s="1"/>
       <c r="E33" s="3" t="s">
+        <v>94</v>
+      </c>
+      <c r="F33" s="1" t="s">
         <v>70</v>
-      </c>
-      <c r="F33" s="1" t="s">
-        <v>105</v>
       </c>
       <c r="G33" s="20"/>
       <c r="H33" s="1"/>
@@ -1677,17 +1792,17 @@
       <c r="J33" s="1"/>
     </row>
     <row r="34" spans="1:10">
-      <c r="A34" s="29"/>
-      <c r="B34" s="26"/>
-      <c r="C34" s="14" t="s">
-        <v>103</v>
+      <c r="A34" s="34"/>
+      <c r="B34" s="23"/>
+      <c r="C34" s="15" t="s">
+        <v>127</v>
       </c>
       <c r="D34" s="1"/>
       <c r="E34" s="3" t="s">
-        <v>70</v>
+        <v>94</v>
       </c>
       <c r="F34" s="1" t="s">
-        <v>93</v>
+        <v>128</v>
       </c>
       <c r="G34" s="20"/>
       <c r="H34" s="1"/>
@@ -1695,17 +1810,19 @@
       <c r="J34" s="1"/>
     </row>
     <row r="35" spans="1:10">
-      <c r="A35" s="29"/>
-      <c r="B35" s="26"/>
+      <c r="A35" s="34"/>
+      <c r="B35" s="31" t="s">
+        <v>50</v>
+      </c>
       <c r="C35" s="14" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="D35" s="1"/>
       <c r="E35" s="3" t="s">
-        <v>70</v>
+        <v>92</v>
       </c>
       <c r="F35" s="1" t="s">
-        <v>93</v>
+        <v>81</v>
       </c>
       <c r="G35" s="20"/>
       <c r="H35" s="1"/>
@@ -1713,19 +1830,17 @@
       <c r="J35" s="1"/>
     </row>
     <row r="36" spans="1:10">
-      <c r="A36" s="29"/>
-      <c r="B36" s="27" t="s">
-        <v>31</v>
-      </c>
-      <c r="C36" s="17" t="s">
-        <v>32</v>
+      <c r="A36" s="34"/>
+      <c r="B36" s="31"/>
+      <c r="C36" s="14" t="s">
+        <v>86</v>
       </c>
       <c r="D36" s="1"/>
       <c r="E36" s="3" t="s">
-        <v>69</v>
+        <v>92</v>
       </c>
       <c r="F36" s="1" t="s">
-        <v>91</v>
+        <v>87</v>
       </c>
       <c r="G36" s="20"/>
       <c r="H36" s="1"/>
@@ -1733,17 +1848,17 @@
       <c r="J36" s="1"/>
     </row>
     <row r="37" spans="1:10">
-      <c r="A37" s="29"/>
-      <c r="B37" s="27"/>
-      <c r="C37" s="17" t="s">
-        <v>33</v>
+      <c r="A37" s="34"/>
+      <c r="B37" s="31"/>
+      <c r="C37" s="14" t="s">
+        <v>85</v>
       </c>
       <c r="D37" s="1"/>
       <c r="E37" s="3" t="s">
-        <v>69</v>
+        <v>92</v>
       </c>
       <c r="F37" s="1" t="s">
-        <v>91</v>
+        <v>89</v>
       </c>
       <c r="G37" s="20"/>
       <c r="H37" s="1"/>
@@ -1751,17 +1866,17 @@
       <c r="J37" s="1"/>
     </row>
     <row r="38" spans="1:10">
-      <c r="A38" s="29"/>
-      <c r="B38" s="27"/>
-      <c r="C38" s="17" t="s">
-        <v>34</v>
+      <c r="A38" s="34"/>
+      <c r="B38" s="31"/>
+      <c r="C38" s="14" t="s">
+        <v>58</v>
       </c>
       <c r="D38" s="1"/>
       <c r="E38" s="3" t="s">
-        <v>69</v>
+        <v>92</v>
       </c>
       <c r="F38" s="1" t="s">
-        <v>91</v>
+        <v>89</v>
       </c>
       <c r="G38" s="20"/>
       <c r="H38" s="1"/>
@@ -1769,19 +1884,19 @@
       <c r="J38" s="1"/>
     </row>
     <row r="39" spans="1:10">
-      <c r="A39" s="29"/>
-      <c r="B39" s="26" t="s">
-        <v>35</v>
-      </c>
-      <c r="C39" s="14" t="s">
-        <v>77</v>
+      <c r="A39" s="34"/>
+      <c r="B39" s="32" t="s">
+        <v>31</v>
+      </c>
+      <c r="C39" s="17" t="s">
+        <v>32</v>
       </c>
       <c r="D39" s="1"/>
       <c r="E39" s="3" t="s">
-        <v>69</v>
+        <v>81</v>
       </c>
       <c r="F39" s="1" t="s">
-        <v>90</v>
+        <v>67</v>
       </c>
       <c r="G39" s="20"/>
       <c r="H39" s="1"/>
@@ -1789,17 +1904,17 @@
       <c r="J39" s="1"/>
     </row>
     <row r="40" spans="1:10">
-      <c r="A40" s="29"/>
-      <c r="B40" s="26"/>
-      <c r="C40" s="14" t="s">
-        <v>36</v>
+      <c r="A40" s="34"/>
+      <c r="B40" s="32"/>
+      <c r="C40" s="17" t="s">
+        <v>33</v>
       </c>
       <c r="D40" s="1"/>
       <c r="E40" s="3" t="s">
-        <v>69</v>
+        <v>81</v>
       </c>
       <c r="F40" s="1" t="s">
-        <v>90</v>
+        <v>67</v>
       </c>
       <c r="G40" s="20"/>
       <c r="H40" s="1"/>
@@ -1807,17 +1922,17 @@
       <c r="J40" s="1"/>
     </row>
     <row r="41" spans="1:10">
-      <c r="A41" s="29"/>
-      <c r="B41" s="26"/>
-      <c r="C41" s="14" t="s">
-        <v>37</v>
+      <c r="A41" s="34"/>
+      <c r="B41" s="32"/>
+      <c r="C41" s="17" t="s">
+        <v>34</v>
       </c>
       <c r="D41" s="1"/>
       <c r="E41" s="3" t="s">
-        <v>74</v>
+        <v>81</v>
       </c>
       <c r="F41" s="1" t="s">
-        <v>89</v>
+        <v>67</v>
       </c>
       <c r="G41" s="20"/>
       <c r="H41" s="1"/>
@@ -1825,19 +1940,19 @@
       <c r="J41" s="1"/>
     </row>
     <row r="42" spans="1:10">
-      <c r="A42" s="29"/>
-      <c r="B42" s="27" t="s">
-        <v>38</v>
-      </c>
-      <c r="C42" s="17" t="s">
-        <v>39</v>
+      <c r="A42" s="34"/>
+      <c r="B42" s="31" t="s">
+        <v>35</v>
+      </c>
+      <c r="C42" s="14" t="s">
+        <v>73</v>
       </c>
       <c r="D42" s="1"/>
       <c r="E42" s="3" t="s">
-        <v>72</v>
+        <v>96</v>
       </c>
       <c r="F42" s="1" t="s">
-        <v>80</v>
+        <v>70</v>
       </c>
       <c r="G42" s="20"/>
       <c r="H42" s="1"/>
@@ -1845,17 +1960,17 @@
       <c r="J42" s="1"/>
     </row>
     <row r="43" spans="1:10">
-      <c r="A43" s="29"/>
-      <c r="B43" s="27"/>
-      <c r="C43" s="17" t="s">
-        <v>40</v>
+      <c r="A43" s="34"/>
+      <c r="B43" s="31"/>
+      <c r="C43" s="14" t="s">
+        <v>36</v>
       </c>
       <c r="D43" s="1"/>
       <c r="E43" s="3" t="s">
+        <v>96</v>
+      </c>
+      <c r="F43" s="1" t="s">
         <v>70</v>
-      </c>
-      <c r="F43" s="1" t="s">
-        <v>93</v>
       </c>
       <c r="G43" s="20"/>
       <c r="H43" s="1"/>
@@ -1863,17 +1978,17 @@
       <c r="J43" s="1"/>
     </row>
     <row r="44" spans="1:10">
-      <c r="A44" s="29"/>
-      <c r="B44" s="27"/>
-      <c r="C44" s="17" t="s">
-        <v>41</v>
+      <c r="A44" s="34"/>
+      <c r="B44" s="31"/>
+      <c r="C44" s="14" t="s">
+        <v>37</v>
       </c>
       <c r="D44" s="1"/>
       <c r="E44" s="3" t="s">
+        <v>96</v>
+      </c>
+      <c r="F44" s="1" t="s">
         <v>70</v>
-      </c>
-      <c r="F44" s="1" t="s">
-        <v>93</v>
       </c>
       <c r="G44" s="20"/>
       <c r="H44" s="1"/>
@@ -1881,17 +1996,19 @@
       <c r="J44" s="1"/>
     </row>
     <row r="45" spans="1:10">
-      <c r="A45" s="29"/>
-      <c r="B45" s="27"/>
+      <c r="A45" s="34"/>
+      <c r="B45" s="32" t="s">
+        <v>38</v>
+      </c>
       <c r="C45" s="17" t="s">
-        <v>42</v>
+        <v>99</v>
       </c>
       <c r="D45" s="1"/>
-      <c r="E45" s="3" t="s">
-        <v>73</v>
-      </c>
-      <c r="F45" s="1" t="s">
-        <v>106</v>
+      <c r="E45" s="24" t="s">
+        <v>94</v>
+      </c>
+      <c r="F45" s="25" t="s">
+        <v>100</v>
       </c>
       <c r="G45" s="20"/>
       <c r="H45" s="1"/>
@@ -1899,17 +2016,17 @@
       <c r="J45" s="1"/>
     </row>
     <row r="46" spans="1:10">
-      <c r="A46" s="29"/>
-      <c r="B46" s="27"/>
+      <c r="A46" s="34"/>
+      <c r="B46" s="32"/>
       <c r="C46" s="17" t="s">
-        <v>102</v>
+        <v>98</v>
       </c>
       <c r="D46" s="1"/>
       <c r="E46" s="3" t="s">
-        <v>72</v>
-      </c>
-      <c r="F46" s="1" t="s">
-        <v>95</v>
+        <v>69</v>
+      </c>
+      <c r="F46" s="24" t="s">
+        <v>89</v>
       </c>
       <c r="G46" s="20"/>
       <c r="H46" s="1"/>
@@ -1917,17 +2034,17 @@
       <c r="J46" s="1"/>
     </row>
     <row r="47" spans="1:10">
-      <c r="A47" s="29"/>
-      <c r="B47" s="27"/>
+      <c r="A47" s="34"/>
+      <c r="B47" s="32"/>
       <c r="C47" s="17" t="s">
-        <v>43</v>
+        <v>39</v>
       </c>
       <c r="D47" s="1"/>
       <c r="E47" s="3" t="s">
-        <v>69</v>
+        <v>91</v>
       </c>
       <c r="F47" s="1" t="s">
-        <v>91</v>
+        <v>129</v>
       </c>
       <c r="G47" s="20"/>
       <c r="H47" s="1"/>
@@ -1935,17 +2052,17 @@
       <c r="J47" s="1"/>
     </row>
     <row r="48" spans="1:10">
-      <c r="A48" s="29"/>
-      <c r="B48" s="27"/>
+      <c r="A48" s="34"/>
+      <c r="B48" s="32"/>
       <c r="C48" s="17" t="s">
-        <v>61</v>
+        <v>40</v>
       </c>
       <c r="D48" s="1"/>
       <c r="E48" s="3" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
       <c r="F48" s="1" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="G48" s="20"/>
       <c r="H48" s="1"/>
@@ -1953,17 +2070,17 @@
       <c r="J48" s="1"/>
     </row>
     <row r="49" spans="1:10">
-      <c r="A49" s="29"/>
-      <c r="B49" s="27"/>
+      <c r="A49" s="34"/>
+      <c r="B49" s="32"/>
       <c r="C49" s="17" t="s">
-        <v>44</v>
+        <v>41</v>
       </c>
       <c r="D49" s="1"/>
       <c r="E49" s="3" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="F49" s="1" t="s">
-        <v>90</v>
+        <v>88</v>
       </c>
       <c r="G49" s="20"/>
       <c r="H49" s="1"/>
@@ -1971,21 +2088,17 @@
       <c r="J49" s="1"/>
     </row>
     <row r="50" spans="1:10">
-      <c r="A50" s="28" t="s">
-        <v>79</v>
-      </c>
-      <c r="B50" s="18" t="s">
-        <v>81</v>
-      </c>
-      <c r="C50" s="19" t="s">
-        <v>82</v>
+      <c r="A50" s="34"/>
+      <c r="B50" s="32"/>
+      <c r="C50" s="17" t="s">
+        <v>84</v>
       </c>
       <c r="D50" s="1"/>
       <c r="E50" s="3" t="s">
-        <v>69</v>
+        <v>92</v>
       </c>
       <c r="F50" s="1" t="s">
-        <v>90</v>
+        <v>97</v>
       </c>
       <c r="G50" s="20"/>
       <c r="H50" s="1"/>
@@ -1993,19 +2106,17 @@
       <c r="J50" s="1"/>
     </row>
     <row r="51" spans="1:10">
-      <c r="A51" s="28"/>
-      <c r="B51" s="18" t="s">
-        <v>83</v>
-      </c>
-      <c r="C51" s="19" t="s">
-        <v>101</v>
+      <c r="A51" s="34"/>
+      <c r="B51" s="32"/>
+      <c r="C51" s="17" t="s">
+        <v>42</v>
       </c>
       <c r="D51" s="1"/>
       <c r="E51" s="3" t="s">
-        <v>69</v>
+        <v>89</v>
       </c>
       <c r="F51" s="1" t="s">
-        <v>90</v>
+        <v>123</v>
       </c>
       <c r="G51" s="20"/>
       <c r="H51" s="1"/>
@@ -2013,19 +2124,17 @@
       <c r="J51" s="1"/>
     </row>
     <row r="52" spans="1:10">
-      <c r="A52" s="28"/>
-      <c r="B52" s="18" t="s">
-        <v>84</v>
-      </c>
-      <c r="C52" s="19" t="s">
-        <v>86</v>
+      <c r="A52" s="34"/>
+      <c r="B52" s="32"/>
+      <c r="C52" s="17" t="s">
+        <v>43</v>
       </c>
       <c r="D52" s="1"/>
       <c r="E52" s="3" t="s">
-        <v>69</v>
+        <v>80</v>
       </c>
       <c r="F52" s="1" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="G52" s="20"/>
       <c r="H52" s="1"/>
@@ -2033,19 +2142,21 @@
       <c r="J52" s="1"/>
     </row>
     <row r="53" spans="1:10">
-      <c r="A53" s="28"/>
+      <c r="A53" s="33" t="s">
+        <v>74</v>
+      </c>
       <c r="B53" s="18" t="s">
-        <v>85</v>
+        <v>76</v>
       </c>
       <c r="C53" s="19" t="s">
-        <v>87</v>
+        <v>75</v>
       </c>
       <c r="D53" s="1"/>
       <c r="E53" s="3" t="s">
-        <v>69</v>
-      </c>
-      <c r="F53" s="1" t="s">
-        <v>90</v>
+        <v>80</v>
+      </c>
+      <c r="F53" s="3" t="s">
+        <v>67</v>
       </c>
       <c r="G53" s="20"/>
       <c r="H53" s="1"/>
@@ -2053,19 +2164,17 @@
       <c r="J53" s="1"/>
     </row>
     <row r="54" spans="1:10">
-      <c r="A54" s="28"/>
-      <c r="B54" s="18" t="s">
-        <v>97</v>
-      </c>
+      <c r="A54" s="33"/>
+      <c r="B54" s="18"/>
       <c r="C54" s="19" t="s">
-        <v>98</v>
+        <v>108</v>
       </c>
       <c r="D54" s="1"/>
       <c r="E54" s="3" t="s">
-        <v>69</v>
-      </c>
-      <c r="F54" s="1" t="s">
-        <v>90</v>
+        <v>80</v>
+      </c>
+      <c r="F54" s="3" t="s">
+        <v>67</v>
       </c>
       <c r="G54" s="20"/>
       <c r="H54" s="1"/>
@@ -2073,19 +2182,17 @@
       <c r="J54" s="1"/>
     </row>
     <row r="55" spans="1:10">
-      <c r="A55" s="28"/>
-      <c r="B55" s="18" t="s">
-        <v>99</v>
-      </c>
+      <c r="A55" s="33"/>
+      <c r="B55" s="18"/>
       <c r="C55" s="19" t="s">
-        <v>100</v>
+        <v>107</v>
       </c>
       <c r="D55" s="1"/>
       <c r="E55" s="3" t="s">
-        <v>69</v>
-      </c>
-      <c r="F55" s="1" t="s">
-        <v>90</v>
+        <v>80</v>
+      </c>
+      <c r="F55" s="3" t="s">
+        <v>67</v>
       </c>
       <c r="G55" s="20"/>
       <c r="H55" s="1"/>
@@ -2093,21 +2200,17 @@
       <c r="J55" s="1"/>
     </row>
     <row r="56" spans="1:10">
-      <c r="A56" s="23" t="s">
-        <v>66</v>
-      </c>
-      <c r="B56" s="24" t="s">
-        <v>67</v>
-      </c>
-      <c r="C56" s="22" t="s">
-        <v>45</v>
+      <c r="A56" s="33"/>
+      <c r="B56" s="18"/>
+      <c r="C56" s="19" t="s">
+        <v>83</v>
       </c>
       <c r="D56" s="1"/>
       <c r="E56" s="3" t="s">
-        <v>72</v>
+        <v>80</v>
       </c>
       <c r="F56" s="1" t="s">
-        <v>95</v>
+        <v>89</v>
       </c>
       <c r="G56" s="20"/>
       <c r="H56" s="1"/>
@@ -2115,17 +2218,17 @@
       <c r="J56" s="1"/>
     </row>
     <row r="57" spans="1:10">
-      <c r="A57" s="23"/>
-      <c r="B57" s="24"/>
-      <c r="C57" s="22" t="s">
-        <v>46</v>
+      <c r="A57" s="33"/>
+      <c r="B57" s="18"/>
+      <c r="C57" s="19" t="s">
+        <v>109</v>
       </c>
       <c r="D57" s="1"/>
       <c r="E57" s="3" t="s">
-        <v>70</v>
+        <v>67</v>
       </c>
       <c r="F57" s="1" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="G57" s="20"/>
       <c r="H57" s="1"/>
@@ -2133,14 +2236,14 @@
       <c r="J57" s="1"/>
     </row>
     <row r="58" spans="1:10">
-      <c r="A58" s="23"/>
-      <c r="B58" s="24"/>
-      <c r="C58" s="22" t="s">
-        <v>47</v>
+      <c r="A58" s="33"/>
+      <c r="B58" s="18"/>
+      <c r="C58" s="19" t="s">
+        <v>110</v>
       </c>
       <c r="D58" s="1"/>
       <c r="E58" s="3" t="s">
-        <v>73</v>
+        <v>67</v>
       </c>
       <c r="F58" s="1" t="s">
         <v>89</v>
@@ -2150,43 +2253,359 @@
       <c r="I58" s="1"/>
       <c r="J58" s="1"/>
     </row>
-    <row r="59" spans="1:10">
-      <c r="A59" s="23"/>
-      <c r="B59" s="24"/>
-      <c r="C59" s="22" t="s">
-        <v>62</v>
+    <row r="59" spans="1:10" ht="27">
+      <c r="A59" s="33"/>
+      <c r="B59" s="18" t="s">
+        <v>111</v>
+      </c>
+      <c r="C59" s="19" t="s">
+        <v>112</v>
       </c>
       <c r="D59" s="1"/>
       <c r="E59" s="3" t="s">
-        <v>69</v>
+        <v>80</v>
       </c>
       <c r="F59" s="1" t="s">
-        <v>91</v>
+        <v>89</v>
       </c>
       <c r="G59" s="20"/>
       <c r="H59" s="1"/>
       <c r="I59" s="1"/>
       <c r="J59" s="1"/>
     </row>
+    <row r="60" spans="1:10">
+      <c r="A60" s="33"/>
+      <c r="B60" s="18" t="s">
+        <v>113</v>
+      </c>
+      <c r="C60" s="19" t="s">
+        <v>114</v>
+      </c>
+      <c r="D60" s="1"/>
+      <c r="E60" s="3" t="s">
+        <v>80</v>
+      </c>
+      <c r="F60" s="1" t="s">
+        <v>89</v>
+      </c>
+      <c r="G60" s="20"/>
+      <c r="H60" s="1"/>
+      <c r="I60" s="1"/>
+      <c r="J60" s="1"/>
+    </row>
+    <row r="61" spans="1:10" ht="27">
+      <c r="A61" s="33"/>
+      <c r="B61" s="18" t="s">
+        <v>115</v>
+      </c>
+      <c r="C61" s="19" t="s">
+        <v>116</v>
+      </c>
+      <c r="D61" s="1"/>
+      <c r="E61" s="3" t="s">
+        <v>80</v>
+      </c>
+      <c r="F61" s="1" t="s">
+        <v>67</v>
+      </c>
+      <c r="G61" s="20"/>
+      <c r="H61" s="1"/>
+      <c r="I61" s="1"/>
+      <c r="J61" s="1"/>
+    </row>
+    <row r="62" spans="1:10">
+      <c r="A62" s="33"/>
+      <c r="B62" s="18" t="s">
+        <v>117</v>
+      </c>
+      <c r="C62" s="19" t="s">
+        <v>118</v>
+      </c>
+      <c r="D62" s="1"/>
+      <c r="E62" s="3" t="s">
+        <v>89</v>
+      </c>
+      <c r="F62" s="1" t="s">
+        <v>123</v>
+      </c>
+      <c r="G62" s="20"/>
+      <c r="H62" s="1"/>
+      <c r="I62" s="1"/>
+      <c r="J62" s="1"/>
+    </row>
+    <row r="63" spans="1:10">
+      <c r="A63" s="33"/>
+      <c r="B63" s="18" t="s">
+        <v>77</v>
+      </c>
+      <c r="C63" s="19" t="s">
+        <v>78</v>
+      </c>
+      <c r="D63" s="1"/>
+      <c r="E63" s="3" t="s">
+        <v>89</v>
+      </c>
+      <c r="F63" s="1" t="s">
+        <v>80</v>
+      </c>
+      <c r="G63" s="20"/>
+      <c r="H63" s="1"/>
+      <c r="I63" s="1"/>
+      <c r="J63" s="1"/>
+    </row>
+    <row r="64" spans="1:10">
+      <c r="A64" s="33"/>
+      <c r="B64" s="18" t="s">
+        <v>105</v>
+      </c>
+      <c r="C64" s="19" t="s">
+        <v>119</v>
+      </c>
+      <c r="D64" s="1"/>
+      <c r="E64" s="3" t="s">
+        <v>80</v>
+      </c>
+      <c r="F64" s="1" t="s">
+        <v>90</v>
+      </c>
+      <c r="G64" s="20"/>
+      <c r="H64" s="1"/>
+      <c r="I64" s="1"/>
+      <c r="J64" s="1"/>
+    </row>
+    <row r="65" spans="1:10">
+      <c r="A65" s="33"/>
+      <c r="B65" s="18"/>
+      <c r="C65" s="19" t="s">
+        <v>120</v>
+      </c>
+      <c r="D65" s="1"/>
+      <c r="E65" s="3" t="s">
+        <v>80</v>
+      </c>
+      <c r="F65" s="1" t="s">
+        <v>89</v>
+      </c>
+      <c r="G65" s="20"/>
+      <c r="H65" s="1"/>
+      <c r="I65" s="1"/>
+      <c r="J65" s="1"/>
+    </row>
+    <row r="66" spans="1:10">
+      <c r="A66" s="33"/>
+      <c r="B66" s="18" t="s">
+        <v>101</v>
+      </c>
+      <c r="C66" s="19" t="s">
+        <v>102</v>
+      </c>
+      <c r="D66" s="1"/>
+      <c r="E66" s="3" t="s">
+        <v>67</v>
+      </c>
+      <c r="F66" s="1" t="s">
+        <v>80</v>
+      </c>
+      <c r="G66" s="20"/>
+      <c r="H66" s="1"/>
+      <c r="I66" s="1"/>
+      <c r="J66" s="1"/>
+    </row>
+    <row r="67" spans="1:10">
+      <c r="A67" s="33"/>
+      <c r="B67" s="18"/>
+      <c r="C67" s="19" t="s">
+        <v>103</v>
+      </c>
+      <c r="D67" s="1"/>
+      <c r="E67" s="3" t="s">
+        <v>80</v>
+      </c>
+      <c r="F67" s="3" t="s">
+        <v>89</v>
+      </c>
+      <c r="G67" s="20"/>
+      <c r="H67" s="1"/>
+      <c r="I67" s="1"/>
+      <c r="J67" s="1"/>
+    </row>
+    <row r="68" spans="1:10">
+      <c r="A68" s="33"/>
+      <c r="B68" s="18"/>
+      <c r="C68" s="19" t="s">
+        <v>104</v>
+      </c>
+      <c r="D68" s="1"/>
+      <c r="E68" s="3" t="s">
+        <v>80</v>
+      </c>
+      <c r="F68" s="3" t="s">
+        <v>89</v>
+      </c>
+      <c r="G68" s="20"/>
+      <c r="H68" s="1"/>
+      <c r="I68" s="1"/>
+      <c r="J68" s="1"/>
+    </row>
+    <row r="69" spans="1:10">
+      <c r="A69" s="33"/>
+      <c r="B69" s="18" t="s">
+        <v>121</v>
+      </c>
+      <c r="C69" s="19" t="s">
+        <v>122</v>
+      </c>
+      <c r="D69" s="1"/>
+      <c r="E69" s="3" t="s">
+        <v>89</v>
+      </c>
+      <c r="F69" s="1" t="s">
+        <v>67</v>
+      </c>
+      <c r="G69" s="20"/>
+      <c r="H69" s="1"/>
+      <c r="I69" s="1"/>
+      <c r="J69" s="1"/>
+    </row>
+    <row r="70" spans="1:10">
+      <c r="A70" s="28" t="s">
+        <v>64</v>
+      </c>
+      <c r="B70" s="29" t="s">
+        <v>65</v>
+      </c>
+      <c r="C70" s="22" t="s">
+        <v>44</v>
+      </c>
+      <c r="D70" s="1"/>
+      <c r="E70" s="3" t="s">
+        <v>69</v>
+      </c>
+      <c r="F70" s="1" t="s">
+        <v>81</v>
+      </c>
+      <c r="G70" s="20"/>
+      <c r="H70" s="1"/>
+      <c r="I70" s="1"/>
+      <c r="J70" s="1"/>
+    </row>
+    <row r="71" spans="1:10">
+      <c r="A71" s="28"/>
+      <c r="B71" s="29"/>
+      <c r="C71" s="22" t="s">
+        <v>45</v>
+      </c>
+      <c r="D71" s="1"/>
+      <c r="E71" s="3" t="s">
+        <v>67</v>
+      </c>
+      <c r="F71" s="1" t="s">
+        <v>89</v>
+      </c>
+      <c r="G71" s="20"/>
+      <c r="H71" s="1"/>
+      <c r="I71" s="1"/>
+      <c r="J71" s="1"/>
+    </row>
+    <row r="72" spans="1:10">
+      <c r="A72" s="28"/>
+      <c r="B72" s="29"/>
+      <c r="C72" s="22" t="s">
+        <v>46</v>
+      </c>
+      <c r="D72" s="1"/>
+      <c r="E72" s="3" t="s">
+        <v>70</v>
+      </c>
+      <c r="F72" s="1" t="s">
+        <v>79</v>
+      </c>
+      <c r="G72" s="20"/>
+      <c r="H72" s="1"/>
+      <c r="I72" s="1"/>
+      <c r="J72" s="1"/>
+    </row>
+    <row r="73" spans="1:10">
+      <c r="A73" s="28"/>
+      <c r="B73" s="29"/>
+      <c r="C73" s="22" t="s">
+        <v>124</v>
+      </c>
+      <c r="D73" s="1"/>
+      <c r="E73" s="3" t="s">
+        <v>94</v>
+      </c>
+      <c r="F73" s="1" t="s">
+        <v>70</v>
+      </c>
+      <c r="G73" s="20"/>
+      <c r="H73" s="1"/>
+      <c r="I73" s="1"/>
+      <c r="J73" s="1"/>
+    </row>
+    <row r="74" spans="1:10">
+      <c r="A74" s="28"/>
+      <c r="B74" s="29"/>
+      <c r="C74" s="22" t="s">
+        <v>125</v>
+      </c>
+      <c r="D74" s="1"/>
+      <c r="E74" s="3" t="s">
+        <v>70</v>
+      </c>
+      <c r="F74" s="1" t="s">
+        <v>79</v>
+      </c>
+      <c r="G74" s="20"/>
+      <c r="H74" s="1"/>
+      <c r="I74" s="1"/>
+      <c r="J74" s="1"/>
+    </row>
+    <row r="75" spans="1:10">
+      <c r="A75" s="28"/>
+      <c r="B75" s="29"/>
+      <c r="C75" s="22" t="s">
+        <v>60</v>
+      </c>
+      <c r="D75" s="1"/>
+      <c r="E75" s="3" t="s">
+        <v>92</v>
+      </c>
+      <c r="F75" s="1" t="s">
+        <v>67</v>
+      </c>
+      <c r="G75" s="20"/>
+      <c r="H75" s="1"/>
+      <c r="I75" s="1"/>
+      <c r="J75" s="1"/>
+    </row>
+    <row r="76" spans="1:10">
+      <c r="A76" s="26"/>
+      <c r="B76" s="27"/>
+      <c r="G76" s="20"/>
+      <c r="H76" s="1"/>
+      <c r="I76" s="1"/>
+      <c r="J76" s="1"/>
+    </row>
   </sheetData>
-  <autoFilter ref="B1:H59">
+  <autoFilter ref="B1:H75">
     <filterColumn colId="3"/>
     <filterColumn colId="5"/>
   </autoFilter>
   <mergeCells count="13">
-    <mergeCell ref="A56:A59"/>
-    <mergeCell ref="B56:B59"/>
-    <mergeCell ref="B28:B31"/>
-    <mergeCell ref="B32:B35"/>
+    <mergeCell ref="A70:A75"/>
+    <mergeCell ref="B70:B75"/>
+    <mergeCell ref="B30:B33"/>
+    <mergeCell ref="B35:B38"/>
     <mergeCell ref="B4:B10"/>
-    <mergeCell ref="A50:A55"/>
-    <mergeCell ref="A2:A49"/>
+    <mergeCell ref="A53:A69"/>
+    <mergeCell ref="A2:A52"/>
     <mergeCell ref="B11:B14"/>
     <mergeCell ref="B15:B19"/>
-    <mergeCell ref="B20:B27"/>
-    <mergeCell ref="B36:B38"/>
+    <mergeCell ref="B20:B29"/>
     <mergeCell ref="B39:B41"/>
-    <mergeCell ref="B42:B49"/>
+    <mergeCell ref="B42:B44"/>
+    <mergeCell ref="B45:B52"/>
   </mergeCells>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/internal_doc/05.测试设计/特性守护矩阵.xlsx
+++ b/internal_doc/05.测试设计/特性守护矩阵.xlsx
@@ -19,7 +19,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="256" uniqueCount="131">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="257" uniqueCount="132">
   <si>
     <t>优先级</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -541,6 +541,12 @@
   </si>
   <si>
     <t>赵小妮</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve">备注：1、所有特性有主次责任人共同维护，优先由主要责任人负责，次要责任人协助主要责任人维护（如主要责任人当前事情较多无法维护，可由次要责任人协助处理）
+2、定期3-6个月更新维护矩阵主次责任人（参考维护频率调整）
+</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -673,7 +679,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="3">
+  <borders count="4">
     <border>
       <left/>
       <right/>
@@ -707,11 +713,20 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="35">
+  <cellXfs count="36">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="5" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
@@ -769,9 +784,6 @@
     <xf numFmtId="0" fontId="0" fillId="7" borderId="0" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="7" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -793,6 +805,10 @@
     <xf numFmtId="0" fontId="0" fillId="4" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -1200,7 +1216,7 @@
       </c>
     </row>
     <row r="2" spans="1:10">
-      <c r="A2" s="34" t="s">
+      <c r="A2" s="33" t="s">
         <v>63</v>
       </c>
       <c r="B2" s="16" t="s">
@@ -1222,7 +1238,7 @@
       <c r="J2" s="3"/>
     </row>
     <row r="3" spans="1:10">
-      <c r="A3" s="34"/>
+      <c r="A3" s="33"/>
       <c r="B3" s="21" t="s">
         <v>12</v>
       </c>
@@ -1242,8 +1258,8 @@
       <c r="J3" s="3"/>
     </row>
     <row r="4" spans="1:10" ht="27" customHeight="1">
-      <c r="A4" s="34"/>
-      <c r="B4" s="32" t="s">
+      <c r="A4" s="33"/>
+      <c r="B4" s="31" t="s">
         <v>68</v>
       </c>
       <c r="C4" s="17" t="s">
@@ -1262,8 +1278,8 @@
       <c r="J4" s="3"/>
     </row>
     <row r="5" spans="1:10">
-      <c r="A5" s="34"/>
-      <c r="B5" s="32"/>
+      <c r="A5" s="33"/>
+      <c r="B5" s="31"/>
       <c r="C5" s="17" t="s">
         <v>14</v>
       </c>
@@ -1280,8 +1296,8 @@
       <c r="J5" s="3"/>
     </row>
     <row r="6" spans="1:10">
-      <c r="A6" s="34"/>
-      <c r="B6" s="32"/>
+      <c r="A6" s="33"/>
+      <c r="B6" s="31"/>
       <c r="C6" s="17" t="s">
         <v>15</v>
       </c>
@@ -1298,8 +1314,8 @@
       <c r="J6" s="3"/>
     </row>
     <row r="7" spans="1:10">
-      <c r="A7" s="34"/>
-      <c r="B7" s="32"/>
+      <c r="A7" s="33"/>
+      <c r="B7" s="31"/>
       <c r="C7" s="17" t="s">
         <v>16</v>
       </c>
@@ -1316,8 +1332,8 @@
       <c r="J7" s="3"/>
     </row>
     <row r="8" spans="1:10">
-      <c r="A8" s="34"/>
-      <c r="B8" s="32"/>
+      <c r="A8" s="33"/>
+      <c r="B8" s="31"/>
       <c r="C8" s="17" t="s">
         <v>53</v>
       </c>
@@ -1334,8 +1350,8 @@
       <c r="J8" s="3"/>
     </row>
     <row r="9" spans="1:10">
-      <c r="A9" s="34"/>
-      <c r="B9" s="32"/>
+      <c r="A9" s="33"/>
+      <c r="B9" s="31"/>
       <c r="C9" s="17" t="s">
         <v>17</v>
       </c>
@@ -1352,8 +1368,8 @@
       <c r="J9" s="3"/>
     </row>
     <row r="10" spans="1:10">
-      <c r="A10" s="34"/>
-      <c r="B10" s="32"/>
+      <c r="A10" s="33"/>
+      <c r="B10" s="31"/>
       <c r="C10" s="17" t="s">
         <v>18</v>
       </c>
@@ -1370,8 +1386,8 @@
       <c r="J10" s="3"/>
     </row>
     <row r="11" spans="1:10">
-      <c r="A11" s="34"/>
-      <c r="B11" s="31" t="s">
+      <c r="A11" s="33"/>
+      <c r="B11" s="30" t="s">
         <v>19</v>
       </c>
       <c r="C11" s="14" t="s">
@@ -1390,8 +1406,8 @@
       <c r="J11" s="3"/>
     </row>
     <row r="12" spans="1:10">
-      <c r="A12" s="34"/>
-      <c r="B12" s="31"/>
+      <c r="A12" s="33"/>
+      <c r="B12" s="30"/>
       <c r="C12" s="14" t="s">
         <v>54</v>
       </c>
@@ -1408,8 +1424,8 @@
       <c r="J12" s="3"/>
     </row>
     <row r="13" spans="1:10">
-      <c r="A13" s="34"/>
-      <c r="B13" s="31"/>
+      <c r="A13" s="33"/>
+      <c r="B13" s="30"/>
       <c r="C13" s="14" t="s">
         <v>55</v>
       </c>
@@ -1426,8 +1442,8 @@
       <c r="J13" s="3"/>
     </row>
     <row r="14" spans="1:10">
-      <c r="A14" s="34"/>
-      <c r="B14" s="31"/>
+      <c r="A14" s="33"/>
+      <c r="B14" s="30"/>
       <c r="C14" s="14" t="s">
         <v>56</v>
       </c>
@@ -1444,8 +1460,8 @@
       <c r="J14" s="3"/>
     </row>
     <row r="15" spans="1:10">
-      <c r="A15" s="34"/>
-      <c r="B15" s="32" t="s">
+      <c r="A15" s="33"/>
+      <c r="B15" s="31" t="s">
         <v>21</v>
       </c>
       <c r="C15" s="17" t="s">
@@ -1464,8 +1480,8 @@
       <c r="J15" s="3"/>
     </row>
     <row r="16" spans="1:10">
-      <c r="A16" s="34"/>
-      <c r="B16" s="32"/>
+      <c r="A16" s="33"/>
+      <c r="B16" s="31"/>
       <c r="C16" s="17" t="s">
         <v>62</v>
       </c>
@@ -1482,8 +1498,8 @@
       <c r="J16" s="3"/>
     </row>
     <row r="17" spans="1:10">
-      <c r="A17" s="34"/>
-      <c r="B17" s="32"/>
+      <c r="A17" s="33"/>
+      <c r="B17" s="31"/>
       <c r="C17" s="17" t="s">
         <v>23</v>
       </c>
@@ -1500,8 +1516,8 @@
       <c r="J17" s="3"/>
     </row>
     <row r="18" spans="1:10">
-      <c r="A18" s="34"/>
-      <c r="B18" s="32"/>
+      <c r="A18" s="33"/>
+      <c r="B18" s="31"/>
       <c r="C18" s="17" t="s">
         <v>24</v>
       </c>
@@ -1518,8 +1534,8 @@
       <c r="J18" s="3"/>
     </row>
     <row r="19" spans="1:10">
-      <c r="A19" s="34"/>
-      <c r="B19" s="32"/>
+      <c r="A19" s="33"/>
+      <c r="B19" s="31"/>
       <c r="C19" s="17" t="s">
         <v>25</v>
       </c>
@@ -1536,8 +1552,8 @@
       <c r="J19" s="3"/>
     </row>
     <row r="20" spans="1:10" ht="27">
-      <c r="A20" s="34"/>
-      <c r="B20" s="31" t="s">
+      <c r="A20" s="33"/>
+      <c r="B20" s="30" t="s">
         <v>26</v>
       </c>
       <c r="C20" s="14" t="s">
@@ -1556,8 +1572,8 @@
       <c r="J20" s="3"/>
     </row>
     <row r="21" spans="1:10" ht="27">
-      <c r="A21" s="34"/>
-      <c r="B21" s="31"/>
+      <c r="A21" s="33"/>
+      <c r="B21" s="30"/>
       <c r="C21" s="14" t="s">
         <v>72</v>
       </c>
@@ -1574,8 +1590,8 @@
       <c r="J21" s="3"/>
     </row>
     <row r="22" spans="1:10">
-      <c r="A22" s="34"/>
-      <c r="B22" s="31"/>
+      <c r="A22" s="33"/>
+      <c r="B22" s="30"/>
       <c r="C22" s="14" t="s">
         <v>93</v>
       </c>
@@ -1592,8 +1608,8 @@
       <c r="J22" s="3"/>
     </row>
     <row r="23" spans="1:10">
-      <c r="A23" s="34"/>
-      <c r="B23" s="31"/>
+      <c r="A23" s="33"/>
+      <c r="B23" s="30"/>
       <c r="C23" s="14" t="s">
         <v>71</v>
       </c>
@@ -1610,8 +1626,8 @@
       <c r="J23" s="3"/>
     </row>
     <row r="24" spans="1:10">
-      <c r="A24" s="34"/>
-      <c r="B24" s="31"/>
+      <c r="A24" s="33"/>
+      <c r="B24" s="30"/>
       <c r="C24" s="14" t="s">
         <v>27</v>
       </c>
@@ -1628,8 +1644,8 @@
       <c r="J24" s="3"/>
     </row>
     <row r="25" spans="1:10">
-      <c r="A25" s="34"/>
-      <c r="B25" s="31"/>
+      <c r="A25" s="33"/>
+      <c r="B25" s="30"/>
       <c r="C25" s="14" t="s">
         <v>28</v>
       </c>
@@ -1646,8 +1662,8 @@
       <c r="J25" s="3"/>
     </row>
     <row r="26" spans="1:10">
-      <c r="A26" s="34"/>
-      <c r="B26" s="31"/>
+      <c r="A26" s="33"/>
+      <c r="B26" s="30"/>
       <c r="C26" s="14" t="s">
         <v>29</v>
       </c>
@@ -1664,8 +1680,8 @@
       <c r="J26" s="1"/>
     </row>
     <row r="27" spans="1:10">
-      <c r="A27" s="34"/>
-      <c r="B27" s="31"/>
+      <c r="A27" s="33"/>
+      <c r="B27" s="30"/>
       <c r="C27" s="14" t="s">
         <v>30</v>
       </c>
@@ -1682,8 +1698,8 @@
       <c r="J27" s="1"/>
     </row>
     <row r="28" spans="1:10">
-      <c r="A28" s="34"/>
-      <c r="B28" s="31"/>
+      <c r="A28" s="33"/>
+      <c r="B28" s="30"/>
       <c r="C28" s="14" t="s">
         <v>106</v>
       </c>
@@ -1700,8 +1716,8 @@
       <c r="J28" s="1"/>
     </row>
     <row r="29" spans="1:10">
-      <c r="A29" s="34"/>
-      <c r="B29" s="31"/>
+      <c r="A29" s="33"/>
+      <c r="B29" s="30"/>
       <c r="C29" s="14" t="s">
         <v>82</v>
       </c>
@@ -1718,8 +1734,8 @@
       <c r="J29" s="1"/>
     </row>
     <row r="30" spans="1:10" ht="27" customHeight="1">
-      <c r="A30" s="34"/>
-      <c r="B30" s="30" t="s">
+      <c r="A30" s="33"/>
+      <c r="B30" s="29" t="s">
         <v>47</v>
       </c>
       <c r="C30" s="15" t="s">
@@ -1738,8 +1754,8 @@
       <c r="J30" s="1"/>
     </row>
     <row r="31" spans="1:10">
-      <c r="A31" s="34"/>
-      <c r="B31" s="30"/>
+      <c r="A31" s="33"/>
+      <c r="B31" s="29"/>
       <c r="C31" s="15" t="s">
         <v>48</v>
       </c>
@@ -1756,8 +1772,8 @@
       <c r="J31" s="1"/>
     </row>
     <row r="32" spans="1:10">
-      <c r="A32" s="34"/>
-      <c r="B32" s="30"/>
+      <c r="A32" s="33"/>
+      <c r="B32" s="29"/>
       <c r="C32" s="15" t="s">
         <v>49</v>
       </c>
@@ -1774,8 +1790,8 @@
       <c r="J32" s="1"/>
     </row>
     <row r="33" spans="1:10">
-      <c r="A33" s="34"/>
-      <c r="B33" s="30"/>
+      <c r="A33" s="33"/>
+      <c r="B33" s="29"/>
       <c r="C33" s="15" t="s">
         <v>59</v>
       </c>
@@ -1792,7 +1808,7 @@
       <c r="J33" s="1"/>
     </row>
     <row r="34" spans="1:10">
-      <c r="A34" s="34"/>
+      <c r="A34" s="33"/>
       <c r="B34" s="23"/>
       <c r="C34" s="15" t="s">
         <v>127</v>
@@ -1810,8 +1826,8 @@
       <c r="J34" s="1"/>
     </row>
     <row r="35" spans="1:10">
-      <c r="A35" s="34"/>
-      <c r="B35" s="31" t="s">
+      <c r="A35" s="33"/>
+      <c r="B35" s="30" t="s">
         <v>50</v>
       </c>
       <c r="C35" s="14" t="s">
@@ -1830,8 +1846,8 @@
       <c r="J35" s="1"/>
     </row>
     <row r="36" spans="1:10">
-      <c r="A36" s="34"/>
-      <c r="B36" s="31"/>
+      <c r="A36" s="33"/>
+      <c r="B36" s="30"/>
       <c r="C36" s="14" t="s">
         <v>86</v>
       </c>
@@ -1848,8 +1864,8 @@
       <c r="J36" s="1"/>
     </row>
     <row r="37" spans="1:10">
-      <c r="A37" s="34"/>
-      <c r="B37" s="31"/>
+      <c r="A37" s="33"/>
+      <c r="B37" s="30"/>
       <c r="C37" s="14" t="s">
         <v>85</v>
       </c>
@@ -1866,8 +1882,8 @@
       <c r="J37" s="1"/>
     </row>
     <row r="38" spans="1:10">
-      <c r="A38" s="34"/>
-      <c r="B38" s="31"/>
+      <c r="A38" s="33"/>
+      <c r="B38" s="30"/>
       <c r="C38" s="14" t="s">
         <v>58</v>
       </c>
@@ -1884,8 +1900,8 @@
       <c r="J38" s="1"/>
     </row>
     <row r="39" spans="1:10">
-      <c r="A39" s="34"/>
-      <c r="B39" s="32" t="s">
+      <c r="A39" s="33"/>
+      <c r="B39" s="31" t="s">
         <v>31</v>
       </c>
       <c r="C39" s="17" t="s">
@@ -1904,8 +1920,8 @@
       <c r="J39" s="1"/>
     </row>
     <row r="40" spans="1:10">
-      <c r="A40" s="34"/>
-      <c r="B40" s="32"/>
+      <c r="A40" s="33"/>
+      <c r="B40" s="31"/>
       <c r="C40" s="17" t="s">
         <v>33</v>
       </c>
@@ -1922,8 +1938,8 @@
       <c r="J40" s="1"/>
     </row>
     <row r="41" spans="1:10">
-      <c r="A41" s="34"/>
-      <c r="B41" s="32"/>
+      <c r="A41" s="33"/>
+      <c r="B41" s="31"/>
       <c r="C41" s="17" t="s">
         <v>34</v>
       </c>
@@ -1940,8 +1956,8 @@
       <c r="J41" s="1"/>
     </row>
     <row r="42" spans="1:10">
-      <c r="A42" s="34"/>
-      <c r="B42" s="31" t="s">
+      <c r="A42" s="33"/>
+      <c r="B42" s="30" t="s">
         <v>35</v>
       </c>
       <c r="C42" s="14" t="s">
@@ -1960,8 +1976,8 @@
       <c r="J42" s="1"/>
     </row>
     <row r="43" spans="1:10">
-      <c r="A43" s="34"/>
-      <c r="B43" s="31"/>
+      <c r="A43" s="33"/>
+      <c r="B43" s="30"/>
       <c r="C43" s="14" t="s">
         <v>36</v>
       </c>
@@ -1978,8 +1994,8 @@
       <c r="J43" s="1"/>
     </row>
     <row r="44" spans="1:10">
-      <c r="A44" s="34"/>
-      <c r="B44" s="31"/>
+      <c r="A44" s="33"/>
+      <c r="B44" s="30"/>
       <c r="C44" s="14" t="s">
         <v>37</v>
       </c>
@@ -1996,8 +2012,8 @@
       <c r="J44" s="1"/>
     </row>
     <row r="45" spans="1:10">
-      <c r="A45" s="34"/>
-      <c r="B45" s="32" t="s">
+      <c r="A45" s="33"/>
+      <c r="B45" s="31" t="s">
         <v>38</v>
       </c>
       <c r="C45" s="17" t="s">
@@ -2016,8 +2032,8 @@
       <c r="J45" s="1"/>
     </row>
     <row r="46" spans="1:10">
-      <c r="A46" s="34"/>
-      <c r="B46" s="32"/>
+      <c r="A46" s="33"/>
+      <c r="B46" s="31"/>
       <c r="C46" s="17" t="s">
         <v>98</v>
       </c>
@@ -2034,8 +2050,8 @@
       <c r="J46" s="1"/>
     </row>
     <row r="47" spans="1:10">
-      <c r="A47" s="34"/>
-      <c r="B47" s="32"/>
+      <c r="A47" s="33"/>
+      <c r="B47" s="31"/>
       <c r="C47" s="17" t="s">
         <v>39</v>
       </c>
@@ -2052,8 +2068,8 @@
       <c r="J47" s="1"/>
     </row>
     <row r="48" spans="1:10">
-      <c r="A48" s="34"/>
-      <c r="B48" s="32"/>
+      <c r="A48" s="33"/>
+      <c r="B48" s="31"/>
       <c r="C48" s="17" t="s">
         <v>40</v>
       </c>
@@ -2070,8 +2086,8 @@
       <c r="J48" s="1"/>
     </row>
     <row r="49" spans="1:10">
-      <c r="A49" s="34"/>
-      <c r="B49" s="32"/>
+      <c r="A49" s="33"/>
+      <c r="B49" s="31"/>
       <c r="C49" s="17" t="s">
         <v>41</v>
       </c>
@@ -2088,8 +2104,8 @@
       <c r="J49" s="1"/>
     </row>
     <row r="50" spans="1:10">
-      <c r="A50" s="34"/>
-      <c r="B50" s="32"/>
+      <c r="A50" s="33"/>
+      <c r="B50" s="31"/>
       <c r="C50" s="17" t="s">
         <v>84</v>
       </c>
@@ -2106,8 +2122,8 @@
       <c r="J50" s="1"/>
     </row>
     <row r="51" spans="1:10">
-      <c r="A51" s="34"/>
-      <c r="B51" s="32"/>
+      <c r="A51" s="33"/>
+      <c r="B51" s="31"/>
       <c r="C51" s="17" t="s">
         <v>42</v>
       </c>
@@ -2124,8 +2140,8 @@
       <c r="J51" s="1"/>
     </row>
     <row r="52" spans="1:10">
-      <c r="A52" s="34"/>
-      <c r="B52" s="32"/>
+      <c r="A52" s="33"/>
+      <c r="B52" s="31"/>
       <c r="C52" s="17" t="s">
         <v>43</v>
       </c>
@@ -2142,7 +2158,7 @@
       <c r="J52" s="1"/>
     </row>
     <row r="53" spans="1:10">
-      <c r="A53" s="33" t="s">
+      <c r="A53" s="32" t="s">
         <v>74</v>
       </c>
       <c r="B53" s="18" t="s">
@@ -2164,7 +2180,7 @@
       <c r="J53" s="1"/>
     </row>
     <row r="54" spans="1:10">
-      <c r="A54" s="33"/>
+      <c r="A54" s="32"/>
       <c r="B54" s="18"/>
       <c r="C54" s="19" t="s">
         <v>108</v>
@@ -2182,7 +2198,7 @@
       <c r="J54" s="1"/>
     </row>
     <row r="55" spans="1:10">
-      <c r="A55" s="33"/>
+      <c r="A55" s="32"/>
       <c r="B55" s="18"/>
       <c r="C55" s="19" t="s">
         <v>107</v>
@@ -2200,7 +2216,7 @@
       <c r="J55" s="1"/>
     </row>
     <row r="56" spans="1:10">
-      <c r="A56" s="33"/>
+      <c r="A56" s="32"/>
       <c r="B56" s="18"/>
       <c r="C56" s="19" t="s">
         <v>83</v>
@@ -2218,7 +2234,7 @@
       <c r="J56" s="1"/>
     </row>
     <row r="57" spans="1:10">
-      <c r="A57" s="33"/>
+      <c r="A57" s="32"/>
       <c r="B57" s="18"/>
       <c r="C57" s="19" t="s">
         <v>109</v>
@@ -2236,7 +2252,7 @@
       <c r="J57" s="1"/>
     </row>
     <row r="58" spans="1:10">
-      <c r="A58" s="33"/>
+      <c r="A58" s="32"/>
       <c r="B58" s="18"/>
       <c r="C58" s="19" t="s">
         <v>110</v>
@@ -2254,7 +2270,7 @@
       <c r="J58" s="1"/>
     </row>
     <row r="59" spans="1:10" ht="27">
-      <c r="A59" s="33"/>
+      <c r="A59" s="32"/>
       <c r="B59" s="18" t="s">
         <v>111</v>
       </c>
@@ -2274,7 +2290,7 @@
       <c r="J59" s="1"/>
     </row>
     <row r="60" spans="1:10">
-      <c r="A60" s="33"/>
+      <c r="A60" s="32"/>
       <c r="B60" s="18" t="s">
         <v>113</v>
       </c>
@@ -2294,7 +2310,7 @@
       <c r="J60" s="1"/>
     </row>
     <row r="61" spans="1:10" ht="27">
-      <c r="A61" s="33"/>
+      <c r="A61" s="32"/>
       <c r="B61" s="18" t="s">
         <v>115</v>
       </c>
@@ -2314,7 +2330,7 @@
       <c r="J61" s="1"/>
     </row>
     <row r="62" spans="1:10">
-      <c r="A62" s="33"/>
+      <c r="A62" s="32"/>
       <c r="B62" s="18" t="s">
         <v>117</v>
       </c>
@@ -2334,7 +2350,7 @@
       <c r="J62" s="1"/>
     </row>
     <row r="63" spans="1:10">
-      <c r="A63" s="33"/>
+      <c r="A63" s="32"/>
       <c r="B63" s="18" t="s">
         <v>77</v>
       </c>
@@ -2354,7 +2370,7 @@
       <c r="J63" s="1"/>
     </row>
     <row r="64" spans="1:10">
-      <c r="A64" s="33"/>
+      <c r="A64" s="32"/>
       <c r="B64" s="18" t="s">
         <v>105</v>
       </c>
@@ -2374,7 +2390,7 @@
       <c r="J64" s="1"/>
     </row>
     <row r="65" spans="1:10">
-      <c r="A65" s="33"/>
+      <c r="A65" s="32"/>
       <c r="B65" s="18"/>
       <c r="C65" s="19" t="s">
         <v>120</v>
@@ -2392,7 +2408,7 @@
       <c r="J65" s="1"/>
     </row>
     <row r="66" spans="1:10">
-      <c r="A66" s="33"/>
+      <c r="A66" s="32"/>
       <c r="B66" s="18" t="s">
         <v>101</v>
       </c>
@@ -2412,7 +2428,7 @@
       <c r="J66" s="1"/>
     </row>
     <row r="67" spans="1:10">
-      <c r="A67" s="33"/>
+      <c r="A67" s="32"/>
       <c r="B67" s="18"/>
       <c r="C67" s="19" t="s">
         <v>103</v>
@@ -2430,7 +2446,7 @@
       <c r="J67" s="1"/>
     </row>
     <row r="68" spans="1:10">
-      <c r="A68" s="33"/>
+      <c r="A68" s="32"/>
       <c r="B68" s="18"/>
       <c r="C68" s="19" t="s">
         <v>104</v>
@@ -2448,7 +2464,7 @@
       <c r="J68" s="1"/>
     </row>
     <row r="69" spans="1:10">
-      <c r="A69" s="33"/>
+      <c r="A69" s="32"/>
       <c r="B69" s="18" t="s">
         <v>121</v>
       </c>
@@ -2468,10 +2484,10 @@
       <c r="J69" s="1"/>
     </row>
     <row r="70" spans="1:10">
-      <c r="A70" s="28" t="s">
+      <c r="A70" s="27" t="s">
         <v>64</v>
       </c>
-      <c r="B70" s="29" t="s">
+      <c r="B70" s="28" t="s">
         <v>65</v>
       </c>
       <c r="C70" s="22" t="s">
@@ -2490,8 +2506,8 @@
       <c r="J70" s="1"/>
     </row>
     <row r="71" spans="1:10">
-      <c r="A71" s="28"/>
-      <c r="B71" s="29"/>
+      <c r="A71" s="27"/>
+      <c r="B71" s="28"/>
       <c r="C71" s="22" t="s">
         <v>45</v>
       </c>
@@ -2508,8 +2524,8 @@
       <c r="J71" s="1"/>
     </row>
     <row r="72" spans="1:10">
-      <c r="A72" s="28"/>
-      <c r="B72" s="29"/>
+      <c r="A72" s="27"/>
+      <c r="B72" s="28"/>
       <c r="C72" s="22" t="s">
         <v>46</v>
       </c>
@@ -2526,8 +2542,8 @@
       <c r="J72" s="1"/>
     </row>
     <row r="73" spans="1:10">
-      <c r="A73" s="28"/>
-      <c r="B73" s="29"/>
+      <c r="A73" s="27"/>
+      <c r="B73" s="28"/>
       <c r="C73" s="22" t="s">
         <v>124</v>
       </c>
@@ -2544,8 +2560,8 @@
       <c r="J73" s="1"/>
     </row>
     <row r="74" spans="1:10">
-      <c r="A74" s="28"/>
-      <c r="B74" s="29"/>
+      <c r="A74" s="27"/>
+      <c r="B74" s="28"/>
       <c r="C74" s="22" t="s">
         <v>125</v>
       </c>
@@ -2562,8 +2578,8 @@
       <c r="J74" s="1"/>
     </row>
     <row r="75" spans="1:10">
-      <c r="A75" s="28"/>
-      <c r="B75" s="29"/>
+      <c r="A75" s="27"/>
+      <c r="B75" s="28"/>
       <c r="C75" s="22" t="s">
         <v>60</v>
       </c>
@@ -2579,9 +2595,14 @@
       <c r="I75" s="1"/>
       <c r="J75" s="1"/>
     </row>
-    <row r="76" spans="1:10">
+    <row r="76" spans="1:10" ht="36.75" customHeight="1">
       <c r="A76" s="26"/>
-      <c r="B76" s="27"/>
+      <c r="B76" s="34" t="s">
+        <v>131</v>
+      </c>
+      <c r="C76" s="35"/>
+      <c r="D76" s="35"/>
+      <c r="E76" s="35"/>
       <c r="G76" s="20"/>
       <c r="H76" s="1"/>
       <c r="I76" s="1"/>
@@ -2592,7 +2613,8 @@
     <filterColumn colId="3"/>
     <filterColumn colId="5"/>
   </autoFilter>
-  <mergeCells count="13">
+  <mergeCells count="14">
+    <mergeCell ref="B76:E76"/>
     <mergeCell ref="A70:A75"/>
     <mergeCell ref="B70:B75"/>
     <mergeCell ref="B30:B33"/>

--- a/internal_doc/05.测试设计/特性守护矩阵.xlsx
+++ b/internal_doc/05.测试设计/特性守护矩阵.xlsx
@@ -12,14 +12,14 @@
     <sheet name="Sheet3" sheetId="3" r:id="rId3"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet1!$B$1:$H$75</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet1!$B$1:$H$76</definedName>
   </definedNames>
   <calcPr calcId="124519"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="257" uniqueCount="132">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="260" uniqueCount="133">
   <si>
     <t>优先级</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -548,6 +548,10 @@
 2、定期3-6个月更新维护矩阵主次责任人（参考维护频率调整）
 </t>
     <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>索引管理（idindex、index）</t>
+    <phoneticPr fontId="8" type="noConversion"/>
   </si>
 </sst>
 </file>
@@ -784,6 +788,10 @@
     <xf numFmtId="0" fontId="0" fillId="7" borderId="0" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="0" fillId="7" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -805,10 +813,6 @@
     <xf numFmtId="0" fontId="0" fillId="4" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -1171,7 +1175,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:J76"/>
+  <dimension ref="A1:J77"/>
   <sheetFormatPr defaultRowHeight="13.5"/>
   <cols>
     <col min="3" max="3" width="55.25" customWidth="1"/>
@@ -1216,7 +1220,7 @@
       </c>
     </row>
     <row r="2" spans="1:10">
-      <c r="A2" s="33" t="s">
+      <c r="A2" s="35" t="s">
         <v>63</v>
       </c>
       <c r="B2" s="16" t="s">
@@ -1238,7 +1242,7 @@
       <c r="J2" s="3"/>
     </row>
     <row r="3" spans="1:10">
-      <c r="A3" s="33"/>
+      <c r="A3" s="35"/>
       <c r="B3" s="21" t="s">
         <v>12</v>
       </c>
@@ -1258,8 +1262,8 @@
       <c r="J3" s="3"/>
     </row>
     <row r="4" spans="1:10" ht="27" customHeight="1">
-      <c r="A4" s="33"/>
-      <c r="B4" s="31" t="s">
+      <c r="A4" s="35"/>
+      <c r="B4" s="33" t="s">
         <v>68</v>
       </c>
       <c r="C4" s="17" t="s">
@@ -1278,8 +1282,8 @@
       <c r="J4" s="3"/>
     </row>
     <row r="5" spans="1:10">
-      <c r="A5" s="33"/>
-      <c r="B5" s="31"/>
+      <c r="A5" s="35"/>
+      <c r="B5" s="33"/>
       <c r="C5" s="17" t="s">
         <v>14</v>
       </c>
@@ -1296,8 +1300,8 @@
       <c r="J5" s="3"/>
     </row>
     <row r="6" spans="1:10">
-      <c r="A6" s="33"/>
-      <c r="B6" s="31"/>
+      <c r="A6" s="35"/>
+      <c r="B6" s="33"/>
       <c r="C6" s="17" t="s">
         <v>15</v>
       </c>
@@ -1314,8 +1318,8 @@
       <c r="J6" s="3"/>
     </row>
     <row r="7" spans="1:10">
-      <c r="A7" s="33"/>
-      <c r="B7" s="31"/>
+      <c r="A7" s="35"/>
+      <c r="B7" s="33"/>
       <c r="C7" s="17" t="s">
         <v>16</v>
       </c>
@@ -1332,8 +1336,8 @@
       <c r="J7" s="3"/>
     </row>
     <row r="8" spans="1:10">
-      <c r="A8" s="33"/>
-      <c r="B8" s="31"/>
+      <c r="A8" s="35"/>
+      <c r="B8" s="33"/>
       <c r="C8" s="17" t="s">
         <v>53</v>
       </c>
@@ -1350,8 +1354,8 @@
       <c r="J8" s="3"/>
     </row>
     <row r="9" spans="1:10">
-      <c r="A9" s="33"/>
-      <c r="B9" s="31"/>
+      <c r="A9" s="35"/>
+      <c r="B9" s="33"/>
       <c r="C9" s="17" t="s">
         <v>17</v>
       </c>
@@ -1368,8 +1372,8 @@
       <c r="J9" s="3"/>
     </row>
     <row r="10" spans="1:10">
-      <c r="A10" s="33"/>
-      <c r="B10" s="31"/>
+      <c r="A10" s="35"/>
+      <c r="B10" s="33"/>
       <c r="C10" s="17" t="s">
         <v>18</v>
       </c>
@@ -1386,8 +1390,8 @@
       <c r="J10" s="3"/>
     </row>
     <row r="11" spans="1:10">
-      <c r="A11" s="33"/>
-      <c r="B11" s="30" t="s">
+      <c r="A11" s="35"/>
+      <c r="B11" s="32" t="s">
         <v>19</v>
       </c>
       <c r="C11" s="14" t="s">
@@ -1406,8 +1410,8 @@
       <c r="J11" s="3"/>
     </row>
     <row r="12" spans="1:10">
-      <c r="A12" s="33"/>
-      <c r="B12" s="30"/>
+      <c r="A12" s="35"/>
+      <c r="B12" s="32"/>
       <c r="C12" s="14" t="s">
         <v>54</v>
       </c>
@@ -1424,8 +1428,8 @@
       <c r="J12" s="3"/>
     </row>
     <row r="13" spans="1:10">
-      <c r="A13" s="33"/>
-      <c r="B13" s="30"/>
+      <c r="A13" s="35"/>
+      <c r="B13" s="32"/>
       <c r="C13" s="14" t="s">
         <v>55</v>
       </c>
@@ -1442,8 +1446,8 @@
       <c r="J13" s="3"/>
     </row>
     <row r="14" spans="1:10">
-      <c r="A14" s="33"/>
-      <c r="B14" s="30"/>
+      <c r="A14" s="35"/>
+      <c r="B14" s="32"/>
       <c r="C14" s="14" t="s">
         <v>56</v>
       </c>
@@ -1460,8 +1464,8 @@
       <c r="J14" s="3"/>
     </row>
     <row r="15" spans="1:10">
-      <c r="A15" s="33"/>
-      <c r="B15" s="31" t="s">
+      <c r="A15" s="35"/>
+      <c r="B15" s="33" t="s">
         <v>21</v>
       </c>
       <c r="C15" s="17" t="s">
@@ -1480,8 +1484,8 @@
       <c r="J15" s="3"/>
     </row>
     <row r="16" spans="1:10">
-      <c r="A16" s="33"/>
-      <c r="B16" s="31"/>
+      <c r="A16" s="35"/>
+      <c r="B16" s="33"/>
       <c r="C16" s="17" t="s">
         <v>62</v>
       </c>
@@ -1498,8 +1502,8 @@
       <c r="J16" s="3"/>
     </row>
     <row r="17" spans="1:10">
-      <c r="A17" s="33"/>
-      <c r="B17" s="31"/>
+      <c r="A17" s="35"/>
+      <c r="B17" s="33"/>
       <c r="C17" s="17" t="s">
         <v>23</v>
       </c>
@@ -1516,8 +1520,8 @@
       <c r="J17" s="3"/>
     </row>
     <row r="18" spans="1:10">
-      <c r="A18" s="33"/>
-      <c r="B18" s="31"/>
+      <c r="A18" s="35"/>
+      <c r="B18" s="33"/>
       <c r="C18" s="17" t="s">
         <v>24</v>
       </c>
@@ -1534,8 +1538,8 @@
       <c r="J18" s="3"/>
     </row>
     <row r="19" spans="1:10">
-      <c r="A19" s="33"/>
-      <c r="B19" s="31"/>
+      <c r="A19" s="35"/>
+      <c r="B19" s="33"/>
       <c r="C19" s="17" t="s">
         <v>25</v>
       </c>
@@ -1552,8 +1556,8 @@
       <c r="J19" s="3"/>
     </row>
     <row r="20" spans="1:10" ht="27">
-      <c r="A20" s="33"/>
-      <c r="B20" s="30" t="s">
+      <c r="A20" s="35"/>
+      <c r="B20" s="32" t="s">
         <v>26</v>
       </c>
       <c r="C20" s="14" t="s">
@@ -1571,36 +1575,36 @@
       <c r="I20" s="3"/>
       <c r="J20" s="3"/>
     </row>
-    <row r="21" spans="1:10" ht="27">
-      <c r="A21" s="33"/>
-      <c r="B21" s="30"/>
+    <row r="21" spans="1:10">
+      <c r="A21" s="35"/>
+      <c r="B21" s="32"/>
       <c r="C21" s="14" t="s">
-        <v>72</v>
+        <v>132</v>
       </c>
       <c r="D21" s="2"/>
       <c r="E21" s="3" t="s">
-        <v>70</v>
+        <v>67</v>
       </c>
       <c r="F21" s="3" t="s">
-        <v>79</v>
+        <v>92</v>
       </c>
       <c r="G21" s="13"/>
       <c r="H21" s="3"/>
       <c r="I21" s="3"/>
       <c r="J21" s="3"/>
     </row>
-    <row r="22" spans="1:10">
-      <c r="A22" s="33"/>
-      <c r="B22" s="30"/>
+    <row r="22" spans="1:10" ht="27">
+      <c r="A22" s="35"/>
+      <c r="B22" s="32"/>
       <c r="C22" s="14" t="s">
-        <v>93</v>
+        <v>72</v>
       </c>
       <c r="D22" s="2"/>
       <c r="E22" s="3" t="s">
-        <v>95</v>
+        <v>70</v>
       </c>
       <c r="F22" s="3" t="s">
-        <v>126</v>
+        <v>79</v>
       </c>
       <c r="G22" s="13"/>
       <c r="H22" s="3"/>
@@ -1608,17 +1612,17 @@
       <c r="J22" s="3"/>
     </row>
     <row r="23" spans="1:10">
-      <c r="A23" s="33"/>
-      <c r="B23" s="30"/>
+      <c r="A23" s="35"/>
+      <c r="B23" s="32"/>
       <c r="C23" s="14" t="s">
-        <v>71</v>
+        <v>93</v>
       </c>
       <c r="D23" s="2"/>
       <c r="E23" s="3" t="s">
-        <v>130</v>
+        <v>95</v>
       </c>
       <c r="F23" s="3" t="s">
-        <v>95</v>
+        <v>126</v>
       </c>
       <c r="G23" s="13"/>
       <c r="H23" s="3"/>
@@ -1626,28 +1630,28 @@
       <c r="J23" s="3"/>
     </row>
     <row r="24" spans="1:10">
-      <c r="A24" s="33"/>
-      <c r="B24" s="30"/>
+      <c r="A24" s="35"/>
+      <c r="B24" s="32"/>
       <c r="C24" s="14" t="s">
-        <v>27</v>
-      </c>
-      <c r="D24" s="3"/>
+        <v>71</v>
+      </c>
+      <c r="D24" s="2"/>
       <c r="E24" s="3" t="s">
-        <v>89</v>
+        <v>130</v>
       </c>
       <c r="F24" s="3" t="s">
-        <v>67</v>
-      </c>
-      <c r="G24" s="3"/>
+        <v>95</v>
+      </c>
+      <c r="G24" s="13"/>
       <c r="H24" s="3"/>
       <c r="I24" s="3"/>
       <c r="J24" s="3"/>
     </row>
     <row r="25" spans="1:10">
-      <c r="A25" s="33"/>
-      <c r="B25" s="30"/>
+      <c r="A25" s="35"/>
+      <c r="B25" s="32"/>
       <c r="C25" s="14" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="D25" s="3"/>
       <c r="E25" s="3" t="s">
@@ -1656,38 +1660,38 @@
       <c r="F25" s="3" t="s">
         <v>67</v>
       </c>
-      <c r="G25" s="7"/>
-      <c r="H25" s="8"/>
-      <c r="I25" s="8"/>
+      <c r="G25" s="3"/>
+      <c r="H25" s="3"/>
+      <c r="I25" s="3"/>
       <c r="J25" s="3"/>
     </row>
     <row r="26" spans="1:10">
-      <c r="A26" s="33"/>
-      <c r="B26" s="30"/>
+      <c r="A26" s="35"/>
+      <c r="B26" s="32"/>
       <c r="C26" s="14" t="s">
+        <v>28</v>
+      </c>
+      <c r="D26" s="3"/>
+      <c r="E26" s="3" t="s">
+        <v>89</v>
+      </c>
+      <c r="F26" s="3" t="s">
+        <v>67</v>
+      </c>
+      <c r="G26" s="7"/>
+      <c r="H26" s="8"/>
+      <c r="I26" s="8"/>
+      <c r="J26" s="3"/>
+    </row>
+    <row r="27" spans="1:10">
+      <c r="A27" s="35"/>
+      <c r="B27" s="32"/>
+      <c r="C27" s="14" t="s">
         <v>29</v>
-      </c>
-      <c r="D26" s="1"/>
-      <c r="E26" s="3" t="s">
-        <v>96</v>
-      </c>
-      <c r="F26" s="3" t="s">
-        <v>70</v>
-      </c>
-      <c r="G26" s="20"/>
-      <c r="H26" s="1"/>
-      <c r="I26" s="1"/>
-      <c r="J26" s="1"/>
-    </row>
-    <row r="27" spans="1:10">
-      <c r="A27" s="33"/>
-      <c r="B27" s="30"/>
-      <c r="C27" s="14" t="s">
-        <v>30</v>
       </c>
       <c r="D27" s="1"/>
       <c r="E27" s="3" t="s">
-        <v>81</v>
+        <v>96</v>
       </c>
       <c r="F27" s="3" t="s">
         <v>70</v>
@@ -1698,10 +1702,10 @@
       <c r="J27" s="1"/>
     </row>
     <row r="28" spans="1:10">
-      <c r="A28" s="33"/>
-      <c r="B28" s="30"/>
+      <c r="A28" s="35"/>
+      <c r="B28" s="32"/>
       <c r="C28" s="14" t="s">
-        <v>106</v>
+        <v>30</v>
       </c>
       <c r="D28" s="1"/>
       <c r="E28" s="3" t="s">
@@ -1716,36 +1720,34 @@
       <c r="J28" s="1"/>
     </row>
     <row r="29" spans="1:10">
-      <c r="A29" s="33"/>
-      <c r="B29" s="30"/>
+      <c r="A29" s="35"/>
+      <c r="B29" s="32"/>
       <c r="C29" s="14" t="s">
-        <v>82</v>
+        <v>106</v>
       </c>
       <c r="D29" s="1"/>
       <c r="E29" s="3" t="s">
-        <v>92</v>
+        <v>81</v>
       </c>
       <c r="F29" s="3" t="s">
-        <v>67</v>
+        <v>70</v>
       </c>
       <c r="G29" s="20"/>
       <c r="H29" s="1"/>
       <c r="I29" s="1"/>
       <c r="J29" s="1"/>
     </row>
-    <row r="30" spans="1:10" ht="27" customHeight="1">
-      <c r="A30" s="33"/>
-      <c r="B30" s="29" t="s">
-        <v>47</v>
-      </c>
-      <c r="C30" s="15" t="s">
-        <v>51</v>
+    <row r="30" spans="1:10">
+      <c r="A30" s="35"/>
+      <c r="B30" s="32"/>
+      <c r="C30" s="14" t="s">
+        <v>82</v>
       </c>
       <c r="D30" s="1"/>
       <c r="E30" s="3" t="s">
-        <v>89</v>
-      </c>
-      <c r="F30" s="1" t="s">
+        <v>92</v>
+      </c>
+      <c r="F30" s="3" t="s">
         <v>67</v>
       </c>
       <c r="G30" s="20"/>
@@ -1753,11 +1755,13 @@
       <c r="I30" s="1"/>
       <c r="J30" s="1"/>
     </row>
-    <row r="31" spans="1:10">
-      <c r="A31" s="33"/>
-      <c r="B31" s="29"/>
+    <row r="31" spans="1:10" ht="27" customHeight="1">
+      <c r="A31" s="35"/>
+      <c r="B31" s="31" t="s">
+        <v>47</v>
+      </c>
       <c r="C31" s="15" t="s">
-        <v>48</v>
+        <v>51</v>
       </c>
       <c r="D31" s="1"/>
       <c r="E31" s="3" t="s">
@@ -1772,10 +1776,10 @@
       <c r="J31" s="1"/>
     </row>
     <row r="32" spans="1:10">
-      <c r="A32" s="33"/>
-      <c r="B32" s="29"/>
+      <c r="A32" s="35"/>
+      <c r="B32" s="31"/>
       <c r="C32" s="15" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="D32" s="1"/>
       <c r="E32" s="3" t="s">
@@ -1790,17 +1794,17 @@
       <c r="J32" s="1"/>
     </row>
     <row r="33" spans="1:10">
-      <c r="A33" s="33"/>
-      <c r="B33" s="29"/>
+      <c r="A33" s="35"/>
+      <c r="B33" s="31"/>
       <c r="C33" s="15" t="s">
-        <v>59</v>
+        <v>49</v>
       </c>
       <c r="D33" s="1"/>
       <c r="E33" s="3" t="s">
-        <v>94</v>
+        <v>89</v>
       </c>
       <c r="F33" s="1" t="s">
-        <v>70</v>
+        <v>67</v>
       </c>
       <c r="G33" s="20"/>
       <c r="H33" s="1"/>
@@ -1808,17 +1812,17 @@
       <c r="J33" s="1"/>
     </row>
     <row r="34" spans="1:10">
-      <c r="A34" s="33"/>
-      <c r="B34" s="23"/>
+      <c r="A34" s="35"/>
+      <c r="B34" s="31"/>
       <c r="C34" s="15" t="s">
-        <v>127</v>
+        <v>59</v>
       </c>
       <c r="D34" s="1"/>
       <c r="E34" s="3" t="s">
         <v>94</v>
       </c>
       <c r="F34" s="1" t="s">
-        <v>128</v>
+        <v>70</v>
       </c>
       <c r="G34" s="20"/>
       <c r="H34" s="1"/>
@@ -1826,19 +1830,17 @@
       <c r="J34" s="1"/>
     </row>
     <row r="35" spans="1:10">
-      <c r="A35" s="33"/>
-      <c r="B35" s="30" t="s">
-        <v>50</v>
-      </c>
-      <c r="C35" s="14" t="s">
-        <v>57</v>
+      <c r="A35" s="35"/>
+      <c r="B35" s="23"/>
+      <c r="C35" s="15" t="s">
+        <v>127</v>
       </c>
       <c r="D35" s="1"/>
       <c r="E35" s="3" t="s">
-        <v>92</v>
+        <v>94</v>
       </c>
       <c r="F35" s="1" t="s">
-        <v>81</v>
+        <v>128</v>
       </c>
       <c r="G35" s="20"/>
       <c r="H35" s="1"/>
@@ -1846,17 +1848,19 @@
       <c r="J35" s="1"/>
     </row>
     <row r="36" spans="1:10">
-      <c r="A36" s="33"/>
-      <c r="B36" s="30"/>
+      <c r="A36" s="35"/>
+      <c r="B36" s="32" t="s">
+        <v>50</v>
+      </c>
       <c r="C36" s="14" t="s">
-        <v>86</v>
+        <v>57</v>
       </c>
       <c r="D36" s="1"/>
       <c r="E36" s="3" t="s">
         <v>92</v>
       </c>
       <c r="F36" s="1" t="s">
-        <v>87</v>
+        <v>81</v>
       </c>
       <c r="G36" s="20"/>
       <c r="H36" s="1"/>
@@ -1864,17 +1868,17 @@
       <c r="J36" s="1"/>
     </row>
     <row r="37" spans="1:10">
-      <c r="A37" s="33"/>
-      <c r="B37" s="30"/>
+      <c r="A37" s="35"/>
+      <c r="B37" s="32"/>
       <c r="C37" s="14" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="D37" s="1"/>
       <c r="E37" s="3" t="s">
         <v>92</v>
       </c>
       <c r="F37" s="1" t="s">
-        <v>89</v>
+        <v>87</v>
       </c>
       <c r="G37" s="20"/>
       <c r="H37" s="1"/>
@@ -1882,10 +1886,10 @@
       <c r="J37" s="1"/>
     </row>
     <row r="38" spans="1:10">
-      <c r="A38" s="33"/>
-      <c r="B38" s="30"/>
+      <c r="A38" s="35"/>
+      <c r="B38" s="32"/>
       <c r="C38" s="14" t="s">
-        <v>58</v>
+        <v>85</v>
       </c>
       <c r="D38" s="1"/>
       <c r="E38" s="3" t="s">
@@ -1900,19 +1904,17 @@
       <c r="J38" s="1"/>
     </row>
     <row r="39" spans="1:10">
-      <c r="A39" s="33"/>
-      <c r="B39" s="31" t="s">
-        <v>31</v>
-      </c>
-      <c r="C39" s="17" t="s">
-        <v>32</v>
+      <c r="A39" s="35"/>
+      <c r="B39" s="32"/>
+      <c r="C39" s="14" t="s">
+        <v>58</v>
       </c>
       <c r="D39" s="1"/>
       <c r="E39" s="3" t="s">
-        <v>81</v>
+        <v>92</v>
       </c>
       <c r="F39" s="1" t="s">
-        <v>67</v>
+        <v>89</v>
       </c>
       <c r="G39" s="20"/>
       <c r="H39" s="1"/>
@@ -1920,10 +1922,12 @@
       <c r="J39" s="1"/>
     </row>
     <row r="40" spans="1:10">
-      <c r="A40" s="33"/>
-      <c r="B40" s="31"/>
+      <c r="A40" s="35"/>
+      <c r="B40" s="33" t="s">
+        <v>31</v>
+      </c>
       <c r="C40" s="17" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="D40" s="1"/>
       <c r="E40" s="3" t="s">
@@ -1938,10 +1942,10 @@
       <c r="J40" s="1"/>
     </row>
     <row r="41" spans="1:10">
-      <c r="A41" s="33"/>
-      <c r="B41" s="31"/>
+      <c r="A41" s="35"/>
+      <c r="B41" s="33"/>
       <c r="C41" s="17" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="D41" s="1"/>
       <c r="E41" s="3" t="s">
@@ -1956,19 +1960,17 @@
       <c r="J41" s="1"/>
     </row>
     <row r="42" spans="1:10">
-      <c r="A42" s="33"/>
-      <c r="B42" s="30" t="s">
-        <v>35</v>
-      </c>
-      <c r="C42" s="14" t="s">
-        <v>73</v>
+      <c r="A42" s="35"/>
+      <c r="B42" s="33"/>
+      <c r="C42" s="17" t="s">
+        <v>34</v>
       </c>
       <c r="D42" s="1"/>
       <c r="E42" s="3" t="s">
-        <v>96</v>
+        <v>81</v>
       </c>
       <c r="F42" s="1" t="s">
-        <v>70</v>
+        <v>67</v>
       </c>
       <c r="G42" s="20"/>
       <c r="H42" s="1"/>
@@ -1976,10 +1978,12 @@
       <c r="J42" s="1"/>
     </row>
     <row r="43" spans="1:10">
-      <c r="A43" s="33"/>
-      <c r="B43" s="30"/>
+      <c r="A43" s="35"/>
+      <c r="B43" s="32" t="s">
+        <v>35</v>
+      </c>
       <c r="C43" s="14" t="s">
-        <v>36</v>
+        <v>73</v>
       </c>
       <c r="D43" s="1"/>
       <c r="E43" s="3" t="s">
@@ -1994,10 +1998,10 @@
       <c r="J43" s="1"/>
     </row>
     <row r="44" spans="1:10">
-      <c r="A44" s="33"/>
-      <c r="B44" s="30"/>
+      <c r="A44" s="35"/>
+      <c r="B44" s="32"/>
       <c r="C44" s="14" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="D44" s="1"/>
       <c r="E44" s="3" t="s">
@@ -2012,19 +2016,17 @@
       <c r="J44" s="1"/>
     </row>
     <row r="45" spans="1:10">
-      <c r="A45" s="33"/>
-      <c r="B45" s="31" t="s">
-        <v>38</v>
-      </c>
-      <c r="C45" s="17" t="s">
-        <v>99</v>
+      <c r="A45" s="35"/>
+      <c r="B45" s="32"/>
+      <c r="C45" s="14" t="s">
+        <v>37</v>
       </c>
       <c r="D45" s="1"/>
-      <c r="E45" s="24" t="s">
-        <v>94</v>
-      </c>
-      <c r="F45" s="25" t="s">
-        <v>100</v>
+      <c r="E45" s="3" t="s">
+        <v>96</v>
+      </c>
+      <c r="F45" s="1" t="s">
+        <v>70</v>
       </c>
       <c r="G45" s="20"/>
       <c r="H45" s="1"/>
@@ -2032,17 +2034,19 @@
       <c r="J45" s="1"/>
     </row>
     <row r="46" spans="1:10">
-      <c r="A46" s="33"/>
-      <c r="B46" s="31"/>
+      <c r="A46" s="35"/>
+      <c r="B46" s="33" t="s">
+        <v>38</v>
+      </c>
       <c r="C46" s="17" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="D46" s="1"/>
-      <c r="E46" s="3" t="s">
-        <v>69</v>
-      </c>
-      <c r="F46" s="24" t="s">
-        <v>89</v>
+      <c r="E46" s="24" t="s">
+        <v>94</v>
+      </c>
+      <c r="F46" s="25" t="s">
+        <v>100</v>
       </c>
       <c r="G46" s="20"/>
       <c r="H46" s="1"/>
@@ -2050,17 +2054,17 @@
       <c r="J46" s="1"/>
     </row>
     <row r="47" spans="1:10">
-      <c r="A47" s="33"/>
-      <c r="B47" s="31"/>
+      <c r="A47" s="35"/>
+      <c r="B47" s="33"/>
       <c r="C47" s="17" t="s">
-        <v>39</v>
+        <v>98</v>
       </c>
       <c r="D47" s="1"/>
       <c r="E47" s="3" t="s">
-        <v>91</v>
-      </c>
-      <c r="F47" s="1" t="s">
-        <v>129</v>
+        <v>69</v>
+      </c>
+      <c r="F47" s="24" t="s">
+        <v>89</v>
       </c>
       <c r="G47" s="20"/>
       <c r="H47" s="1"/>
@@ -2068,17 +2072,17 @@
       <c r="J47" s="1"/>
     </row>
     <row r="48" spans="1:10">
-      <c r="A48" s="33"/>
-      <c r="B48" s="31"/>
+      <c r="A48" s="35"/>
+      <c r="B48" s="33"/>
       <c r="C48" s="17" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="D48" s="1"/>
       <c r="E48" s="3" t="s">
-        <v>67</v>
+        <v>91</v>
       </c>
       <c r="F48" s="1" t="s">
-        <v>92</v>
+        <v>129</v>
       </c>
       <c r="G48" s="20"/>
       <c r="H48" s="1"/>
@@ -2086,17 +2090,17 @@
       <c r="J48" s="1"/>
     </row>
     <row r="49" spans="1:10">
-      <c r="A49" s="33"/>
-      <c r="B49" s="31"/>
+      <c r="A49" s="35"/>
+      <c r="B49" s="33"/>
       <c r="C49" s="17" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="D49" s="1"/>
       <c r="E49" s="3" t="s">
-        <v>70</v>
+        <v>67</v>
       </c>
       <c r="F49" s="1" t="s">
-        <v>88</v>
+        <v>92</v>
       </c>
       <c r="G49" s="20"/>
       <c r="H49" s="1"/>
@@ -2104,17 +2108,17 @@
       <c r="J49" s="1"/>
     </row>
     <row r="50" spans="1:10">
-      <c r="A50" s="33"/>
-      <c r="B50" s="31"/>
+      <c r="A50" s="35"/>
+      <c r="B50" s="33"/>
       <c r="C50" s="17" t="s">
-        <v>84</v>
+        <v>41</v>
       </c>
       <c r="D50" s="1"/>
       <c r="E50" s="3" t="s">
-        <v>92</v>
+        <v>70</v>
       </c>
       <c r="F50" s="1" t="s">
-        <v>97</v>
+        <v>88</v>
       </c>
       <c r="G50" s="20"/>
       <c r="H50" s="1"/>
@@ -2122,17 +2126,17 @@
       <c r="J50" s="1"/>
     </row>
     <row r="51" spans="1:10">
-      <c r="A51" s="33"/>
-      <c r="B51" s="31"/>
+      <c r="A51" s="35"/>
+      <c r="B51" s="33"/>
       <c r="C51" s="17" t="s">
-        <v>42</v>
+        <v>84</v>
       </c>
       <c r="D51" s="1"/>
       <c r="E51" s="3" t="s">
-        <v>89</v>
+        <v>92</v>
       </c>
       <c r="F51" s="1" t="s">
-        <v>123</v>
+        <v>97</v>
       </c>
       <c r="G51" s="20"/>
       <c r="H51" s="1"/>
@@ -2140,17 +2144,17 @@
       <c r="J51" s="1"/>
     </row>
     <row r="52" spans="1:10">
-      <c r="A52" s="33"/>
-      <c r="B52" s="31"/>
+      <c r="A52" s="35"/>
+      <c r="B52" s="33"/>
       <c r="C52" s="17" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="D52" s="1"/>
       <c r="E52" s="3" t="s">
-        <v>80</v>
+        <v>89</v>
       </c>
       <c r="F52" s="1" t="s">
-        <v>89</v>
+        <v>123</v>
       </c>
       <c r="G52" s="20"/>
       <c r="H52" s="1"/>
@@ -2158,21 +2162,17 @@
       <c r="J52" s="1"/>
     </row>
     <row r="53" spans="1:10">
-      <c r="A53" s="32" t="s">
-        <v>74</v>
-      </c>
-      <c r="B53" s="18" t="s">
-        <v>76</v>
-      </c>
-      <c r="C53" s="19" t="s">
-        <v>75</v>
+      <c r="A53" s="35"/>
+      <c r="B53" s="33"/>
+      <c r="C53" s="17" t="s">
+        <v>43</v>
       </c>
       <c r="D53" s="1"/>
       <c r="E53" s="3" t="s">
         <v>80</v>
       </c>
-      <c r="F53" s="3" t="s">
-        <v>67</v>
+      <c r="F53" s="1" t="s">
+        <v>89</v>
       </c>
       <c r="G53" s="20"/>
       <c r="H53" s="1"/>
@@ -2180,10 +2180,14 @@
       <c r="J53" s="1"/>
     </row>
     <row r="54" spans="1:10">
-      <c r="A54" s="32"/>
-      <c r="B54" s="18"/>
+      <c r="A54" s="34" t="s">
+        <v>74</v>
+      </c>
+      <c r="B54" s="18" t="s">
+        <v>76</v>
+      </c>
       <c r="C54" s="19" t="s">
-        <v>108</v>
+        <v>75</v>
       </c>
       <c r="D54" s="1"/>
       <c r="E54" s="3" t="s">
@@ -2198,10 +2202,10 @@
       <c r="J54" s="1"/>
     </row>
     <row r="55" spans="1:10">
-      <c r="A55" s="32"/>
+      <c r="A55" s="34"/>
       <c r="B55" s="18"/>
       <c r="C55" s="19" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="D55" s="1"/>
       <c r="E55" s="3" t="s">
@@ -2216,17 +2220,17 @@
       <c r="J55" s="1"/>
     </row>
     <row r="56" spans="1:10">
-      <c r="A56" s="32"/>
+      <c r="A56" s="34"/>
       <c r="B56" s="18"/>
       <c r="C56" s="19" t="s">
-        <v>83</v>
+        <v>107</v>
       </c>
       <c r="D56" s="1"/>
       <c r="E56" s="3" t="s">
         <v>80</v>
       </c>
-      <c r="F56" s="1" t="s">
-        <v>89</v>
+      <c r="F56" s="3" t="s">
+        <v>67</v>
       </c>
       <c r="G56" s="20"/>
       <c r="H56" s="1"/>
@@ -2234,14 +2238,14 @@
       <c r="J56" s="1"/>
     </row>
     <row r="57" spans="1:10">
-      <c r="A57" s="32"/>
+      <c r="A57" s="34"/>
       <c r="B57" s="18"/>
       <c r="C57" s="19" t="s">
-        <v>109</v>
+        <v>83</v>
       </c>
       <c r="D57" s="1"/>
       <c r="E57" s="3" t="s">
-        <v>67</v>
+        <v>80</v>
       </c>
       <c r="F57" s="1" t="s">
         <v>89</v>
@@ -2252,10 +2256,10 @@
       <c r="J57" s="1"/>
     </row>
     <row r="58" spans="1:10">
-      <c r="A58" s="32"/>
+      <c r="A58" s="34"/>
       <c r="B58" s="18"/>
       <c r="C58" s="19" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="D58" s="1"/>
       <c r="E58" s="3" t="s">
@@ -2269,17 +2273,15 @@
       <c r="I58" s="1"/>
       <c r="J58" s="1"/>
     </row>
-    <row r="59" spans="1:10" ht="27">
-      <c r="A59" s="32"/>
-      <c r="B59" s="18" t="s">
-        <v>111</v>
-      </c>
+    <row r="59" spans="1:10">
+      <c r="A59" s="34"/>
+      <c r="B59" s="18"/>
       <c r="C59" s="19" t="s">
-        <v>112</v>
+        <v>110</v>
       </c>
       <c r="D59" s="1"/>
       <c r="E59" s="3" t="s">
-        <v>80</v>
+        <v>67</v>
       </c>
       <c r="F59" s="1" t="s">
         <v>89</v>
@@ -2289,13 +2291,13 @@
       <c r="I59" s="1"/>
       <c r="J59" s="1"/>
     </row>
-    <row r="60" spans="1:10">
-      <c r="A60" s="32"/>
+    <row r="60" spans="1:10" ht="27">
+      <c r="A60" s="34"/>
       <c r="B60" s="18" t="s">
-        <v>113</v>
+        <v>111</v>
       </c>
       <c r="C60" s="19" t="s">
-        <v>114</v>
+        <v>112</v>
       </c>
       <c r="D60" s="1"/>
       <c r="E60" s="3" t="s">
@@ -2309,40 +2311,40 @@
       <c r="I60" s="1"/>
       <c r="J60" s="1"/>
     </row>
-    <row r="61" spans="1:10" ht="27">
-      <c r="A61" s="32"/>
+    <row r="61" spans="1:10">
+      <c r="A61" s="34"/>
       <c r="B61" s="18" t="s">
-        <v>115</v>
+        <v>113</v>
       </c>
       <c r="C61" s="19" t="s">
-        <v>116</v>
+        <v>114</v>
       </c>
       <c r="D61" s="1"/>
       <c r="E61" s="3" t="s">
         <v>80</v>
       </c>
       <c r="F61" s="1" t="s">
-        <v>67</v>
+        <v>89</v>
       </c>
       <c r="G61" s="20"/>
       <c r="H61" s="1"/>
       <c r="I61" s="1"/>
       <c r="J61" s="1"/>
     </row>
-    <row r="62" spans="1:10">
-      <c r="A62" s="32"/>
+    <row r="62" spans="1:10" ht="27">
+      <c r="A62" s="34"/>
       <c r="B62" s="18" t="s">
-        <v>117</v>
+        <v>115</v>
       </c>
       <c r="C62" s="19" t="s">
-        <v>118</v>
+        <v>116</v>
       </c>
       <c r="D62" s="1"/>
       <c r="E62" s="3" t="s">
-        <v>89</v>
+        <v>80</v>
       </c>
       <c r="F62" s="1" t="s">
-        <v>123</v>
+        <v>67</v>
       </c>
       <c r="G62" s="20"/>
       <c r="H62" s="1"/>
@@ -2350,19 +2352,19 @@
       <c r="J62" s="1"/>
     </row>
     <row r="63" spans="1:10">
-      <c r="A63" s="32"/>
+      <c r="A63" s="34"/>
       <c r="B63" s="18" t="s">
-        <v>77</v>
+        <v>117</v>
       </c>
       <c r="C63" s="19" t="s">
-        <v>78</v>
+        <v>118</v>
       </c>
       <c r="D63" s="1"/>
       <c r="E63" s="3" t="s">
         <v>89</v>
       </c>
       <c r="F63" s="1" t="s">
-        <v>80</v>
+        <v>123</v>
       </c>
       <c r="G63" s="20"/>
       <c r="H63" s="1"/>
@@ -2370,19 +2372,19 @@
       <c r="J63" s="1"/>
     </row>
     <row r="64" spans="1:10">
-      <c r="A64" s="32"/>
+      <c r="A64" s="34"/>
       <c r="B64" s="18" t="s">
-        <v>105</v>
+        <v>77</v>
       </c>
       <c r="C64" s="19" t="s">
-        <v>119</v>
+        <v>78</v>
       </c>
       <c r="D64" s="1"/>
       <c r="E64" s="3" t="s">
+        <v>89</v>
+      </c>
+      <c r="F64" s="1" t="s">
         <v>80</v>
-      </c>
-      <c r="F64" s="1" t="s">
-        <v>90</v>
       </c>
       <c r="G64" s="20"/>
       <c r="H64" s="1"/>
@@ -2390,17 +2392,19 @@
       <c r="J64" s="1"/>
     </row>
     <row r="65" spans="1:10">
-      <c r="A65" s="32"/>
-      <c r="B65" s="18"/>
+      <c r="A65" s="34"/>
+      <c r="B65" s="18" t="s">
+        <v>105</v>
+      </c>
       <c r="C65" s="19" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="D65" s="1"/>
       <c r="E65" s="3" t="s">
         <v>80</v>
       </c>
       <c r="F65" s="1" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="G65" s="20"/>
       <c r="H65" s="1"/>
@@ -2408,19 +2412,17 @@
       <c r="J65" s="1"/>
     </row>
     <row r="66" spans="1:10">
-      <c r="A66" s="32"/>
-      <c r="B66" s="18" t="s">
-        <v>101</v>
-      </c>
+      <c r="A66" s="34"/>
+      <c r="B66" s="18"/>
       <c r="C66" s="19" t="s">
-        <v>102</v>
+        <v>120</v>
       </c>
       <c r="D66" s="1"/>
       <c r="E66" s="3" t="s">
-        <v>67</v>
+        <v>80</v>
       </c>
       <c r="F66" s="1" t="s">
-        <v>80</v>
+        <v>89</v>
       </c>
       <c r="G66" s="20"/>
       <c r="H66" s="1"/>
@@ -2428,17 +2430,19 @@
       <c r="J66" s="1"/>
     </row>
     <row r="67" spans="1:10">
-      <c r="A67" s="32"/>
-      <c r="B67" s="18"/>
+      <c r="A67" s="34"/>
+      <c r="B67" s="18" t="s">
+        <v>101</v>
+      </c>
       <c r="C67" s="19" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="D67" s="1"/>
       <c r="E67" s="3" t="s">
+        <v>67</v>
+      </c>
+      <c r="F67" s="1" t="s">
         <v>80</v>
-      </c>
-      <c r="F67" s="3" t="s">
-        <v>89</v>
       </c>
       <c r="G67" s="20"/>
       <c r="H67" s="1"/>
@@ -2446,10 +2450,10 @@
       <c r="J67" s="1"/>
     </row>
     <row r="68" spans="1:10">
-      <c r="A68" s="32"/>
+      <c r="A68" s="34"/>
       <c r="B68" s="18"/>
       <c r="C68" s="19" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="D68" s="1"/>
       <c r="E68" s="3" t="s">
@@ -2464,19 +2468,17 @@
       <c r="J68" s="1"/>
     </row>
     <row r="69" spans="1:10">
-      <c r="A69" s="32"/>
-      <c r="B69" s="18" t="s">
-        <v>121</v>
-      </c>
+      <c r="A69" s="34"/>
+      <c r="B69" s="18"/>
       <c r="C69" s="19" t="s">
-        <v>122</v>
+        <v>104</v>
       </c>
       <c r="D69" s="1"/>
       <c r="E69" s="3" t="s">
+        <v>80</v>
+      </c>
+      <c r="F69" s="3" t="s">
         <v>89</v>
-      </c>
-      <c r="F69" s="1" t="s">
-        <v>67</v>
       </c>
       <c r="G69" s="20"/>
       <c r="H69" s="1"/>
@@ -2484,21 +2486,19 @@
       <c r="J69" s="1"/>
     </row>
     <row r="70" spans="1:10">
-      <c r="A70" s="27" t="s">
-        <v>64</v>
-      </c>
-      <c r="B70" s="28" t="s">
-        <v>65</v>
-      </c>
-      <c r="C70" s="22" t="s">
-        <v>44</v>
+      <c r="A70" s="34"/>
+      <c r="B70" s="18" t="s">
+        <v>121</v>
+      </c>
+      <c r="C70" s="19" t="s">
+        <v>122</v>
       </c>
       <c r="D70" s="1"/>
       <c r="E70" s="3" t="s">
-        <v>69</v>
+        <v>89</v>
       </c>
       <c r="F70" s="1" t="s">
-        <v>81</v>
+        <v>67</v>
       </c>
       <c r="G70" s="20"/>
       <c r="H70" s="1"/>
@@ -2506,17 +2506,21 @@
       <c r="J70" s="1"/>
     </row>
     <row r="71" spans="1:10">
-      <c r="A71" s="27"/>
-      <c r="B71" s="28"/>
+      <c r="A71" s="29" t="s">
+        <v>64</v>
+      </c>
+      <c r="B71" s="30" t="s">
+        <v>65</v>
+      </c>
       <c r="C71" s="22" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="D71" s="1"/>
       <c r="E71" s="3" t="s">
-        <v>67</v>
+        <v>69</v>
       </c>
       <c r="F71" s="1" t="s">
-        <v>89</v>
+        <v>81</v>
       </c>
       <c r="G71" s="20"/>
       <c r="H71" s="1"/>
@@ -2524,17 +2528,17 @@
       <c r="J71" s="1"/>
     </row>
     <row r="72" spans="1:10">
-      <c r="A72" s="27"/>
-      <c r="B72" s="28"/>
+      <c r="A72" s="29"/>
+      <c r="B72" s="30"/>
       <c r="C72" s="22" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="D72" s="1"/>
       <c r="E72" s="3" t="s">
-        <v>70</v>
+        <v>67</v>
       </c>
       <c r="F72" s="1" t="s">
-        <v>79</v>
+        <v>89</v>
       </c>
       <c r="G72" s="20"/>
       <c r="H72" s="1"/>
@@ -2542,17 +2546,17 @@
       <c r="J72" s="1"/>
     </row>
     <row r="73" spans="1:10">
-      <c r="A73" s="27"/>
-      <c r="B73" s="28"/>
+      <c r="A73" s="29"/>
+      <c r="B73" s="30"/>
       <c r="C73" s="22" t="s">
-        <v>124</v>
+        <v>46</v>
       </c>
       <c r="D73" s="1"/>
       <c r="E73" s="3" t="s">
-        <v>94</v>
+        <v>70</v>
       </c>
       <c r="F73" s="1" t="s">
-        <v>70</v>
+        <v>79</v>
       </c>
       <c r="G73" s="20"/>
       <c r="H73" s="1"/>
@@ -2560,17 +2564,17 @@
       <c r="J73" s="1"/>
     </row>
     <row r="74" spans="1:10">
-      <c r="A74" s="27"/>
-      <c r="B74" s="28"/>
+      <c r="A74" s="29"/>
+      <c r="B74" s="30"/>
       <c r="C74" s="22" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="D74" s="1"/>
       <c r="E74" s="3" t="s">
+        <v>94</v>
+      </c>
+      <c r="F74" s="1" t="s">
         <v>70</v>
-      </c>
-      <c r="F74" s="1" t="s">
-        <v>79</v>
       </c>
       <c r="G74" s="20"/>
       <c r="H74" s="1"/>
@@ -2578,56 +2582,74 @@
       <c r="J74" s="1"/>
     </row>
     <row r="75" spans="1:10">
-      <c r="A75" s="27"/>
-      <c r="B75" s="28"/>
+      <c r="A75" s="29"/>
+      <c r="B75" s="30"/>
       <c r="C75" s="22" t="s">
-        <v>60</v>
+        <v>125</v>
       </c>
       <c r="D75" s="1"/>
       <c r="E75" s="3" t="s">
-        <v>92</v>
+        <v>70</v>
       </c>
       <c r="F75" s="1" t="s">
-        <v>67</v>
+        <v>79</v>
       </c>
       <c r="G75" s="20"/>
       <c r="H75" s="1"/>
       <c r="I75" s="1"/>
       <c r="J75" s="1"/>
     </row>
-    <row r="76" spans="1:10" ht="36.75" customHeight="1">
-      <c r="A76" s="26"/>
-      <c r="B76" s="34" t="s">
-        <v>131</v>
-      </c>
-      <c r="C76" s="35"/>
-      <c r="D76" s="35"/>
-      <c r="E76" s="35"/>
+    <row r="76" spans="1:10">
+      <c r="A76" s="29"/>
+      <c r="B76" s="30"/>
+      <c r="C76" s="22" t="s">
+        <v>60</v>
+      </c>
+      <c r="D76" s="1"/>
+      <c r="E76" s="3" t="s">
+        <v>92</v>
+      </c>
+      <c r="F76" s="1" t="s">
+        <v>67</v>
+      </c>
       <c r="G76" s="20"/>
       <c r="H76" s="1"/>
       <c r="I76" s="1"/>
       <c r="J76" s="1"/>
     </row>
+    <row r="77" spans="1:10" ht="36.75" customHeight="1">
+      <c r="A77" s="26"/>
+      <c r="B77" s="27" t="s">
+        <v>131</v>
+      </c>
+      <c r="C77" s="28"/>
+      <c r="D77" s="28"/>
+      <c r="E77" s="28"/>
+      <c r="G77" s="20"/>
+      <c r="H77" s="1"/>
+      <c r="I77" s="1"/>
+      <c r="J77" s="1"/>
+    </row>
   </sheetData>
-  <autoFilter ref="B1:H75">
+  <autoFilter ref="B1:H76">
     <filterColumn colId="3"/>
     <filterColumn colId="5"/>
   </autoFilter>
   <mergeCells count="14">
-    <mergeCell ref="B76:E76"/>
-    <mergeCell ref="A70:A75"/>
-    <mergeCell ref="B70:B75"/>
-    <mergeCell ref="B30:B33"/>
-    <mergeCell ref="B35:B38"/>
     <mergeCell ref="B4:B10"/>
-    <mergeCell ref="A53:A69"/>
-    <mergeCell ref="A2:A52"/>
+    <mergeCell ref="A54:A70"/>
+    <mergeCell ref="A2:A53"/>
     <mergeCell ref="B11:B14"/>
     <mergeCell ref="B15:B19"/>
-    <mergeCell ref="B20:B29"/>
-    <mergeCell ref="B39:B41"/>
-    <mergeCell ref="B42:B44"/>
-    <mergeCell ref="B45:B52"/>
+    <mergeCell ref="B20:B30"/>
+    <mergeCell ref="B40:B42"/>
+    <mergeCell ref="B43:B45"/>
+    <mergeCell ref="B46:B53"/>
+    <mergeCell ref="B77:E77"/>
+    <mergeCell ref="A71:A76"/>
+    <mergeCell ref="B71:B76"/>
+    <mergeCell ref="B31:B34"/>
+    <mergeCell ref="B36:B39"/>
   </mergeCells>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/internal_doc/05.测试设计/特性守护矩阵.xlsx
+++ b/internal_doc/05.测试设计/特性守护矩阵.xlsx
@@ -19,7 +19,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="260" uniqueCount="133">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="260" uniqueCount="134">
   <si>
     <t>优先级</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -552,6 +552,10 @@
   <si>
     <t>索引管理（idindex、index）</t>
     <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
+    <t>陈仲文</t>
+    <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
 </file>
@@ -788,6 +792,18 @@
     <xf numFmtId="0" fontId="0" fillId="7" borderId="0" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="9" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -799,18 +815,6 @@
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="8" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="9" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -1220,7 +1224,7 @@
       </c>
     </row>
     <row r="2" spans="1:10">
-      <c r="A2" s="35" t="s">
+      <c r="A2" s="29" t="s">
         <v>63</v>
       </c>
       <c r="B2" s="16" t="s">
@@ -1242,7 +1246,7 @@
       <c r="J2" s="3"/>
     </row>
     <row r="3" spans="1:10">
-      <c r="A3" s="35"/>
+      <c r="A3" s="29"/>
       <c r="B3" s="21" t="s">
         <v>12</v>
       </c>
@@ -1262,8 +1266,8 @@
       <c r="J3" s="3"/>
     </row>
     <row r="4" spans="1:10" ht="27" customHeight="1">
-      <c r="A4" s="35"/>
-      <c r="B4" s="33" t="s">
+      <c r="A4" s="29"/>
+      <c r="B4" s="27" t="s">
         <v>68</v>
       </c>
       <c r="C4" s="17" t="s">
@@ -1282,8 +1286,8 @@
       <c r="J4" s="3"/>
     </row>
     <row r="5" spans="1:10">
-      <c r="A5" s="35"/>
-      <c r="B5" s="33"/>
+      <c r="A5" s="29"/>
+      <c r="B5" s="27"/>
       <c r="C5" s="17" t="s">
         <v>14</v>
       </c>
@@ -1300,8 +1304,8 @@
       <c r="J5" s="3"/>
     </row>
     <row r="6" spans="1:10">
-      <c r="A6" s="35"/>
-      <c r="B6" s="33"/>
+      <c r="A6" s="29"/>
+      <c r="B6" s="27"/>
       <c r="C6" s="17" t="s">
         <v>15</v>
       </c>
@@ -1318,8 +1322,8 @@
       <c r="J6" s="3"/>
     </row>
     <row r="7" spans="1:10">
-      <c r="A7" s="35"/>
-      <c r="B7" s="33"/>
+      <c r="A7" s="29"/>
+      <c r="B7" s="27"/>
       <c r="C7" s="17" t="s">
         <v>16</v>
       </c>
@@ -1336,8 +1340,8 @@
       <c r="J7" s="3"/>
     </row>
     <row r="8" spans="1:10">
-      <c r="A8" s="35"/>
-      <c r="B8" s="33"/>
+      <c r="A8" s="29"/>
+      <c r="B8" s="27"/>
       <c r="C8" s="17" t="s">
         <v>53</v>
       </c>
@@ -1354,8 +1358,8 @@
       <c r="J8" s="3"/>
     </row>
     <row r="9" spans="1:10">
-      <c r="A9" s="35"/>
-      <c r="B9" s="33"/>
+      <c r="A9" s="29"/>
+      <c r="B9" s="27"/>
       <c r="C9" s="17" t="s">
         <v>17</v>
       </c>
@@ -1372,8 +1376,8 @@
       <c r="J9" s="3"/>
     </row>
     <row r="10" spans="1:10">
-      <c r="A10" s="35"/>
-      <c r="B10" s="33"/>
+      <c r="A10" s="29"/>
+      <c r="B10" s="27"/>
       <c r="C10" s="17" t="s">
         <v>18</v>
       </c>
@@ -1390,8 +1394,8 @@
       <c r="J10" s="3"/>
     </row>
     <row r="11" spans="1:10">
-      <c r="A11" s="35"/>
-      <c r="B11" s="32" t="s">
+      <c r="A11" s="29"/>
+      <c r="B11" s="30" t="s">
         <v>19</v>
       </c>
       <c r="C11" s="14" t="s">
@@ -1410,8 +1414,8 @@
       <c r="J11" s="3"/>
     </row>
     <row r="12" spans="1:10">
-      <c r="A12" s="35"/>
-      <c r="B12" s="32"/>
+      <c r="A12" s="29"/>
+      <c r="B12" s="30"/>
       <c r="C12" s="14" t="s">
         <v>54</v>
       </c>
@@ -1428,8 +1432,8 @@
       <c r="J12" s="3"/>
     </row>
     <row r="13" spans="1:10">
-      <c r="A13" s="35"/>
-      <c r="B13" s="32"/>
+      <c r="A13" s="29"/>
+      <c r="B13" s="30"/>
       <c r="C13" s="14" t="s">
         <v>55</v>
       </c>
@@ -1446,8 +1450,8 @@
       <c r="J13" s="3"/>
     </row>
     <row r="14" spans="1:10">
-      <c r="A14" s="35"/>
-      <c r="B14" s="32"/>
+      <c r="A14" s="29"/>
+      <c r="B14" s="30"/>
       <c r="C14" s="14" t="s">
         <v>56</v>
       </c>
@@ -1464,8 +1468,8 @@
       <c r="J14" s="3"/>
     </row>
     <row r="15" spans="1:10">
-      <c r="A15" s="35"/>
-      <c r="B15" s="33" t="s">
+      <c r="A15" s="29"/>
+      <c r="B15" s="27" t="s">
         <v>21</v>
       </c>
       <c r="C15" s="17" t="s">
@@ -1484,8 +1488,8 @@
       <c r="J15" s="3"/>
     </row>
     <row r="16" spans="1:10">
-      <c r="A16" s="35"/>
-      <c r="B16" s="33"/>
+      <c r="A16" s="29"/>
+      <c r="B16" s="27"/>
       <c r="C16" s="17" t="s">
         <v>62</v>
       </c>
@@ -1502,8 +1506,8 @@
       <c r="J16" s="3"/>
     </row>
     <row r="17" spans="1:10">
-      <c r="A17" s="35"/>
-      <c r="B17" s="33"/>
+      <c r="A17" s="29"/>
+      <c r="B17" s="27"/>
       <c r="C17" s="17" t="s">
         <v>23</v>
       </c>
@@ -1520,8 +1524,8 @@
       <c r="J17" s="3"/>
     </row>
     <row r="18" spans="1:10">
-      <c r="A18" s="35"/>
-      <c r="B18" s="33"/>
+      <c r="A18" s="29"/>
+      <c r="B18" s="27"/>
       <c r="C18" s="17" t="s">
         <v>24</v>
       </c>
@@ -1538,8 +1542,8 @@
       <c r="J18" s="3"/>
     </row>
     <row r="19" spans="1:10">
-      <c r="A19" s="35"/>
-      <c r="B19" s="33"/>
+      <c r="A19" s="29"/>
+      <c r="B19" s="27"/>
       <c r="C19" s="17" t="s">
         <v>25</v>
       </c>
@@ -1556,8 +1560,8 @@
       <c r="J19" s="3"/>
     </row>
     <row r="20" spans="1:10" ht="27">
-      <c r="A20" s="35"/>
-      <c r="B20" s="32" t="s">
+      <c r="A20" s="29"/>
+      <c r="B20" s="30" t="s">
         <v>26</v>
       </c>
       <c r="C20" s="14" t="s">
@@ -1576,8 +1580,8 @@
       <c r="J20" s="3"/>
     </row>
     <row r="21" spans="1:10">
-      <c r="A21" s="35"/>
-      <c r="B21" s="32"/>
+      <c r="A21" s="29"/>
+      <c r="B21" s="30"/>
       <c r="C21" s="14" t="s">
         <v>132</v>
       </c>
@@ -1594,8 +1598,8 @@
       <c r="J21" s="3"/>
     </row>
     <row r="22" spans="1:10" ht="27">
-      <c r="A22" s="35"/>
-      <c r="B22" s="32"/>
+      <c r="A22" s="29"/>
+      <c r="B22" s="30"/>
       <c r="C22" s="14" t="s">
         <v>72</v>
       </c>
@@ -1612,8 +1616,8 @@
       <c r="J22" s="3"/>
     </row>
     <row r="23" spans="1:10">
-      <c r="A23" s="35"/>
-      <c r="B23" s="32"/>
+      <c r="A23" s="29"/>
+      <c r="B23" s="30"/>
       <c r="C23" s="14" t="s">
         <v>93</v>
       </c>
@@ -1630,8 +1634,8 @@
       <c r="J23" s="3"/>
     </row>
     <row r="24" spans="1:10">
-      <c r="A24" s="35"/>
-      <c r="B24" s="32"/>
+      <c r="A24" s="29"/>
+      <c r="B24" s="30"/>
       <c r="C24" s="14" t="s">
         <v>71</v>
       </c>
@@ -1648,8 +1652,8 @@
       <c r="J24" s="3"/>
     </row>
     <row r="25" spans="1:10">
-      <c r="A25" s="35"/>
-      <c r="B25" s="32"/>
+      <c r="A25" s="29"/>
+      <c r="B25" s="30"/>
       <c r="C25" s="14" t="s">
         <v>27</v>
       </c>
@@ -1666,8 +1670,8 @@
       <c r="J25" s="3"/>
     </row>
     <row r="26" spans="1:10">
-      <c r="A26" s="35"/>
-      <c r="B26" s="32"/>
+      <c r="A26" s="29"/>
+      <c r="B26" s="30"/>
       <c r="C26" s="14" t="s">
         <v>28</v>
       </c>
@@ -1684,8 +1688,8 @@
       <c r="J26" s="3"/>
     </row>
     <row r="27" spans="1:10">
-      <c r="A27" s="35"/>
-      <c r="B27" s="32"/>
+      <c r="A27" s="29"/>
+      <c r="B27" s="30"/>
       <c r="C27" s="14" t="s">
         <v>29</v>
       </c>
@@ -1702,8 +1706,8 @@
       <c r="J27" s="1"/>
     </row>
     <row r="28" spans="1:10">
-      <c r="A28" s="35"/>
-      <c r="B28" s="32"/>
+      <c r="A28" s="29"/>
+      <c r="B28" s="30"/>
       <c r="C28" s="14" t="s">
         <v>30</v>
       </c>
@@ -1720,8 +1724,8 @@
       <c r="J28" s="1"/>
     </row>
     <row r="29" spans="1:10">
-      <c r="A29" s="35"/>
-      <c r="B29" s="32"/>
+      <c r="A29" s="29"/>
+      <c r="B29" s="30"/>
       <c r="C29" s="14" t="s">
         <v>106</v>
       </c>
@@ -1738,8 +1742,8 @@
       <c r="J29" s="1"/>
     </row>
     <row r="30" spans="1:10">
-      <c r="A30" s="35"/>
-      <c r="B30" s="32"/>
+      <c r="A30" s="29"/>
+      <c r="B30" s="30"/>
       <c r="C30" s="14" t="s">
         <v>82</v>
       </c>
@@ -1756,8 +1760,8 @@
       <c r="J30" s="1"/>
     </row>
     <row r="31" spans="1:10" ht="27" customHeight="1">
-      <c r="A31" s="35"/>
-      <c r="B31" s="31" t="s">
+      <c r="A31" s="29"/>
+      <c r="B31" s="35" t="s">
         <v>47</v>
       </c>
       <c r="C31" s="15" t="s">
@@ -1776,8 +1780,8 @@
       <c r="J31" s="1"/>
     </row>
     <row r="32" spans="1:10">
-      <c r="A32" s="35"/>
-      <c r="B32" s="31"/>
+      <c r="A32" s="29"/>
+      <c r="B32" s="35"/>
       <c r="C32" s="15" t="s">
         <v>48</v>
       </c>
@@ -1794,8 +1798,8 @@
       <c r="J32" s="1"/>
     </row>
     <row r="33" spans="1:10">
-      <c r="A33" s="35"/>
-      <c r="B33" s="31"/>
+      <c r="A33" s="29"/>
+      <c r="B33" s="35"/>
       <c r="C33" s="15" t="s">
         <v>49</v>
       </c>
@@ -1812,8 +1816,8 @@
       <c r="J33" s="1"/>
     </row>
     <row r="34" spans="1:10">
-      <c r="A34" s="35"/>
-      <c r="B34" s="31"/>
+      <c r="A34" s="29"/>
+      <c r="B34" s="35"/>
       <c r="C34" s="15" t="s">
         <v>59</v>
       </c>
@@ -1830,7 +1834,7 @@
       <c r="J34" s="1"/>
     </row>
     <row r="35" spans="1:10">
-      <c r="A35" s="35"/>
+      <c r="A35" s="29"/>
       <c r="B35" s="23"/>
       <c r="C35" s="15" t="s">
         <v>127</v>
@@ -1848,8 +1852,8 @@
       <c r="J35" s="1"/>
     </row>
     <row r="36" spans="1:10">
-      <c r="A36" s="35"/>
-      <c r="B36" s="32" t="s">
+      <c r="A36" s="29"/>
+      <c r="B36" s="30" t="s">
         <v>50</v>
       </c>
       <c r="C36" s="14" t="s">
@@ -1868,8 +1872,8 @@
       <c r="J36" s="1"/>
     </row>
     <row r="37" spans="1:10">
-      <c r="A37" s="35"/>
-      <c r="B37" s="32"/>
+      <c r="A37" s="29"/>
+      <c r="B37" s="30"/>
       <c r="C37" s="14" t="s">
         <v>86</v>
       </c>
@@ -1886,8 +1890,8 @@
       <c r="J37" s="1"/>
     </row>
     <row r="38" spans="1:10">
-      <c r="A38" s="35"/>
-      <c r="B38" s="32"/>
+      <c r="A38" s="29"/>
+      <c r="B38" s="30"/>
       <c r="C38" s="14" t="s">
         <v>85</v>
       </c>
@@ -1904,8 +1908,8 @@
       <c r="J38" s="1"/>
     </row>
     <row r="39" spans="1:10">
-      <c r="A39" s="35"/>
-      <c r="B39" s="32"/>
+      <c r="A39" s="29"/>
+      <c r="B39" s="30"/>
       <c r="C39" s="14" t="s">
         <v>58</v>
       </c>
@@ -1922,8 +1926,8 @@
       <c r="J39" s="1"/>
     </row>
     <row r="40" spans="1:10">
-      <c r="A40" s="35"/>
-      <c r="B40" s="33" t="s">
+      <c r="A40" s="29"/>
+      <c r="B40" s="27" t="s">
         <v>31</v>
       </c>
       <c r="C40" s="17" t="s">
@@ -1942,8 +1946,8 @@
       <c r="J40" s="1"/>
     </row>
     <row r="41" spans="1:10">
-      <c r="A41" s="35"/>
-      <c r="B41" s="33"/>
+      <c r="A41" s="29"/>
+      <c r="B41" s="27"/>
       <c r="C41" s="17" t="s">
         <v>33</v>
       </c>
@@ -1960,8 +1964,8 @@
       <c r="J41" s="1"/>
     </row>
     <row r="42" spans="1:10">
-      <c r="A42" s="35"/>
-      <c r="B42" s="33"/>
+      <c r="A42" s="29"/>
+      <c r="B42" s="27"/>
       <c r="C42" s="17" t="s">
         <v>34</v>
       </c>
@@ -1978,8 +1982,8 @@
       <c r="J42" s="1"/>
     </row>
     <row r="43" spans="1:10">
-      <c r="A43" s="35"/>
-      <c r="B43" s="32" t="s">
+      <c r="A43" s="29"/>
+      <c r="B43" s="30" t="s">
         <v>35</v>
       </c>
       <c r="C43" s="14" t="s">
@@ -1998,8 +2002,8 @@
       <c r="J43" s="1"/>
     </row>
     <row r="44" spans="1:10">
-      <c r="A44" s="35"/>
-      <c r="B44" s="32"/>
+      <c r="A44" s="29"/>
+      <c r="B44" s="30"/>
       <c r="C44" s="14" t="s">
         <v>36</v>
       </c>
@@ -2016,8 +2020,8 @@
       <c r="J44" s="1"/>
     </row>
     <row r="45" spans="1:10">
-      <c r="A45" s="35"/>
-      <c r="B45" s="32"/>
+      <c r="A45" s="29"/>
+      <c r="B45" s="30"/>
       <c r="C45" s="14" t="s">
         <v>37</v>
       </c>
@@ -2034,8 +2038,8 @@
       <c r="J45" s="1"/>
     </row>
     <row r="46" spans="1:10">
-      <c r="A46" s="35"/>
-      <c r="B46" s="33" t="s">
+      <c r="A46" s="29"/>
+      <c r="B46" s="27" t="s">
         <v>38</v>
       </c>
       <c r="C46" s="17" t="s">
@@ -2054,8 +2058,8 @@
       <c r="J46" s="1"/>
     </row>
     <row r="47" spans="1:10">
-      <c r="A47" s="35"/>
-      <c r="B47" s="33"/>
+      <c r="A47" s="29"/>
+      <c r="B47" s="27"/>
       <c r="C47" s="17" t="s">
         <v>98</v>
       </c>
@@ -2064,7 +2068,7 @@
         <v>69</v>
       </c>
       <c r="F47" s="24" t="s">
-        <v>89</v>
+        <v>133</v>
       </c>
       <c r="G47" s="20"/>
       <c r="H47" s="1"/>
@@ -2072,8 +2076,8 @@
       <c r="J47" s="1"/>
     </row>
     <row r="48" spans="1:10">
-      <c r="A48" s="35"/>
-      <c r="B48" s="33"/>
+      <c r="A48" s="29"/>
+      <c r="B48" s="27"/>
       <c r="C48" s="17" t="s">
         <v>39</v>
       </c>
@@ -2090,8 +2094,8 @@
       <c r="J48" s="1"/>
     </row>
     <row r="49" spans="1:10">
-      <c r="A49" s="35"/>
-      <c r="B49" s="33"/>
+      <c r="A49" s="29"/>
+      <c r="B49" s="27"/>
       <c r="C49" s="17" t="s">
         <v>40</v>
       </c>
@@ -2108,8 +2112,8 @@
       <c r="J49" s="1"/>
     </row>
     <row r="50" spans="1:10">
-      <c r="A50" s="35"/>
-      <c r="B50" s="33"/>
+      <c r="A50" s="29"/>
+      <c r="B50" s="27"/>
       <c r="C50" s="17" t="s">
         <v>41</v>
       </c>
@@ -2126,8 +2130,8 @@
       <c r="J50" s="1"/>
     </row>
     <row r="51" spans="1:10">
-      <c r="A51" s="35"/>
-      <c r="B51" s="33"/>
+      <c r="A51" s="29"/>
+      <c r="B51" s="27"/>
       <c r="C51" s="17" t="s">
         <v>84</v>
       </c>
@@ -2144,8 +2148,8 @@
       <c r="J51" s="1"/>
     </row>
     <row r="52" spans="1:10">
-      <c r="A52" s="35"/>
-      <c r="B52" s="33"/>
+      <c r="A52" s="29"/>
+      <c r="B52" s="27"/>
       <c r="C52" s="17" t="s">
         <v>42</v>
       </c>
@@ -2162,8 +2166,8 @@
       <c r="J52" s="1"/>
     </row>
     <row r="53" spans="1:10">
-      <c r="A53" s="35"/>
-      <c r="B53" s="33"/>
+      <c r="A53" s="29"/>
+      <c r="B53" s="27"/>
       <c r="C53" s="17" t="s">
         <v>43</v>
       </c>
@@ -2180,7 +2184,7 @@
       <c r="J53" s="1"/>
     </row>
     <row r="54" spans="1:10">
-      <c r="A54" s="34" t="s">
+      <c r="A54" s="28" t="s">
         <v>74</v>
       </c>
       <c r="B54" s="18" t="s">
@@ -2202,7 +2206,7 @@
       <c r="J54" s="1"/>
     </row>
     <row r="55" spans="1:10">
-      <c r="A55" s="34"/>
+      <c r="A55" s="28"/>
       <c r="B55" s="18"/>
       <c r="C55" s="19" t="s">
         <v>108</v>
@@ -2220,7 +2224,7 @@
       <c r="J55" s="1"/>
     </row>
     <row r="56" spans="1:10">
-      <c r="A56" s="34"/>
+      <c r="A56" s="28"/>
       <c r="B56" s="18"/>
       <c r="C56" s="19" t="s">
         <v>107</v>
@@ -2238,7 +2242,7 @@
       <c r="J56" s="1"/>
     </row>
     <row r="57" spans="1:10">
-      <c r="A57" s="34"/>
+      <c r="A57" s="28"/>
       <c r="B57" s="18"/>
       <c r="C57" s="19" t="s">
         <v>83</v>
@@ -2256,7 +2260,7 @@
       <c r="J57" s="1"/>
     </row>
     <row r="58" spans="1:10">
-      <c r="A58" s="34"/>
+      <c r="A58" s="28"/>
       <c r="B58" s="18"/>
       <c r="C58" s="19" t="s">
         <v>109</v>
@@ -2274,7 +2278,7 @@
       <c r="J58" s="1"/>
     </row>
     <row r="59" spans="1:10">
-      <c r="A59" s="34"/>
+      <c r="A59" s="28"/>
       <c r="B59" s="18"/>
       <c r="C59" s="19" t="s">
         <v>110</v>
@@ -2292,7 +2296,7 @@
       <c r="J59" s="1"/>
     </row>
     <row r="60" spans="1:10" ht="27">
-      <c r="A60" s="34"/>
+      <c r="A60" s="28"/>
       <c r="B60" s="18" t="s">
         <v>111</v>
       </c>
@@ -2312,7 +2316,7 @@
       <c r="J60" s="1"/>
     </row>
     <row r="61" spans="1:10">
-      <c r="A61" s="34"/>
+      <c r="A61" s="28"/>
       <c r="B61" s="18" t="s">
         <v>113</v>
       </c>
@@ -2332,7 +2336,7 @@
       <c r="J61" s="1"/>
     </row>
     <row r="62" spans="1:10" ht="27">
-      <c r="A62" s="34"/>
+      <c r="A62" s="28"/>
       <c r="B62" s="18" t="s">
         <v>115</v>
       </c>
@@ -2352,7 +2356,7 @@
       <c r="J62" s="1"/>
     </row>
     <row r="63" spans="1:10">
-      <c r="A63" s="34"/>
+      <c r="A63" s="28"/>
       <c r="B63" s="18" t="s">
         <v>117</v>
       </c>
@@ -2372,7 +2376,7 @@
       <c r="J63" s="1"/>
     </row>
     <row r="64" spans="1:10">
-      <c r="A64" s="34"/>
+      <c r="A64" s="28"/>
       <c r="B64" s="18" t="s">
         <v>77</v>
       </c>
@@ -2392,7 +2396,7 @@
       <c r="J64" s="1"/>
     </row>
     <row r="65" spans="1:10">
-      <c r="A65" s="34"/>
+      <c r="A65" s="28"/>
       <c r="B65" s="18" t="s">
         <v>105</v>
       </c>
@@ -2412,7 +2416,7 @@
       <c r="J65" s="1"/>
     </row>
     <row r="66" spans="1:10">
-      <c r="A66" s="34"/>
+      <c r="A66" s="28"/>
       <c r="B66" s="18"/>
       <c r="C66" s="19" t="s">
         <v>120</v>
@@ -2430,7 +2434,7 @@
       <c r="J66" s="1"/>
     </row>
     <row r="67" spans="1:10">
-      <c r="A67" s="34"/>
+      <c r="A67" s="28"/>
       <c r="B67" s="18" t="s">
         <v>101</v>
       </c>
@@ -2450,7 +2454,7 @@
       <c r="J67" s="1"/>
     </row>
     <row r="68" spans="1:10">
-      <c r="A68" s="34"/>
+      <c r="A68" s="28"/>
       <c r="B68" s="18"/>
       <c r="C68" s="19" t="s">
         <v>103</v>
@@ -2468,7 +2472,7 @@
       <c r="J68" s="1"/>
     </row>
     <row r="69" spans="1:10">
-      <c r="A69" s="34"/>
+      <c r="A69" s="28"/>
       <c r="B69" s="18"/>
       <c r="C69" s="19" t="s">
         <v>104</v>
@@ -2486,7 +2490,7 @@
       <c r="J69" s="1"/>
     </row>
     <row r="70" spans="1:10">
-      <c r="A70" s="34"/>
+      <c r="A70" s="28"/>
       <c r="B70" s="18" t="s">
         <v>121</v>
       </c>
@@ -2506,10 +2510,10 @@
       <c r="J70" s="1"/>
     </row>
     <row r="71" spans="1:10">
-      <c r="A71" s="29" t="s">
+      <c r="A71" s="33" t="s">
         <v>64</v>
       </c>
-      <c r="B71" s="30" t="s">
+      <c r="B71" s="34" t="s">
         <v>65</v>
       </c>
       <c r="C71" s="22" t="s">
@@ -2528,8 +2532,8 @@
       <c r="J71" s="1"/>
     </row>
     <row r="72" spans="1:10">
-      <c r="A72" s="29"/>
-      <c r="B72" s="30"/>
+      <c r="A72" s="33"/>
+      <c r="B72" s="34"/>
       <c r="C72" s="22" t="s">
         <v>45</v>
       </c>
@@ -2546,8 +2550,8 @@
       <c r="J72" s="1"/>
     </row>
     <row r="73" spans="1:10">
-      <c r="A73" s="29"/>
-      <c r="B73" s="30"/>
+      <c r="A73" s="33"/>
+      <c r="B73" s="34"/>
       <c r="C73" s="22" t="s">
         <v>46</v>
       </c>
@@ -2564,8 +2568,8 @@
       <c r="J73" s="1"/>
     </row>
     <row r="74" spans="1:10">
-      <c r="A74" s="29"/>
-      <c r="B74" s="30"/>
+      <c r="A74" s="33"/>
+      <c r="B74" s="34"/>
       <c r="C74" s="22" t="s">
         <v>124</v>
       </c>
@@ -2582,8 +2586,8 @@
       <c r="J74" s="1"/>
     </row>
     <row r="75" spans="1:10">
-      <c r="A75" s="29"/>
-      <c r="B75" s="30"/>
+      <c r="A75" s="33"/>
+      <c r="B75" s="34"/>
       <c r="C75" s="22" t="s">
         <v>125</v>
       </c>
@@ -2600,8 +2604,8 @@
       <c r="J75" s="1"/>
     </row>
     <row r="76" spans="1:10">
-      <c r="A76" s="29"/>
-      <c r="B76" s="30"/>
+      <c r="A76" s="33"/>
+      <c r="B76" s="34"/>
       <c r="C76" s="22" t="s">
         <v>60</v>
       </c>
@@ -2619,12 +2623,12 @@
     </row>
     <row r="77" spans="1:10" ht="36.75" customHeight="1">
       <c r="A77" s="26"/>
-      <c r="B77" s="27" t="s">
+      <c r="B77" s="31" t="s">
         <v>131</v>
       </c>
-      <c r="C77" s="28"/>
-      <c r="D77" s="28"/>
-      <c r="E77" s="28"/>
+      <c r="C77" s="32"/>
+      <c r="D77" s="32"/>
+      <c r="E77" s="32"/>
       <c r="G77" s="20"/>
       <c r="H77" s="1"/>
       <c r="I77" s="1"/>
@@ -2636,6 +2640,11 @@
     <filterColumn colId="5"/>
   </autoFilter>
   <mergeCells count="14">
+    <mergeCell ref="B77:E77"/>
+    <mergeCell ref="A71:A76"/>
+    <mergeCell ref="B71:B76"/>
+    <mergeCell ref="B31:B34"/>
+    <mergeCell ref="B36:B39"/>
     <mergeCell ref="B4:B10"/>
     <mergeCell ref="A54:A70"/>
     <mergeCell ref="A2:A53"/>
@@ -2645,11 +2654,6 @@
     <mergeCell ref="B40:B42"/>
     <mergeCell ref="B43:B45"/>
     <mergeCell ref="B46:B53"/>
-    <mergeCell ref="B77:E77"/>
-    <mergeCell ref="A71:A76"/>
-    <mergeCell ref="B71:B76"/>
-    <mergeCell ref="B31:B34"/>
-    <mergeCell ref="B36:B39"/>
   </mergeCells>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/internal_doc/05.测试设计/特性守护矩阵.xlsx
+++ b/internal_doc/05.测试设计/特性守护矩阵.xlsx
@@ -19,7 +19,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="260" uniqueCount="134">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="260" uniqueCount="133">
   <si>
     <t>优先级</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -552,10 +552,6 @@
   <si>
     <t>索引管理（idindex、index）</t>
     <phoneticPr fontId="8" type="noConversion"/>
-  </si>
-  <si>
-    <t>陈仲文</t>
-    <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
 </file>
@@ -792,18 +788,6 @@
     <xf numFmtId="0" fontId="0" fillId="7" borderId="0" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="9" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -815,6 +799,18 @@
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="8" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="9" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -1224,7 +1220,7 @@
       </c>
     </row>
     <row r="2" spans="1:10">
-      <c r="A2" s="29" t="s">
+      <c r="A2" s="35" t="s">
         <v>63</v>
       </c>
       <c r="B2" s="16" t="s">
@@ -1246,7 +1242,7 @@
       <c r="J2" s="3"/>
     </row>
     <row r="3" spans="1:10">
-      <c r="A3" s="29"/>
+      <c r="A3" s="35"/>
       <c r="B3" s="21" t="s">
         <v>12</v>
       </c>
@@ -1266,8 +1262,8 @@
       <c r="J3" s="3"/>
     </row>
     <row r="4" spans="1:10" ht="27" customHeight="1">
-      <c r="A4" s="29"/>
-      <c r="B4" s="27" t="s">
+      <c r="A4" s="35"/>
+      <c r="B4" s="33" t="s">
         <v>68</v>
       </c>
       <c r="C4" s="17" t="s">
@@ -1286,8 +1282,8 @@
       <c r="J4" s="3"/>
     </row>
     <row r="5" spans="1:10">
-      <c r="A5" s="29"/>
-      <c r="B5" s="27"/>
+      <c r="A5" s="35"/>
+      <c r="B5" s="33"/>
       <c r="C5" s="17" t="s">
         <v>14</v>
       </c>
@@ -1304,8 +1300,8 @@
       <c r="J5" s="3"/>
     </row>
     <row r="6" spans="1:10">
-      <c r="A6" s="29"/>
-      <c r="B6" s="27"/>
+      <c r="A6" s="35"/>
+      <c r="B6" s="33"/>
       <c r="C6" s="17" t="s">
         <v>15</v>
       </c>
@@ -1322,8 +1318,8 @@
       <c r="J6" s="3"/>
     </row>
     <row r="7" spans="1:10">
-      <c r="A7" s="29"/>
-      <c r="B7" s="27"/>
+      <c r="A7" s="35"/>
+      <c r="B7" s="33"/>
       <c r="C7" s="17" t="s">
         <v>16</v>
       </c>
@@ -1340,8 +1336,8 @@
       <c r="J7" s="3"/>
     </row>
     <row r="8" spans="1:10">
-      <c r="A8" s="29"/>
-      <c r="B8" s="27"/>
+      <c r="A8" s="35"/>
+      <c r="B8" s="33"/>
       <c r="C8" s="17" t="s">
         <v>53</v>
       </c>
@@ -1358,8 +1354,8 @@
       <c r="J8" s="3"/>
     </row>
     <row r="9" spans="1:10">
-      <c r="A9" s="29"/>
-      <c r="B9" s="27"/>
+      <c r="A9" s="35"/>
+      <c r="B9" s="33"/>
       <c r="C9" s="17" t="s">
         <v>17</v>
       </c>
@@ -1376,8 +1372,8 @@
       <c r="J9" s="3"/>
     </row>
     <row r="10" spans="1:10">
-      <c r="A10" s="29"/>
-      <c r="B10" s="27"/>
+      <c r="A10" s="35"/>
+      <c r="B10" s="33"/>
       <c r="C10" s="17" t="s">
         <v>18</v>
       </c>
@@ -1394,8 +1390,8 @@
       <c r="J10" s="3"/>
     </row>
     <row r="11" spans="1:10">
-      <c r="A11" s="29"/>
-      <c r="B11" s="30" t="s">
+      <c r="A11" s="35"/>
+      <c r="B11" s="32" t="s">
         <v>19</v>
       </c>
       <c r="C11" s="14" t="s">
@@ -1414,8 +1410,8 @@
       <c r="J11" s="3"/>
     </row>
     <row r="12" spans="1:10">
-      <c r="A12" s="29"/>
-      <c r="B12" s="30"/>
+      <c r="A12" s="35"/>
+      <c r="B12" s="32"/>
       <c r="C12" s="14" t="s">
         <v>54</v>
       </c>
@@ -1432,8 +1428,8 @@
       <c r="J12" s="3"/>
     </row>
     <row r="13" spans="1:10">
-      <c r="A13" s="29"/>
-      <c r="B13" s="30"/>
+      <c r="A13" s="35"/>
+      <c r="B13" s="32"/>
       <c r="C13" s="14" t="s">
         <v>55</v>
       </c>
@@ -1450,8 +1446,8 @@
       <c r="J13" s="3"/>
     </row>
     <row r="14" spans="1:10">
-      <c r="A14" s="29"/>
-      <c r="B14" s="30"/>
+      <c r="A14" s="35"/>
+      <c r="B14" s="32"/>
       <c r="C14" s="14" t="s">
         <v>56</v>
       </c>
@@ -1468,8 +1464,8 @@
       <c r="J14" s="3"/>
     </row>
     <row r="15" spans="1:10">
-      <c r="A15" s="29"/>
-      <c r="B15" s="27" t="s">
+      <c r="A15" s="35"/>
+      <c r="B15" s="33" t="s">
         <v>21</v>
       </c>
       <c r="C15" s="17" t="s">
@@ -1488,8 +1484,8 @@
       <c r="J15" s="3"/>
     </row>
     <row r="16" spans="1:10">
-      <c r="A16" s="29"/>
-      <c r="B16" s="27"/>
+      <c r="A16" s="35"/>
+      <c r="B16" s="33"/>
       <c r="C16" s="17" t="s">
         <v>62</v>
       </c>
@@ -1506,8 +1502,8 @@
       <c r="J16" s="3"/>
     </row>
     <row r="17" spans="1:10">
-      <c r="A17" s="29"/>
-      <c r="B17" s="27"/>
+      <c r="A17" s="35"/>
+      <c r="B17" s="33"/>
       <c r="C17" s="17" t="s">
         <v>23</v>
       </c>
@@ -1524,8 +1520,8 @@
       <c r="J17" s="3"/>
     </row>
     <row r="18" spans="1:10">
-      <c r="A18" s="29"/>
-      <c r="B18" s="27"/>
+      <c r="A18" s="35"/>
+      <c r="B18" s="33"/>
       <c r="C18" s="17" t="s">
         <v>24</v>
       </c>
@@ -1542,8 +1538,8 @@
       <c r="J18" s="3"/>
     </row>
     <row r="19" spans="1:10">
-      <c r="A19" s="29"/>
-      <c r="B19" s="27"/>
+      <c r="A19" s="35"/>
+      <c r="B19" s="33"/>
       <c r="C19" s="17" t="s">
         <v>25</v>
       </c>
@@ -1560,8 +1556,8 @@
       <c r="J19" s="3"/>
     </row>
     <row r="20" spans="1:10" ht="27">
-      <c r="A20" s="29"/>
-      <c r="B20" s="30" t="s">
+      <c r="A20" s="35"/>
+      <c r="B20" s="32" t="s">
         <v>26</v>
       </c>
       <c r="C20" s="14" t="s">
@@ -1580,8 +1576,8 @@
       <c r="J20" s="3"/>
     </row>
     <row r="21" spans="1:10">
-      <c r="A21" s="29"/>
-      <c r="B21" s="30"/>
+      <c r="A21" s="35"/>
+      <c r="B21" s="32"/>
       <c r="C21" s="14" t="s">
         <v>132</v>
       </c>
@@ -1598,8 +1594,8 @@
       <c r="J21" s="3"/>
     </row>
     <row r="22" spans="1:10" ht="27">
-      <c r="A22" s="29"/>
-      <c r="B22" s="30"/>
+      <c r="A22" s="35"/>
+      <c r="B22" s="32"/>
       <c r="C22" s="14" t="s">
         <v>72</v>
       </c>
@@ -1616,8 +1612,8 @@
       <c r="J22" s="3"/>
     </row>
     <row r="23" spans="1:10">
-      <c r="A23" s="29"/>
-      <c r="B23" s="30"/>
+      <c r="A23" s="35"/>
+      <c r="B23" s="32"/>
       <c r="C23" s="14" t="s">
         <v>93</v>
       </c>
@@ -1634,8 +1630,8 @@
       <c r="J23" s="3"/>
     </row>
     <row r="24" spans="1:10">
-      <c r="A24" s="29"/>
-      <c r="B24" s="30"/>
+      <c r="A24" s="35"/>
+      <c r="B24" s="32"/>
       <c r="C24" s="14" t="s">
         <v>71</v>
       </c>
@@ -1652,8 +1648,8 @@
       <c r="J24" s="3"/>
     </row>
     <row r="25" spans="1:10">
-      <c r="A25" s="29"/>
-      <c r="B25" s="30"/>
+      <c r="A25" s="35"/>
+      <c r="B25" s="32"/>
       <c r="C25" s="14" t="s">
         <v>27</v>
       </c>
@@ -1670,8 +1666,8 @@
       <c r="J25" s="3"/>
     </row>
     <row r="26" spans="1:10">
-      <c r="A26" s="29"/>
-      <c r="B26" s="30"/>
+      <c r="A26" s="35"/>
+      <c r="B26" s="32"/>
       <c r="C26" s="14" t="s">
         <v>28</v>
       </c>
@@ -1688,8 +1684,8 @@
       <c r="J26" s="3"/>
     </row>
     <row r="27" spans="1:10">
-      <c r="A27" s="29"/>
-      <c r="B27" s="30"/>
+      <c r="A27" s="35"/>
+      <c r="B27" s="32"/>
       <c r="C27" s="14" t="s">
         <v>29</v>
       </c>
@@ -1706,8 +1702,8 @@
       <c r="J27" s="1"/>
     </row>
     <row r="28" spans="1:10">
-      <c r="A28" s="29"/>
-      <c r="B28" s="30"/>
+      <c r="A28" s="35"/>
+      <c r="B28" s="32"/>
       <c r="C28" s="14" t="s">
         <v>30</v>
       </c>
@@ -1724,8 +1720,8 @@
       <c r="J28" s="1"/>
     </row>
     <row r="29" spans="1:10">
-      <c r="A29" s="29"/>
-      <c r="B29" s="30"/>
+      <c r="A29" s="35"/>
+      <c r="B29" s="32"/>
       <c r="C29" s="14" t="s">
         <v>106</v>
       </c>
@@ -1742,8 +1738,8 @@
       <c r="J29" s="1"/>
     </row>
     <row r="30" spans="1:10">
-      <c r="A30" s="29"/>
-      <c r="B30" s="30"/>
+      <c r="A30" s="35"/>
+      <c r="B30" s="32"/>
       <c r="C30" s="14" t="s">
         <v>82</v>
       </c>
@@ -1760,8 +1756,8 @@
       <c r="J30" s="1"/>
     </row>
     <row r="31" spans="1:10" ht="27" customHeight="1">
-      <c r="A31" s="29"/>
-      <c r="B31" s="35" t="s">
+      <c r="A31" s="35"/>
+      <c r="B31" s="31" t="s">
         <v>47</v>
       </c>
       <c r="C31" s="15" t="s">
@@ -1780,8 +1776,8 @@
       <c r="J31" s="1"/>
     </row>
     <row r="32" spans="1:10">
-      <c r="A32" s="29"/>
-      <c r="B32" s="35"/>
+      <c r="A32" s="35"/>
+      <c r="B32" s="31"/>
       <c r="C32" s="15" t="s">
         <v>48</v>
       </c>
@@ -1798,8 +1794,8 @@
       <c r="J32" s="1"/>
     </row>
     <row r="33" spans="1:10">
-      <c r="A33" s="29"/>
-      <c r="B33" s="35"/>
+      <c r="A33" s="35"/>
+      <c r="B33" s="31"/>
       <c r="C33" s="15" t="s">
         <v>49</v>
       </c>
@@ -1816,8 +1812,8 @@
       <c r="J33" s="1"/>
     </row>
     <row r="34" spans="1:10">
-      <c r="A34" s="29"/>
-      <c r="B34" s="35"/>
+      <c r="A34" s="35"/>
+      <c r="B34" s="31"/>
       <c r="C34" s="15" t="s">
         <v>59</v>
       </c>
@@ -1834,7 +1830,7 @@
       <c r="J34" s="1"/>
     </row>
     <row r="35" spans="1:10">
-      <c r="A35" s="29"/>
+      <c r="A35" s="35"/>
       <c r="B35" s="23"/>
       <c r="C35" s="15" t="s">
         <v>127</v>
@@ -1852,8 +1848,8 @@
       <c r="J35" s="1"/>
     </row>
     <row r="36" spans="1:10">
-      <c r="A36" s="29"/>
-      <c r="B36" s="30" t="s">
+      <c r="A36" s="35"/>
+      <c r="B36" s="32" t="s">
         <v>50</v>
       </c>
       <c r="C36" s="14" t="s">
@@ -1872,8 +1868,8 @@
       <c r="J36" s="1"/>
     </row>
     <row r="37" spans="1:10">
-      <c r="A37" s="29"/>
-      <c r="B37" s="30"/>
+      <c r="A37" s="35"/>
+      <c r="B37" s="32"/>
       <c r="C37" s="14" t="s">
         <v>86</v>
       </c>
@@ -1890,8 +1886,8 @@
       <c r="J37" s="1"/>
     </row>
     <row r="38" spans="1:10">
-      <c r="A38" s="29"/>
-      <c r="B38" s="30"/>
+      <c r="A38" s="35"/>
+      <c r="B38" s="32"/>
       <c r="C38" s="14" t="s">
         <v>85</v>
       </c>
@@ -1908,8 +1904,8 @@
       <c r="J38" s="1"/>
     </row>
     <row r="39" spans="1:10">
-      <c r="A39" s="29"/>
-      <c r="B39" s="30"/>
+      <c r="A39" s="35"/>
+      <c r="B39" s="32"/>
       <c r="C39" s="14" t="s">
         <v>58</v>
       </c>
@@ -1926,8 +1922,8 @@
       <c r="J39" s="1"/>
     </row>
     <row r="40" spans="1:10">
-      <c r="A40" s="29"/>
-      <c r="B40" s="27" t="s">
+      <c r="A40" s="35"/>
+      <c r="B40" s="33" t="s">
         <v>31</v>
       </c>
       <c r="C40" s="17" t="s">
@@ -1946,8 +1942,8 @@
       <c r="J40" s="1"/>
     </row>
     <row r="41" spans="1:10">
-      <c r="A41" s="29"/>
-      <c r="B41" s="27"/>
+      <c r="A41" s="35"/>
+      <c r="B41" s="33"/>
       <c r="C41" s="17" t="s">
         <v>33</v>
       </c>
@@ -1964,8 +1960,8 @@
       <c r="J41" s="1"/>
     </row>
     <row r="42" spans="1:10">
-      <c r="A42" s="29"/>
-      <c r="B42" s="27"/>
+      <c r="A42" s="35"/>
+      <c r="B42" s="33"/>
       <c r="C42" s="17" t="s">
         <v>34</v>
       </c>
@@ -1982,8 +1978,8 @@
       <c r="J42" s="1"/>
     </row>
     <row r="43" spans="1:10">
-      <c r="A43" s="29"/>
-      <c r="B43" s="30" t="s">
+      <c r="A43" s="35"/>
+      <c r="B43" s="32" t="s">
         <v>35</v>
       </c>
       <c r="C43" s="14" t="s">
@@ -2002,8 +1998,8 @@
       <c r="J43" s="1"/>
     </row>
     <row r="44" spans="1:10">
-      <c r="A44" s="29"/>
-      <c r="B44" s="30"/>
+      <c r="A44" s="35"/>
+      <c r="B44" s="32"/>
       <c r="C44" s="14" t="s">
         <v>36</v>
       </c>
@@ -2020,8 +2016,8 @@
       <c r="J44" s="1"/>
     </row>
     <row r="45" spans="1:10">
-      <c r="A45" s="29"/>
-      <c r="B45" s="30"/>
+      <c r="A45" s="35"/>
+      <c r="B45" s="32"/>
       <c r="C45" s="14" t="s">
         <v>37</v>
       </c>
@@ -2038,8 +2034,8 @@
       <c r="J45" s="1"/>
     </row>
     <row r="46" spans="1:10">
-      <c r="A46" s="29"/>
-      <c r="B46" s="27" t="s">
+      <c r="A46" s="35"/>
+      <c r="B46" s="33" t="s">
         <v>38</v>
       </c>
       <c r="C46" s="17" t="s">
@@ -2058,8 +2054,8 @@
       <c r="J46" s="1"/>
     </row>
     <row r="47" spans="1:10">
-      <c r="A47" s="29"/>
-      <c r="B47" s="27"/>
+      <c r="A47" s="35"/>
+      <c r="B47" s="33"/>
       <c r="C47" s="17" t="s">
         <v>98</v>
       </c>
@@ -2068,7 +2064,7 @@
         <v>69</v>
       </c>
       <c r="F47" s="24" t="s">
-        <v>133</v>
+        <v>79</v>
       </c>
       <c r="G47" s="20"/>
       <c r="H47" s="1"/>
@@ -2076,8 +2072,8 @@
       <c r="J47" s="1"/>
     </row>
     <row r="48" spans="1:10">
-      <c r="A48" s="29"/>
-      <c r="B48" s="27"/>
+      <c r="A48" s="35"/>
+      <c r="B48" s="33"/>
       <c r="C48" s="17" t="s">
         <v>39</v>
       </c>
@@ -2094,8 +2090,8 @@
       <c r="J48" s="1"/>
     </row>
     <row r="49" spans="1:10">
-      <c r="A49" s="29"/>
-      <c r="B49" s="27"/>
+      <c r="A49" s="35"/>
+      <c r="B49" s="33"/>
       <c r="C49" s="17" t="s">
         <v>40</v>
       </c>
@@ -2112,8 +2108,8 @@
       <c r="J49" s="1"/>
     </row>
     <row r="50" spans="1:10">
-      <c r="A50" s="29"/>
-      <c r="B50" s="27"/>
+      <c r="A50" s="35"/>
+      <c r="B50" s="33"/>
       <c r="C50" s="17" t="s">
         <v>41</v>
       </c>
@@ -2130,8 +2126,8 @@
       <c r="J50" s="1"/>
     </row>
     <row r="51" spans="1:10">
-      <c r="A51" s="29"/>
-      <c r="B51" s="27"/>
+      <c r="A51" s="35"/>
+      <c r="B51" s="33"/>
       <c r="C51" s="17" t="s">
         <v>84</v>
       </c>
@@ -2148,8 +2144,8 @@
       <c r="J51" s="1"/>
     </row>
     <row r="52" spans="1:10">
-      <c r="A52" s="29"/>
-      <c r="B52" s="27"/>
+      <c r="A52" s="35"/>
+      <c r="B52" s="33"/>
       <c r="C52" s="17" t="s">
         <v>42</v>
       </c>
@@ -2166,8 +2162,8 @@
       <c r="J52" s="1"/>
     </row>
     <row r="53" spans="1:10">
-      <c r="A53" s="29"/>
-      <c r="B53" s="27"/>
+      <c r="A53" s="35"/>
+      <c r="B53" s="33"/>
       <c r="C53" s="17" t="s">
         <v>43</v>
       </c>
@@ -2184,7 +2180,7 @@
       <c r="J53" s="1"/>
     </row>
     <row r="54" spans="1:10">
-      <c r="A54" s="28" t="s">
+      <c r="A54" s="34" t="s">
         <v>74</v>
       </c>
       <c r="B54" s="18" t="s">
@@ -2206,7 +2202,7 @@
       <c r="J54" s="1"/>
     </row>
     <row r="55" spans="1:10">
-      <c r="A55" s="28"/>
+      <c r="A55" s="34"/>
       <c r="B55" s="18"/>
       <c r="C55" s="19" t="s">
         <v>108</v>
@@ -2224,7 +2220,7 @@
       <c r="J55" s="1"/>
     </row>
     <row r="56" spans="1:10">
-      <c r="A56" s="28"/>
+      <c r="A56" s="34"/>
       <c r="B56" s="18"/>
       <c r="C56" s="19" t="s">
         <v>107</v>
@@ -2242,7 +2238,7 @@
       <c r="J56" s="1"/>
     </row>
     <row r="57" spans="1:10">
-      <c r="A57" s="28"/>
+      <c r="A57" s="34"/>
       <c r="B57" s="18"/>
       <c r="C57" s="19" t="s">
         <v>83</v>
@@ -2260,7 +2256,7 @@
       <c r="J57" s="1"/>
     </row>
     <row r="58" spans="1:10">
-      <c r="A58" s="28"/>
+      <c r="A58" s="34"/>
       <c r="B58" s="18"/>
       <c r="C58" s="19" t="s">
         <v>109</v>
@@ -2278,7 +2274,7 @@
       <c r="J58" s="1"/>
     </row>
     <row r="59" spans="1:10">
-      <c r="A59" s="28"/>
+      <c r="A59" s="34"/>
       <c r="B59" s="18"/>
       <c r="C59" s="19" t="s">
         <v>110</v>
@@ -2296,7 +2292,7 @@
       <c r="J59" s="1"/>
     </row>
     <row r="60" spans="1:10" ht="27">
-      <c r="A60" s="28"/>
+      <c r="A60" s="34"/>
       <c r="B60" s="18" t="s">
         <v>111</v>
       </c>
@@ -2316,7 +2312,7 @@
       <c r="J60" s="1"/>
     </row>
     <row r="61" spans="1:10">
-      <c r="A61" s="28"/>
+      <c r="A61" s="34"/>
       <c r="B61" s="18" t="s">
         <v>113</v>
       </c>
@@ -2336,7 +2332,7 @@
       <c r="J61" s="1"/>
     </row>
     <row r="62" spans="1:10" ht="27">
-      <c r="A62" s="28"/>
+      <c r="A62" s="34"/>
       <c r="B62" s="18" t="s">
         <v>115</v>
       </c>
@@ -2356,7 +2352,7 @@
       <c r="J62" s="1"/>
     </row>
     <row r="63" spans="1:10">
-      <c r="A63" s="28"/>
+      <c r="A63" s="34"/>
       <c r="B63" s="18" t="s">
         <v>117</v>
       </c>
@@ -2376,7 +2372,7 @@
       <c r="J63" s="1"/>
     </row>
     <row r="64" spans="1:10">
-      <c r="A64" s="28"/>
+      <c r="A64" s="34"/>
       <c r="B64" s="18" t="s">
         <v>77</v>
       </c>
@@ -2396,7 +2392,7 @@
       <c r="J64" s="1"/>
     </row>
     <row r="65" spans="1:10">
-      <c r="A65" s="28"/>
+      <c r="A65" s="34"/>
       <c r="B65" s="18" t="s">
         <v>105</v>
       </c>
@@ -2416,7 +2412,7 @@
       <c r="J65" s="1"/>
     </row>
     <row r="66" spans="1:10">
-      <c r="A66" s="28"/>
+      <c r="A66" s="34"/>
       <c r="B66" s="18"/>
       <c r="C66" s="19" t="s">
         <v>120</v>
@@ -2434,7 +2430,7 @@
       <c r="J66" s="1"/>
     </row>
     <row r="67" spans="1:10">
-      <c r="A67" s="28"/>
+      <c r="A67" s="34"/>
       <c r="B67" s="18" t="s">
         <v>101</v>
       </c>
@@ -2454,7 +2450,7 @@
       <c r="J67" s="1"/>
     </row>
     <row r="68" spans="1:10">
-      <c r="A68" s="28"/>
+      <c r="A68" s="34"/>
       <c r="B68" s="18"/>
       <c r="C68" s="19" t="s">
         <v>103</v>
@@ -2472,7 +2468,7 @@
       <c r="J68" s="1"/>
     </row>
     <row r="69" spans="1:10">
-      <c r="A69" s="28"/>
+      <c r="A69" s="34"/>
       <c r="B69" s="18"/>
       <c r="C69" s="19" t="s">
         <v>104</v>
@@ -2490,7 +2486,7 @@
       <c r="J69" s="1"/>
     </row>
     <row r="70" spans="1:10">
-      <c r="A70" s="28"/>
+      <c r="A70" s="34"/>
       <c r="B70" s="18" t="s">
         <v>121</v>
       </c>
@@ -2510,10 +2506,10 @@
       <c r="J70" s="1"/>
     </row>
     <row r="71" spans="1:10">
-      <c r="A71" s="33" t="s">
+      <c r="A71" s="29" t="s">
         <v>64</v>
       </c>
-      <c r="B71" s="34" t="s">
+      <c r="B71" s="30" t="s">
         <v>65</v>
       </c>
       <c r="C71" s="22" t="s">
@@ -2532,8 +2528,8 @@
       <c r="J71" s="1"/>
     </row>
     <row r="72" spans="1:10">
-      <c r="A72" s="33"/>
-      <c r="B72" s="34"/>
+      <c r="A72" s="29"/>
+      <c r="B72" s="30"/>
       <c r="C72" s="22" t="s">
         <v>45</v>
       </c>
@@ -2550,8 +2546,8 @@
       <c r="J72" s="1"/>
     </row>
     <row r="73" spans="1:10">
-      <c r="A73" s="33"/>
-      <c r="B73" s="34"/>
+      <c r="A73" s="29"/>
+      <c r="B73" s="30"/>
       <c r="C73" s="22" t="s">
         <v>46</v>
       </c>
@@ -2568,8 +2564,8 @@
       <c r="J73" s="1"/>
     </row>
     <row r="74" spans="1:10">
-      <c r="A74" s="33"/>
-      <c r="B74" s="34"/>
+      <c r="A74" s="29"/>
+      <c r="B74" s="30"/>
       <c r="C74" s="22" t="s">
         <v>124</v>
       </c>
@@ -2586,8 +2582,8 @@
       <c r="J74" s="1"/>
     </row>
     <row r="75" spans="1:10">
-      <c r="A75" s="33"/>
-      <c r="B75" s="34"/>
+      <c r="A75" s="29"/>
+      <c r="B75" s="30"/>
       <c r="C75" s="22" t="s">
         <v>125</v>
       </c>
@@ -2604,8 +2600,8 @@
       <c r="J75" s="1"/>
     </row>
     <row r="76" spans="1:10">
-      <c r="A76" s="33"/>
-      <c r="B76" s="34"/>
+      <c r="A76" s="29"/>
+      <c r="B76" s="30"/>
       <c r="C76" s="22" t="s">
         <v>60</v>
       </c>
@@ -2623,12 +2619,12 @@
     </row>
     <row r="77" spans="1:10" ht="36.75" customHeight="1">
       <c r="A77" s="26"/>
-      <c r="B77" s="31" t="s">
+      <c r="B77" s="27" t="s">
         <v>131</v>
       </c>
-      <c r="C77" s="32"/>
-      <c r="D77" s="32"/>
-      <c r="E77" s="32"/>
+      <c r="C77" s="28"/>
+      <c r="D77" s="28"/>
+      <c r="E77" s="28"/>
       <c r="G77" s="20"/>
       <c r="H77" s="1"/>
       <c r="I77" s="1"/>
@@ -2640,11 +2636,6 @@
     <filterColumn colId="5"/>
   </autoFilter>
   <mergeCells count="14">
-    <mergeCell ref="B77:E77"/>
-    <mergeCell ref="A71:A76"/>
-    <mergeCell ref="B71:B76"/>
-    <mergeCell ref="B31:B34"/>
-    <mergeCell ref="B36:B39"/>
     <mergeCell ref="B4:B10"/>
     <mergeCell ref="A54:A70"/>
     <mergeCell ref="A2:A53"/>
@@ -2654,6 +2645,11 @@
     <mergeCell ref="B40:B42"/>
     <mergeCell ref="B43:B45"/>
     <mergeCell ref="B46:B53"/>
+    <mergeCell ref="B77:E77"/>
+    <mergeCell ref="A71:A76"/>
+    <mergeCell ref="B71:B76"/>
+    <mergeCell ref="B31:B34"/>
+    <mergeCell ref="B36:B39"/>
   </mergeCells>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/internal_doc/05.测试设计/特性守护矩阵.xlsx
+++ b/internal_doc/05.测试设计/特性守护矩阵.xlsx
@@ -466,10 +466,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>桶管理</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>用户管理</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -571,6 +567,10 @@
   </si>
   <si>
     <t>基本功能自动化</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>桶管理/区域管理</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -804,18 +804,6 @@
     <xf numFmtId="0" fontId="0" fillId="8" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="9" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -826,6 +814,9 @@
     <xf numFmtId="0" fontId="0" fillId="8" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
@@ -834,6 +825,15 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="9" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -1229,17 +1229,17 @@
         <v>0</v>
       </c>
       <c r="G1" s="4" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="H1" s="4" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="I1" s="4" t="s">
         <v>3</v>
       </c>
     </row>
     <row r="2" spans="1:9">
-      <c r="A2" s="25" t="s">
+      <c r="A2" s="33" t="s">
         <v>39</v>
       </c>
       <c r="B2" s="12" t="s">
@@ -1256,13 +1256,13 @@
       </c>
       <c r="F2" s="2"/>
       <c r="G2" s="2" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="H2" s="2"/>
       <c r="I2" s="2"/>
     </row>
     <row r="3" spans="1:9">
-      <c r="A3" s="25"/>
+      <c r="A3" s="33"/>
       <c r="B3" s="17" t="s">
         <v>9</v>
       </c>
@@ -1277,18 +1277,18 @@
       </c>
       <c r="F3" s="5"/>
       <c r="G3" s="2" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="H3" s="2"/>
       <c r="I3" s="2"/>
     </row>
     <row r="4" spans="1:9" ht="27" customHeight="1">
-      <c r="A4" s="25"/>
-      <c r="B4" s="23" t="s">
+      <c r="A4" s="33"/>
+      <c r="B4" s="31" t="s">
         <v>43</v>
       </c>
       <c r="C4" s="13" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="D4" s="2" t="s">
         <v>58</v>
@@ -1298,16 +1298,16 @@
       </c>
       <c r="F4" s="5"/>
       <c r="G4" s="2" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="H4" s="2" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="I4" s="2"/>
     </row>
     <row r="5" spans="1:9">
-      <c r="A5" s="25"/>
-      <c r="B5" s="23"/>
+      <c r="A5" s="33"/>
+      <c r="B5" s="31"/>
       <c r="C5" s="13" t="s">
         <v>10</v>
       </c>
@@ -1319,14 +1319,14 @@
       </c>
       <c r="F5" s="5"/>
       <c r="G5" s="2" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="H5" s="2"/>
       <c r="I5" s="2"/>
     </row>
     <row r="6" spans="1:9">
-      <c r="A6" s="25"/>
-      <c r="B6" s="23"/>
+      <c r="A6" s="33"/>
+      <c r="B6" s="31"/>
       <c r="C6" s="13" t="s">
         <v>36</v>
       </c>
@@ -1338,14 +1338,14 @@
       </c>
       <c r="F6" s="6"/>
       <c r="G6" s="7" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="H6" s="7"/>
       <c r="I6" s="2"/>
     </row>
     <row r="7" spans="1:9">
-      <c r="A7" s="25"/>
-      <c r="B7" s="23"/>
+      <c r="A7" s="33"/>
+      <c r="B7" s="31"/>
       <c r="C7" s="13" t="s">
         <v>11</v>
       </c>
@@ -1357,14 +1357,14 @@
       </c>
       <c r="F7" s="6"/>
       <c r="G7" s="7" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="H7" s="7"/>
       <c r="I7" s="2"/>
     </row>
     <row r="8" spans="1:9">
-      <c r="A8" s="25"/>
-      <c r="B8" s="23"/>
+      <c r="A8" s="33"/>
+      <c r="B8" s="31"/>
       <c r="C8" s="13" t="s">
         <v>12</v>
       </c>
@@ -1376,14 +1376,14 @@
       </c>
       <c r="F8" s="6"/>
       <c r="G8" s="7" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="H8" s="7"/>
       <c r="I8" s="2"/>
     </row>
     <row r="9" spans="1:9">
-      <c r="A9" s="25"/>
-      <c r="B9" s="26" t="s">
+      <c r="A9" s="33"/>
+      <c r="B9" s="27" t="s">
         <v>13</v>
       </c>
       <c r="C9" s="10" t="s">
@@ -1397,16 +1397,16 @@
       </c>
       <c r="F9" s="8"/>
       <c r="G9" s="7" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="H9" s="2"/>
       <c r="I9" s="2"/>
     </row>
     <row r="10" spans="1:9">
-      <c r="A10" s="25"/>
-      <c r="B10" s="26"/>
+      <c r="A10" s="33"/>
+      <c r="B10" s="27"/>
       <c r="C10" s="10" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="D10" s="2" t="s">
         <v>41</v>
@@ -1416,35 +1416,35 @@
       </c>
       <c r="F10" s="8"/>
       <c r="G10" s="2" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="H10" s="2"/>
       <c r="I10" s="2"/>
     </row>
     <row r="11" spans="1:9">
-      <c r="A11" s="25"/>
-      <c r="B11" s="23" t="s">
+      <c r="A11" s="33"/>
+      <c r="B11" s="31" t="s">
         <v>15</v>
       </c>
       <c r="C11" s="13" t="s">
         <v>101</v>
       </c>
       <c r="D11" s="2" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="E11" s="2" t="s">
         <v>58</v>
       </c>
       <c r="F11" s="6"/>
       <c r="G11" s="2" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="H11" s="7"/>
       <c r="I11" s="2"/>
     </row>
     <row r="12" spans="1:9">
-      <c r="A12" s="25"/>
-      <c r="B12" s="23"/>
+      <c r="A12" s="33"/>
+      <c r="B12" s="31"/>
       <c r="C12" s="13" t="s">
         <v>38</v>
       </c>
@@ -1456,14 +1456,14 @@
       </c>
       <c r="F12" s="8"/>
       <c r="G12" s="2" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="H12" s="2"/>
       <c r="I12" s="2"/>
     </row>
     <row r="13" spans="1:9" ht="27">
-      <c r="A13" s="25"/>
-      <c r="B13" s="26" t="s">
+      <c r="A13" s="33"/>
+      <c r="B13" s="27" t="s">
         <v>16</v>
       </c>
       <c r="C13" s="10" t="s">
@@ -1477,14 +1477,14 @@
       </c>
       <c r="F13" s="9"/>
       <c r="G13" s="2" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="H13" s="2"/>
       <c r="I13" s="2"/>
     </row>
     <row r="14" spans="1:9">
-      <c r="A14" s="25"/>
-      <c r="B14" s="26"/>
+      <c r="A14" s="33"/>
+      <c r="B14" s="27"/>
       <c r="C14" s="10" t="s">
         <v>100</v>
       </c>
@@ -1496,71 +1496,71 @@
       </c>
       <c r="F14" s="9"/>
       <c r="G14" s="2" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="H14" s="2"/>
       <c r="I14" s="2"/>
     </row>
     <row r="15" spans="1:9" ht="27">
-      <c r="A15" s="25"/>
-      <c r="B15" s="26"/>
+      <c r="A15" s="33"/>
+      <c r="B15" s="27"/>
       <c r="C15" s="10" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="D15" s="2" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="E15" s="2" t="s">
         <v>54</v>
       </c>
       <c r="F15" s="9"/>
       <c r="G15" s="2" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="H15" s="2"/>
       <c r="I15" s="2"/>
     </row>
     <row r="16" spans="1:9">
-      <c r="A16" s="25"/>
-      <c r="B16" s="26"/>
+      <c r="A16" s="33"/>
+      <c r="B16" s="27"/>
       <c r="C16" s="10" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="D16" s="2" t="s">
         <v>94</v>
       </c>
       <c r="E16" s="19" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="F16" s="9"/>
       <c r="G16" s="2" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="H16" s="2"/>
       <c r="I16" s="2"/>
     </row>
     <row r="17" spans="1:9">
-      <c r="A17" s="25"/>
-      <c r="B17" s="26"/>
+      <c r="A17" s="33"/>
+      <c r="B17" s="27"/>
       <c r="C17" s="10" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="D17" s="2" t="s">
         <v>52</v>
       </c>
       <c r="E17" s="2" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="F17" s="9"/>
       <c r="G17" s="2" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="H17" s="2"/>
       <c r="I17" s="2"/>
     </row>
     <row r="18" spans="1:9">
-      <c r="A18" s="25"/>
-      <c r="B18" s="26"/>
+      <c r="A18" s="33"/>
+      <c r="B18" s="27"/>
       <c r="C18" s="10" t="s">
         <v>46</v>
       </c>
@@ -1572,33 +1572,33 @@
       </c>
       <c r="F18" s="9"/>
       <c r="G18" s="2" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="H18" s="2"/>
       <c r="I18" s="2"/>
     </row>
     <row r="19" spans="1:9">
-      <c r="A19" s="25"/>
-      <c r="B19" s="26"/>
+      <c r="A19" s="33"/>
+      <c r="B19" s="27"/>
       <c r="C19" s="10" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="D19" s="2" t="s">
         <v>58</v>
       </c>
       <c r="E19" s="2" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="F19" s="9"/>
       <c r="G19" s="2" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="H19" s="2"/>
       <c r="I19" s="2"/>
     </row>
     <row r="20" spans="1:9">
-      <c r="A20" s="25"/>
-      <c r="B20" s="26"/>
+      <c r="A20" s="33"/>
+      <c r="B20" s="27"/>
       <c r="C20" s="10" t="s">
         <v>17</v>
       </c>
@@ -1606,20 +1606,20 @@
         <v>54</v>
       </c>
       <c r="E20" s="2" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="F20" s="2"/>
       <c r="G20" s="2" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="H20" s="2"/>
       <c r="I20" s="2"/>
     </row>
     <row r="21" spans="1:9">
-      <c r="A21" s="25"/>
-      <c r="B21" s="26"/>
+      <c r="A21" s="33"/>
+      <c r="B21" s="27"/>
       <c r="C21" s="10" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="D21" s="2" t="s">
         <v>64</v>
@@ -1629,14 +1629,14 @@
       </c>
       <c r="F21" s="6"/>
       <c r="G21" s="2" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="H21" s="7"/>
       <c r="I21" s="2"/>
     </row>
     <row r="22" spans="1:9">
-      <c r="A22" s="25"/>
-      <c r="B22" s="26"/>
+      <c r="A22" s="33"/>
+      <c r="B22" s="27"/>
       <c r="C22" s="10" t="s">
         <v>18</v>
       </c>
@@ -1648,14 +1648,14 @@
       </c>
       <c r="F22" s="16"/>
       <c r="G22" s="2" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="H22" s="1"/>
       <c r="I22" s="1"/>
     </row>
     <row r="23" spans="1:9">
-      <c r="A23" s="25"/>
-      <c r="B23" s="26"/>
+      <c r="A23" s="33"/>
+      <c r="B23" s="27"/>
       <c r="C23" s="10" t="s">
         <v>19</v>
       </c>
@@ -1667,14 +1667,14 @@
       </c>
       <c r="F23" s="16"/>
       <c r="G23" s="2" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="H23" s="1"/>
       <c r="I23" s="1"/>
     </row>
     <row r="24" spans="1:9">
-      <c r="A24" s="25"/>
-      <c r="B24" s="26"/>
+      <c r="A24" s="33"/>
+      <c r="B24" s="27"/>
       <c r="C24" s="10" t="s">
         <v>74</v>
       </c>
@@ -1682,18 +1682,18 @@
         <v>54</v>
       </c>
       <c r="E24" s="2" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="F24" s="16"/>
       <c r="G24" s="2" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="H24" s="1"/>
       <c r="I24" s="1"/>
     </row>
     <row r="25" spans="1:9">
-      <c r="A25" s="25"/>
-      <c r="B25" s="26"/>
+      <c r="A25" s="33"/>
+      <c r="B25" s="27"/>
       <c r="C25" s="10" t="s">
         <v>55</v>
       </c>
@@ -1705,14 +1705,14 @@
       </c>
       <c r="F25" s="16"/>
       <c r="G25" s="2" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="H25" s="1"/>
       <c r="I25" s="1"/>
     </row>
     <row r="26" spans="1:9" ht="27" customHeight="1">
-      <c r="A26" s="25"/>
-      <c r="B26" s="30" t="s">
+      <c r="A26" s="33"/>
+      <c r="B26" s="26" t="s">
         <v>30</v>
       </c>
       <c r="C26" s="11" t="s">
@@ -1722,18 +1722,18 @@
         <v>58</v>
       </c>
       <c r="E26" s="1" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="F26" s="16"/>
       <c r="G26" s="2" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="H26" s="1"/>
       <c r="I26" s="1"/>
     </row>
     <row r="27" spans="1:9">
-      <c r="A27" s="25"/>
-      <c r="B27" s="30"/>
+      <c r="A27" s="33"/>
+      <c r="B27" s="26"/>
       <c r="C27" s="11" t="s">
         <v>31</v>
       </c>
@@ -1741,18 +1741,18 @@
         <v>58</v>
       </c>
       <c r="E27" s="1" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="F27" s="16"/>
       <c r="G27" s="2" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="H27" s="1"/>
       <c r="I27" s="1"/>
     </row>
     <row r="28" spans="1:9">
-      <c r="A28" s="25"/>
-      <c r="B28" s="30"/>
+      <c r="A28" s="33"/>
+      <c r="B28" s="26"/>
       <c r="C28" s="11" t="s">
         <v>32</v>
       </c>
@@ -1760,17 +1760,17 @@
         <v>58</v>
       </c>
       <c r="E28" s="1" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="F28" s="16"/>
       <c r="G28" s="2" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="H28" s="1"/>
       <c r="I28" s="1"/>
     </row>
     <row r="29" spans="1:9">
-      <c r="A29" s="25"/>
+      <c r="A29" s="33"/>
       <c r="B29" s="22"/>
       <c r="C29" s="11" t="s">
         <v>95</v>
@@ -1783,14 +1783,14 @@
       </c>
       <c r="F29" s="16"/>
       <c r="G29" s="2" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="H29" s="1"/>
       <c r="I29" s="1"/>
     </row>
     <row r="30" spans="1:9">
-      <c r="A30" s="25"/>
-      <c r="B30" s="26" t="s">
+      <c r="A30" s="33"/>
+      <c r="B30" s="27" t="s">
         <v>33</v>
       </c>
       <c r="C30" s="10" t="s">
@@ -1804,14 +1804,14 @@
       </c>
       <c r="F30" s="16"/>
       <c r="G30" s="2" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="H30" s="1"/>
       <c r="I30" s="1"/>
     </row>
     <row r="31" spans="1:9">
-      <c r="A31" s="25"/>
-      <c r="B31" s="26"/>
+      <c r="A31" s="33"/>
+      <c r="B31" s="27"/>
       <c r="C31" s="10" t="s">
         <v>103</v>
       </c>
@@ -1823,14 +1823,14 @@
       </c>
       <c r="F31" s="16"/>
       <c r="G31" s="2" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="H31" s="1"/>
       <c r="I31" s="1"/>
     </row>
     <row r="32" spans="1:9">
-      <c r="A32" s="25"/>
-      <c r="B32" s="26"/>
+      <c r="A32" s="33"/>
+      <c r="B32" s="27"/>
       <c r="C32" s="10" t="s">
         <v>56</v>
       </c>
@@ -1842,14 +1842,14 @@
       </c>
       <c r="F32" s="16"/>
       <c r="G32" s="2" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="H32" s="1"/>
       <c r="I32" s="1"/>
     </row>
     <row r="33" spans="1:9">
-      <c r="A33" s="25"/>
-      <c r="B33" s="23" t="s">
+      <c r="A33" s="33"/>
+      <c r="B33" s="31" t="s">
         <v>20</v>
       </c>
       <c r="C33" s="13" t="s">
@@ -1859,20 +1859,20 @@
         <v>58</v>
       </c>
       <c r="E33" s="1" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="F33" s="16"/>
       <c r="G33" s="2" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="H33" s="1"/>
       <c r="I33" s="1"/>
     </row>
     <row r="34" spans="1:9">
-      <c r="A34" s="25"/>
-      <c r="B34" s="23"/>
+      <c r="A34" s="33"/>
+      <c r="B34" s="31"/>
       <c r="C34" s="13" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="D34" s="2" t="s">
         <v>54</v>
@@ -1882,18 +1882,18 @@
       </c>
       <c r="F34" s="16"/>
       <c r="G34" s="2" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="H34" s="1"/>
       <c r="I34" s="1"/>
     </row>
     <row r="35" spans="1:9">
-      <c r="A35" s="25"/>
-      <c r="B35" s="26" t="s">
+      <c r="A35" s="33"/>
+      <c r="B35" s="27" t="s">
         <v>22</v>
       </c>
       <c r="C35" s="10" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="D35" s="2" t="s">
         <v>64</v>
@@ -1903,14 +1903,14 @@
       </c>
       <c r="F35" s="16"/>
       <c r="G35" s="2" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="H35" s="1"/>
       <c r="I35" s="1"/>
     </row>
     <row r="36" spans="1:9">
-      <c r="A36" s="25"/>
-      <c r="B36" s="26"/>
+      <c r="A36" s="33"/>
+      <c r="B36" s="27"/>
       <c r="C36" s="10" t="s">
         <v>23</v>
       </c>
@@ -1922,14 +1922,14 @@
       </c>
       <c r="F36" s="16"/>
       <c r="G36" s="2" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="H36" s="1"/>
       <c r="I36" s="1"/>
     </row>
     <row r="37" spans="1:9">
-      <c r="A37" s="25"/>
-      <c r="B37" s="23" t="s">
+      <c r="A37" s="33"/>
+      <c r="B37" s="31" t="s">
         <v>24</v>
       </c>
       <c r="C37" s="13" t="s">
@@ -1943,14 +1943,14 @@
       </c>
       <c r="F37" s="16"/>
       <c r="G37" s="2" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="H37" s="1"/>
       <c r="I37" s="1"/>
     </row>
     <row r="38" spans="1:9">
-      <c r="A38" s="25"/>
-      <c r="B38" s="23"/>
+      <c r="A38" s="33"/>
+      <c r="B38" s="31"/>
       <c r="C38" s="13" t="s">
         <v>66</v>
       </c>
@@ -1962,14 +1962,14 @@
       </c>
       <c r="F38" s="16"/>
       <c r="G38" s="2" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="H38" s="1"/>
       <c r="I38" s="1"/>
     </row>
     <row r="39" spans="1:9">
-      <c r="A39" s="25"/>
-      <c r="B39" s="23"/>
+      <c r="A39" s="33"/>
+      <c r="B39" s="31"/>
       <c r="C39" s="13" t="s">
         <v>25</v>
       </c>
@@ -1981,14 +1981,14 @@
       </c>
       <c r="F39" s="16"/>
       <c r="G39" s="2" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="H39" s="1"/>
       <c r="I39" s="1"/>
     </row>
     <row r="40" spans="1:9">
-      <c r="A40" s="25"/>
-      <c r="B40" s="23"/>
+      <c r="A40" s="33"/>
+      <c r="B40" s="31"/>
       <c r="C40" s="13" t="s">
         <v>26</v>
       </c>
@@ -2000,52 +2000,52 @@
       </c>
       <c r="F40" s="16"/>
       <c r="G40" s="2" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="H40" s="1"/>
       <c r="I40" s="1"/>
     </row>
     <row r="41" spans="1:9">
-      <c r="A41" s="25"/>
-      <c r="B41" s="23"/>
+      <c r="A41" s="33"/>
+      <c r="B41" s="31"/>
       <c r="C41" s="13" t="s">
         <v>27</v>
       </c>
       <c r="D41" s="2" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="E41" s="1" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="F41" s="16"/>
       <c r="G41" s="2" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="H41" s="1"/>
       <c r="I41" s="1"/>
     </row>
     <row r="42" spans="1:9">
-      <c r="A42" s="25"/>
-      <c r="B42" s="23"/>
+      <c r="A42" s="33"/>
+      <c r="B42" s="31"/>
       <c r="C42" s="13" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="D42" s="2" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="E42" s="1" t="s">
         <v>58</v>
       </c>
       <c r="F42" s="16"/>
       <c r="G42" s="2" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="H42" s="1"/>
       <c r="I42" s="1"/>
     </row>
     <row r="43" spans="1:9">
-      <c r="A43" s="25"/>
-      <c r="B43" s="23"/>
+      <c r="A43" s="33"/>
+      <c r="B43" s="31"/>
       <c r="C43" s="13" t="s">
         <v>28</v>
       </c>
@@ -2053,18 +2053,18 @@
         <v>58</v>
       </c>
       <c r="E43" s="1" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="F43" s="16"/>
       <c r="G43" s="2" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="H43" s="1"/>
       <c r="I43" s="1"/>
     </row>
     <row r="44" spans="1:9">
-      <c r="A44" s="25"/>
-      <c r="B44" s="23"/>
+      <c r="A44" s="33"/>
+      <c r="B44" s="31"/>
       <c r="C44" s="13" t="s">
         <v>29</v>
       </c>
@@ -2072,17 +2072,17 @@
         <v>53</v>
       </c>
       <c r="E44" s="1" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="F44" s="16"/>
       <c r="G44" s="2" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="H44" s="1"/>
       <c r="I44" s="1"/>
     </row>
     <row r="45" spans="1:9">
-      <c r="A45" s="24" t="s">
+      <c r="A45" s="32" t="s">
         <v>47</v>
       </c>
       <c r="B45" s="14" t="s">
@@ -2099,13 +2099,13 @@
       </c>
       <c r="F45" s="16"/>
       <c r="G45" s="2" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="H45" s="1"/>
       <c r="I45" s="1"/>
     </row>
     <row r="46" spans="1:9">
-      <c r="A46" s="24"/>
+      <c r="A46" s="32"/>
       <c r="B46" s="14"/>
       <c r="C46" s="15" t="s">
         <v>76</v>
@@ -2118,13 +2118,13 @@
       </c>
       <c r="F46" s="16"/>
       <c r="G46" s="2" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="H46" s="1"/>
       <c r="I46" s="1"/>
     </row>
     <row r="47" spans="1:9">
-      <c r="A47" s="24"/>
+      <c r="A47" s="32"/>
       <c r="B47" s="14"/>
       <c r="C47" s="15" t="s">
         <v>75</v>
@@ -2137,13 +2137,13 @@
       </c>
       <c r="F47" s="16"/>
       <c r="G47" s="2" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="H47" s="1"/>
       <c r="I47" s="1"/>
     </row>
     <row r="48" spans="1:9">
-      <c r="A48" s="24"/>
+      <c r="A48" s="32"/>
       <c r="B48" s="14"/>
       <c r="C48" s="15" t="s">
         <v>77</v>
@@ -2156,13 +2156,13 @@
       </c>
       <c r="F48" s="16"/>
       <c r="G48" s="2" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="H48" s="1"/>
       <c r="I48" s="1"/>
     </row>
     <row r="49" spans="1:9">
-      <c r="A49" s="24"/>
+      <c r="A49" s="32"/>
       <c r="B49" s="14"/>
       <c r="C49" s="15" t="s">
         <v>78</v>
@@ -2175,13 +2175,13 @@
       </c>
       <c r="F49" s="16"/>
       <c r="G49" s="2" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="H49" s="1"/>
       <c r="I49" s="1"/>
     </row>
     <row r="50" spans="1:9" ht="27">
-      <c r="A50" s="24"/>
+      <c r="A50" s="32"/>
       <c r="B50" s="14" t="s">
         <v>79</v>
       </c>
@@ -2196,13 +2196,13 @@
       </c>
       <c r="F50" s="16"/>
       <c r="G50" s="2" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="H50" s="1"/>
       <c r="I50" s="1"/>
     </row>
     <row r="51" spans="1:9">
-      <c r="A51" s="24"/>
+      <c r="A51" s="32"/>
       <c r="B51" s="14" t="s">
         <v>81</v>
       </c>
@@ -2217,13 +2217,13 @@
       </c>
       <c r="F51" s="16"/>
       <c r="G51" s="2" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="H51" s="1"/>
       <c r="I51" s="1"/>
     </row>
     <row r="52" spans="1:9" ht="27">
-      <c r="A52" s="24"/>
+      <c r="A52" s="32"/>
       <c r="B52" s="14" t="s">
         <v>83</v>
       </c>
@@ -2238,13 +2238,13 @@
       </c>
       <c r="F52" s="16"/>
       <c r="G52" s="2" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="H52" s="1"/>
       <c r="I52" s="1"/>
     </row>
     <row r="53" spans="1:9">
-      <c r="A53" s="24"/>
+      <c r="A53" s="32"/>
       <c r="B53" s="14" t="s">
         <v>85</v>
       </c>
@@ -2259,13 +2259,13 @@
       </c>
       <c r="F53" s="16"/>
       <c r="G53" s="2" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="H53" s="1"/>
       <c r="I53" s="1"/>
     </row>
     <row r="54" spans="1:9">
-      <c r="A54" s="24"/>
+      <c r="A54" s="32"/>
       <c r="B54" s="14" t="s">
         <v>50</v>
       </c>
@@ -2280,13 +2280,13 @@
       </c>
       <c r="F54" s="16"/>
       <c r="G54" s="2" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="H54" s="1"/>
       <c r="I54" s="1"/>
     </row>
     <row r="55" spans="1:9">
-      <c r="A55" s="24"/>
+      <c r="A55" s="32"/>
       <c r="B55" s="14" t="s">
         <v>73</v>
       </c>
@@ -2301,13 +2301,13 @@
       </c>
       <c r="F55" s="16"/>
       <c r="G55" s="2" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="H55" s="1"/>
       <c r="I55" s="1"/>
     </row>
     <row r="56" spans="1:9">
-      <c r="A56" s="24"/>
+      <c r="A56" s="32"/>
       <c r="B56" s="14"/>
       <c r="C56" s="15" t="s">
         <v>88</v>
@@ -2320,13 +2320,13 @@
       </c>
       <c r="F56" s="16"/>
       <c r="G56" s="2" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="H56" s="1"/>
       <c r="I56" s="1"/>
     </row>
     <row r="57" spans="1:9">
-      <c r="A57" s="24"/>
+      <c r="A57" s="32"/>
       <c r="B57" s="14" t="s">
         <v>69</v>
       </c>
@@ -2341,13 +2341,13 @@
       </c>
       <c r="F57" s="16"/>
       <c r="G57" s="2" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="H57" s="1"/>
       <c r="I57" s="1"/>
     </row>
     <row r="58" spans="1:9">
-      <c r="A58" s="24"/>
+      <c r="A58" s="32"/>
       <c r="B58" s="14"/>
       <c r="C58" s="15" t="s">
         <v>71</v>
@@ -2360,13 +2360,13 @@
       </c>
       <c r="F58" s="16"/>
       <c r="G58" s="2" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="H58" s="1"/>
       <c r="I58" s="1"/>
     </row>
     <row r="59" spans="1:9">
-      <c r="A59" s="24"/>
+      <c r="A59" s="32"/>
       <c r="B59" s="14"/>
       <c r="C59" s="15" t="s">
         <v>72</v>
@@ -2379,13 +2379,13 @@
       </c>
       <c r="F59" s="16"/>
       <c r="G59" s="2" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="H59" s="1"/>
       <c r="I59" s="1"/>
     </row>
     <row r="60" spans="1:9">
-      <c r="A60" s="24"/>
+      <c r="A60" s="32"/>
       <c r="B60" s="14" t="s">
         <v>89</v>
       </c>
@@ -2400,13 +2400,13 @@
       </c>
       <c r="F60" s="16"/>
       <c r="G60" s="2" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="H60" s="1"/>
       <c r="I60" s="1"/>
     </row>
     <row r="61" spans="1:9" ht="13.5" customHeight="1">
-      <c r="A61" s="29" t="s">
+      <c r="A61" s="25" t="s">
         <v>40</v>
       </c>
       <c r="B61" s="18" t="s">
@@ -2423,12 +2423,12 @@
       </c>
       <c r="F61" s="1"/>
       <c r="G61" s="2" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="H61" s="1"/>
     </row>
     <row r="62" spans="1:9">
-      <c r="A62" s="29"/>
+      <c r="A62" s="25"/>
       <c r="B62" s="18" t="s">
         <v>107</v>
       </c>
@@ -2443,12 +2443,12 @@
       </c>
       <c r="F62" s="1"/>
       <c r="G62" s="2" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="H62" s="1"/>
     </row>
     <row r="63" spans="1:9" ht="27">
-      <c r="A63" s="29"/>
+      <c r="A63" s="25"/>
       <c r="B63" s="18" t="s">
         <v>109</v>
       </c>
@@ -2456,21 +2456,21 @@
         <v>108</v>
       </c>
       <c r="D63" s="2" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="E63" s="1" t="s">
         <v>58</v>
       </c>
       <c r="F63" s="1"/>
       <c r="G63" s="2" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="H63" s="1" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
     </row>
     <row r="64" spans="1:9" ht="27">
-      <c r="A64" s="29"/>
+      <c r="A64" s="25"/>
       <c r="B64" s="18" t="s">
         <v>92</v>
       </c>
@@ -2479,16 +2479,16 @@
         <v>45</v>
       </c>
       <c r="E64" s="16" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="F64" s="1"/>
       <c r="G64" s="2" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="H64" s="1"/>
     </row>
     <row r="65" spans="1:9" ht="27">
-      <c r="A65" s="29"/>
+      <c r="A65" s="25"/>
       <c r="B65" s="18" t="s">
         <v>93</v>
       </c>
@@ -2501,71 +2501,71 @@
       </c>
       <c r="F65" s="1"/>
       <c r="G65" s="2" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="H65" s="1"/>
     </row>
     <row r="66" spans="1:9">
-      <c r="A66" s="29"/>
-      <c r="B66" s="31" t="s">
+      <c r="A66" s="25"/>
+      <c r="B66" s="28" t="s">
         <v>110</v>
       </c>
       <c r="C66" s="1" t="s">
-        <v>111</v>
+        <v>137</v>
       </c>
       <c r="D66" s="1" t="s">
+        <v>132</v>
+      </c>
+      <c r="E66" s="16" t="s">
         <v>133</v>
-      </c>
-      <c r="E66" s="16" t="s">
-        <v>134</v>
       </c>
       <c r="F66" s="1"/>
       <c r="G66" s="2" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="H66" s="1"/>
     </row>
     <row r="67" spans="1:9">
-      <c r="A67" s="29"/>
-      <c r="B67" s="32"/>
+      <c r="A67" s="25"/>
+      <c r="B67" s="29"/>
       <c r="C67" s="1" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="D67" s="1" t="s">
+        <v>132</v>
+      </c>
+      <c r="E67" s="16" t="s">
         <v>133</v>
-      </c>
-      <c r="E67" s="16" t="s">
-        <v>134</v>
       </c>
       <c r="F67" s="1"/>
       <c r="G67" s="2" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="H67" s="1"/>
     </row>
     <row r="68" spans="1:9">
-      <c r="A68" s="29"/>
-      <c r="B68" s="32"/>
+      <c r="A68" s="25"/>
+      <c r="B68" s="29"/>
       <c r="C68" s="1" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="D68" s="1" t="s">
+        <v>132</v>
+      </c>
+      <c r="E68" s="16" t="s">
         <v>133</v>
-      </c>
-      <c r="E68" s="16" t="s">
-        <v>134</v>
       </c>
       <c r="F68" s="1"/>
       <c r="G68" s="2" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="H68" s="1"/>
     </row>
     <row r="69" spans="1:9">
-      <c r="A69" s="29"/>
-      <c r="B69" s="33"/>
+      <c r="A69" s="25"/>
+      <c r="B69" s="30"/>
       <c r="C69" s="1" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="D69" s="2" t="s">
         <v>65</v>
@@ -2575,17 +2575,17 @@
       </c>
       <c r="F69" s="1"/>
       <c r="G69" s="2" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="H69" s="1"/>
     </row>
     <row r="70" spans="1:9" ht="36.75" customHeight="1">
       <c r="A70" s="21"/>
-      <c r="B70" s="27" t="s">
+      <c r="B70" s="23" t="s">
         <v>99</v>
       </c>
-      <c r="C70" s="28"/>
-      <c r="D70" s="28"/>
+      <c r="C70" s="24"/>
+      <c r="D70" s="24"/>
       <c r="F70" s="16"/>
       <c r="G70" s="1"/>
       <c r="H70" s="1"/>
@@ -2594,11 +2594,6 @@
   </sheetData>
   <autoFilter ref="D1:D73"/>
   <mergeCells count="14">
-    <mergeCell ref="B70:D70"/>
-    <mergeCell ref="A61:A69"/>
-    <mergeCell ref="B26:B28"/>
-    <mergeCell ref="B30:B32"/>
-    <mergeCell ref="B66:B69"/>
     <mergeCell ref="B4:B8"/>
     <mergeCell ref="A45:A60"/>
     <mergeCell ref="A2:A44"/>
@@ -2608,6 +2603,11 @@
     <mergeCell ref="B33:B34"/>
     <mergeCell ref="B35:B36"/>
     <mergeCell ref="B37:B44"/>
+    <mergeCell ref="B70:D70"/>
+    <mergeCell ref="A61:A69"/>
+    <mergeCell ref="B26:B28"/>
+    <mergeCell ref="B30:B32"/>
+    <mergeCell ref="B66:B69"/>
   </mergeCells>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
